--- a/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
+++ b/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4448" uniqueCount="1375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4448" uniqueCount="1376">
   <si>
     <t>Campo</t>
   </si>
@@ -829,7 +829,7 @@
     <t>number</t>
   </si>
   <si>
-    <t>tipo di richiedente (1 - privato, 2 - ente pubblico) (decodifica ANSC_117)</t>
+    <t>tipo di richiedente decodifica ANSC_117, per usecase 1351 decodifica ANSC_134</t>
   </si>
   <si>
     <t>privato</t>
@@ -1630,6 +1630,9 @@
     <t>datiAssegnoMantenimento</t>
   </si>
   <si>
+    <t>di concordare l'assegno di mantenimento/divorzile di xxxx €</t>
+  </si>
+  <si>
     <t>Nel caso esista l'assegno di mantenimento o divorzile</t>
   </si>
   <si>
@@ -2749,7 +2752,7 @@
     <t>tipoRichiedente</t>
   </si>
   <si>
-    <t>Id del tipo richiedente (decodifica ANSC_64), per usecase 1334 e 1335 (decodifica ANSC_123), per usecase 1317 (decodifica ANSC_134)</t>
+    <t>Id del tipo richiedente (decodifica ANSC_64), per usecase 1334 e 1335 (decodifica ANSC_123), per usecase 1317 (decodifica ANSC_134), per usecase 1368 (decodifica ANSC_171)</t>
   </si>
   <si>
     <t>tipoLuogoNascita</t>
@@ -9375,10 +9378,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>64</v>
+        <v>509</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -9491,7 +9494,7 @@
     </row>
     <row r="8">
       <c r="A8" s="58" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>387</v>
@@ -9505,7 +9508,7 @@
     </row>
     <row r="9">
       <c r="A9" s="58" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B9" s="58" t="s">
         <v>5</v>
@@ -9519,7 +9522,7 @@
     </row>
     <row r="10">
       <c r="A10" s="58" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B10" s="58" t="s">
         <v>387</v>
@@ -9693,16 +9696,16 @@
     </row>
     <row r="5">
       <c r="A5" s="60" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B5" s="60" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6">
@@ -9713,7 +9716,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="60" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D6" s="60" t="s">
         <v>500</v>
@@ -9777,7 +9780,7 @@
     </row>
     <row r="11">
       <c r="A11" s="60" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B11" s="60" t="s">
         <v>347</v>
@@ -9797,10 +9800,10 @@
         <v>5</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>64</v>
+        <v>509</v>
       </c>
       <c r="D12" s="60" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13">
@@ -9814,12 +9817,12 @@
         <v>503</v>
       </c>
       <c r="D13" s="60" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="60" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B14" s="60" t="s">
         <v>387</v>
@@ -9833,7 +9836,7 @@
     </row>
     <row r="15">
       <c r="A15" s="60" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B15" s="60" t="s">
         <v>347</v>
@@ -9871,7 +9874,7 @@
     </row>
     <row r="2">
       <c r="A2" s="62" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B2" s="62" t="s">
         <v>347</v>
@@ -9885,7 +9888,7 @@
     </row>
     <row r="3">
       <c r="A3" s="62" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B3" s="62" t="s">
         <v>347</v>
@@ -9899,7 +9902,7 @@
     </row>
     <row r="4">
       <c r="A4" s="62" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B4" s="62" t="s">
         <v>361</v>
@@ -9951,7 +9954,7 @@
     </row>
     <row r="3">
       <c r="A3" s="64" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B3" s="64" t="s">
         <v>5</v>
@@ -9960,7 +9963,7 @@
         <v>64</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -9989,7 +9992,7 @@
     </row>
     <row r="2">
       <c r="A2" s="66" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B2" s="66" t="s">
         <v>5</v>
@@ -9998,12 +10001,12 @@
         <v>193</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="66" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B3" s="66" t="s">
         <v>5</v>
@@ -10012,26 +10015,26 @@
         <v>193</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="66" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B4" s="66" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="66" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B5" s="66" t="s">
         <v>5</v>
@@ -10040,7 +10043,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -10069,7 +10072,7 @@
     </row>
     <row r="2">
       <c r="A2" s="68" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B2" s="68" t="s">
         <v>5</v>
@@ -10083,7 +10086,7 @@
     </row>
     <row r="3">
       <c r="A3" s="68" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B3" s="68" t="s">
         <v>5</v>
@@ -10106,7 +10109,7 @@
         <v>333</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -10135,16 +10138,16 @@
     </row>
     <row r="2">
       <c r="A2" s="70" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B2" s="70" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="70" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D2" s="70" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -10173,24 +10176,24 @@
     </row>
     <row r="2">
       <c r="A2" s="72" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B2" s="72" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D2" s="72" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="72" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B3" s="72" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C3" s="72" t="s">
         <v>64</v>
@@ -10201,16 +10204,16 @@
     </row>
     <row r="4">
       <c r="A4" s="72" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B4" s="72" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="72" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D4" s="72" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -10253,7 +10256,7 @@
     </row>
     <row r="3">
       <c r="A3" s="74" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B3" s="74" t="s">
         <v>5</v>
@@ -10291,16 +10294,16 @@
     </row>
     <row r="2">
       <c r="A2" s="76" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B2" s="76" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D2" s="76" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -10433,7 +10436,7 @@
     </row>
     <row r="2">
       <c r="A2" s="80" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B2" s="80" t="s">
         <v>345</v>
@@ -10447,7 +10450,7 @@
     </row>
     <row r="3">
       <c r="A3" s="80" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B3" s="80" t="s">
         <v>387</v>
@@ -10522,7 +10525,7 @@
         <v>64</v>
       </c>
       <c r="D4" s="82" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -10665,113 +10668,113 @@
         <v>5</v>
       </c>
       <c r="C2" s="88" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D2" s="88" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="88" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B3" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="88" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D3" s="88" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B4" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="88" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D4" s="88" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="88" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B5" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="88" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D5" s="88" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="88" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B6" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="88" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B7" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="88" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D7" s="88" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="88" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B8" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D8" s="88" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="88" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B9" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="88" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B10" s="88" t="s">
         <v>5</v>
@@ -10780,68 +10783,68 @@
         <v>15</v>
       </c>
       <c r="D10" s="88" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="88" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B11" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="88" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D11" s="88" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="88" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B12" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="88" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B13" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="88" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D13" s="88" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="88" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B14" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="88" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B15" s="88" t="s">
         <v>5</v>
@@ -10850,82 +10853,82 @@
         <v>72</v>
       </c>
       <c r="D15" s="88" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="88" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B16" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="88" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="88" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B17" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="88" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B18" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="88" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D18" s="88" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="88" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B19" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D19" s="88" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="88" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B20" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="88" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D20" s="88" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="88" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B21" s="88" t="s">
         <v>5</v>
@@ -10934,49 +10937,49 @@
         <v>72</v>
       </c>
       <c r="D21" s="88" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="88" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B22" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="88" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D22" s="88" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="88" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B23" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="88" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D23" s="88" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="88" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B24" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="88" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D24" s="88" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="25">
@@ -10990,12 +10993,12 @@
         <v>314</v>
       </c>
       <c r="D25" s="88" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="88" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B26" s="88" t="s">
         <v>5</v>
@@ -11004,26 +11007,26 @@
         <v>15</v>
       </c>
       <c r="D26" s="88" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="88" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B27" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="88" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D27" s="88" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="88" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B28" s="88" t="s">
         <v>5</v>
@@ -11032,12 +11035,12 @@
         <v>64</v>
       </c>
       <c r="D28" s="88" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="88" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B29" s="88" t="s">
         <v>5</v>
@@ -11046,21 +11049,21 @@
         <v>15</v>
       </c>
       <c r="D29" s="88" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="88" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B30" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="88" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D30" s="88" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="31">
@@ -11079,7 +11082,7 @@
     </row>
     <row r="32">
       <c r="A32" s="88" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B32" s="88" t="s">
         <v>59</v>
@@ -11088,12 +11091,12 @@
         <v>99</v>
       </c>
       <c r="D32" s="88" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="88" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B33" s="88" t="s">
         <v>59</v>
@@ -11102,12 +11105,12 @@
         <v>99</v>
       </c>
       <c r="D33" s="88" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="88" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B34" s="88" t="s">
         <v>59</v>
@@ -11116,40 +11119,40 @@
         <v>99</v>
       </c>
       <c r="D34" s="88" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="88" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B35" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D35" s="88" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="88" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B36" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D36" s="88" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="88" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B37" s="88" t="s">
         <v>5</v>
@@ -11158,29 +11161,29 @@
         <v>72</v>
       </c>
       <c r="D37" s="88" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="88" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B38" s="88" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="88" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D38" s="88" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="88" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B39" s="88" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C39" s="88" t="s">
         <v>64</v>
@@ -11191,10 +11194,10 @@
     </row>
     <row r="40">
       <c r="A40" s="88" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B40" s="88" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C40" s="88" t="s">
         <v>64</v>
@@ -11214,12 +11217,12 @@
         <v>299</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="88" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B42" s="88" t="s">
         <v>59</v>
@@ -11228,12 +11231,12 @@
         <v>99</v>
       </c>
       <c r="D42" s="88" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="88" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B43" s="88" t="s">
         <v>59</v>
@@ -11242,7 +11245,7 @@
         <v>99</v>
       </c>
       <c r="D43" s="88" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="44">
@@ -11285,7 +11288,7 @@
     </row>
     <row r="2">
       <c r="A2" s="90" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B2" s="90" t="s">
         <v>5</v>
@@ -11294,12 +11297,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="90" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="90" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B3" s="90" t="s">
         <v>5</v>
@@ -11308,12 +11311,12 @@
         <v>193</v>
       </c>
       <c r="D3" s="90" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="90" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B4" s="90" t="s">
         <v>5</v>
@@ -11322,40 +11325,40 @@
         <v>193</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="90" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B5" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="90" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D5" s="90" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="90" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B6" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="90" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D6" s="90" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="90" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B7" s="90" t="s">
         <v>5</v>
@@ -11364,12 +11367,12 @@
         <v>72</v>
       </c>
       <c r="D7" s="90" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="90" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B8" s="90" t="s">
         <v>5</v>
@@ -11378,96 +11381,96 @@
         <v>72</v>
       </c>
       <c r="D8" s="90" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="90" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B9" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="90" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D9" s="90" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="90" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B10" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="90" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="90" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B11" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="90" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D11" s="90" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="90" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B12" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="90" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D12" s="90" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="90" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B13" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="90" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D13" s="90" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="90" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B14" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="90" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D14" s="90" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="90" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B15" s="90" t="s">
         <v>5</v>
@@ -11476,21 +11479,21 @@
         <v>3</v>
       </c>
       <c r="D15" s="90" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="90" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B16" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="90" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D16" s="90" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -11553,10 +11556,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="92" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D4" s="92" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -11595,15 +11598,15 @@
         <v>5</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D2" s="94" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="94" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B3" s="94" t="s">
         <v>5</v>
@@ -11612,40 +11615,40 @@
         <v>15</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="94" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B4" s="94" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="94" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B5" s="94" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="94" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D5" s="94" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="94" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B6" s="94" t="s">
         <v>5</v>
@@ -11654,12 +11657,12 @@
         <v>369</v>
       </c>
       <c r="D6" s="94" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="94" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B7" s="94" t="s">
         <v>5</v>
@@ -11668,12 +11671,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="94" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B8" s="94" t="s">
         <v>5</v>
@@ -11682,7 +11685,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="94" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -11700,7 +11703,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -11748,12 +11751,12 @@
         <v>314</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="96" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B5" s="96" t="s">
         <v>5</v>
@@ -11762,26 +11765,26 @@
         <v>64</v>
       </c>
       <c r="D5" s="96" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="96" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B6" s="96" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="96" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="96" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B7" s="96" t="s">
         <v>5</v>
@@ -11790,7 +11793,7 @@
         <v>40</v>
       </c>
       <c r="D7" s="96" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -11809,7 +11812,7 @@
     </row>
     <row r="9">
       <c r="A9" s="96" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B9" s="96" t="s">
         <v>5</v>
@@ -11818,12 +11821,12 @@
         <v>102</v>
       </c>
       <c r="D9" s="96" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="96" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B10" s="96" t="s">
         <v>5</v>
@@ -11832,26 +11835,26 @@
         <v>64</v>
       </c>
       <c r="D10" s="96" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="96" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="96" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D11" s="96" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="96" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B12" s="96" t="s">
         <v>5</v>
@@ -11860,12 +11863,12 @@
         <v>102</v>
       </c>
       <c r="D12" s="96" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="96" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B13" s="96" t="s">
         <v>5</v>
@@ -11874,7 +11877,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="96" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14">
@@ -11907,7 +11910,7 @@
     </row>
     <row r="16">
       <c r="A16" s="96" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B16" s="96" t="s">
         <v>5</v>
@@ -11916,12 +11919,12 @@
         <v>15</v>
       </c>
       <c r="D16" s="96" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="96" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B17" s="96" t="s">
         <v>5</v>
@@ -11930,40 +11933,40 @@
         <v>15</v>
       </c>
       <c r="D17" s="96" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="96" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B18" s="96" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="96" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D18" s="96" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="96" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B19" s="96" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="96" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D19" s="96" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="96" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B20" s="96" t="s">
         <v>5</v>
@@ -11972,7 +11975,7 @@
         <v>40</v>
       </c>
       <c r="D20" s="96" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -11993,7 +11996,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="98" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -12018,21 +12021,21 @@
     </row>
     <row r="3">
       <c r="A3" s="98" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B3" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="98" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D3" s="98" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="98" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B4" s="98" t="s">
         <v>5</v>
@@ -12041,26 +12044,26 @@
         <v>15</v>
       </c>
       <c r="D4" s="98" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="98" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B5" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="98" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D5" s="98" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="98" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B6" s="98" t="s">
         <v>5</v>
@@ -12069,21 +12072,21 @@
         <v>15</v>
       </c>
       <c r="D6" s="98" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="98" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B7" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="98" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D7" s="98" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -12517,58 +12520,58 @@
     </row>
     <row r="2">
       <c r="A2" s="100" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B2" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="100" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D2" s="100" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="100" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B3" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="100" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D3" s="100" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="100" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B4" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="100" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D4" s="100" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="100" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B5" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="100" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D5" s="100" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="6">
@@ -12582,7 +12585,7 @@
         <v>324</v>
       </c>
       <c r="D6" s="100" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -12593,10 +12596,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="100" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D7" s="100" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8">
@@ -12607,24 +12610,24 @@
         <v>5</v>
       </c>
       <c r="C8" s="100" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D8" s="100" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="100" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B9" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="100" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D9" s="100" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10">
@@ -12638,7 +12641,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="100" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
   </sheetData>
@@ -12667,30 +12670,30 @@
     </row>
     <row r="2">
       <c r="A2" s="102" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B2" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="102" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D2" s="102" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="102" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B3" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="102" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D3" s="102" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="4">
@@ -12709,21 +12712,21 @@
     </row>
     <row r="5">
       <c r="A5" s="102" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B5" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="102" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D5" s="102" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="102" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B6" s="102" t="s">
         <v>5</v>
@@ -12732,12 +12735,12 @@
         <v>64</v>
       </c>
       <c r="D6" s="102" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="102" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B7" s="102" t="s">
         <v>5</v>
@@ -12746,7 +12749,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="102" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8">
@@ -12803,7 +12806,7 @@
     </row>
     <row r="3">
       <c r="A3" s="104" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B3" s="104" t="s">
         <v>5</v>
@@ -12812,12 +12815,12 @@
         <v>66</v>
       </c>
       <c r="D3" s="104" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="104" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B4" s="104" t="s">
         <v>5</v>
@@ -12826,12 +12829,12 @@
         <v>69</v>
       </c>
       <c r="D4" s="104" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="104" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B5" s="104" t="s">
         <v>5</v>
@@ -12840,12 +12843,12 @@
         <v>72</v>
       </c>
       <c r="D5" s="104" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="104" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B6" s="104" t="s">
         <v>5</v>
@@ -12854,35 +12857,35 @@
         <v>72</v>
       </c>
       <c r="D6" s="104" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="104" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B7" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="104" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D7" s="104" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="104" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B8" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="104" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D8" s="104" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9">
@@ -12915,72 +12918,72 @@
     </row>
     <row r="11">
       <c r="A11" s="104" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B11" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="104" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D11" s="104" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="104" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B12" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="104" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D12" s="104" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="104" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B13" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="104" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D13" s="104" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="104" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B14" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="104" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D14" s="104" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="104" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B15" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="104" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D15" s="104" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="16">
@@ -12991,15 +12994,15 @@
         <v>5</v>
       </c>
       <c r="C16" s="104" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D16" s="104" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="104" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B17" s="104" t="s">
         <v>5</v>
@@ -13008,40 +13011,40 @@
         <v>35</v>
       </c>
       <c r="D17" s="104" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="104" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B18" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="104" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D18" s="104" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="104" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B19" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="104" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D19" s="104" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="104" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B20" s="104" t="s">
         <v>5</v>
@@ -13050,21 +13053,21 @@
         <v>45</v>
       </c>
       <c r="D20" s="104" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="104" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B21" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="104" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D21" s="104" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="22">
@@ -13107,49 +13110,49 @@
     </row>
     <row r="2">
       <c r="A2" s="106" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B2" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="106" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="106" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B3" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="106" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D3" s="106" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="106" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B4" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="106" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D4" s="106" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="106" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B5" s="106" t="s">
         <v>5</v>
@@ -13158,7 +13161,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="106" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
   </sheetData>
@@ -13187,7 +13190,7 @@
     </row>
     <row r="2">
       <c r="A2" s="108" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B2" s="108" t="s">
         <v>5</v>
@@ -13196,12 +13199,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="108" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="108" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B3" s="108" t="s">
         <v>5</v>
@@ -13210,7 +13213,7 @@
         <v>137</v>
       </c>
       <c r="D3" s="108" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -13248,21 +13251,21 @@
         <v>15</v>
       </c>
       <c r="D2" s="110" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="110" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B3" s="110" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="110" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D3" s="110" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="4">
@@ -13361,7 +13364,7 @@
     </row>
     <row r="3">
       <c r="A3" s="112" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B3" s="112" t="s">
         <v>5</v>
@@ -13370,12 +13373,12 @@
         <v>15</v>
       </c>
       <c r="D3" s="112" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="112" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B4" s="112" t="s">
         <v>5</v>
@@ -13384,21 +13387,21 @@
         <v>15</v>
       </c>
       <c r="D4" s="112" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="112" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B5" s="112" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="112" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D5" s="112" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="6">
@@ -13431,21 +13434,21 @@
     </row>
     <row r="8">
       <c r="A8" s="112" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B8" s="112" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="112" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D8" s="112" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="112" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B9" s="112" t="s">
         <v>5</v>
@@ -13454,12 +13457,12 @@
         <v>78</v>
       </c>
       <c r="D9" s="112" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="112" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B10" s="112" t="s">
         <v>59</v>
@@ -13468,12 +13471,12 @@
         <v>99</v>
       </c>
       <c r="D10" s="112" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="112" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B11" s="112" t="s">
         <v>59</v>
@@ -13482,12 +13485,12 @@
         <v>99</v>
       </c>
       <c r="D11" s="112" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="112" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B12" s="112" t="s">
         <v>59</v>
@@ -13496,12 +13499,12 @@
         <v>99</v>
       </c>
       <c r="D12" s="112" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="112" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B13" s="112" t="s">
         <v>59</v>
@@ -13510,12 +13513,12 @@
         <v>99</v>
       </c>
       <c r="D13" s="112" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="112" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B14" s="112" t="s">
         <v>59</v>
@@ -13524,12 +13527,12 @@
         <v>60</v>
       </c>
       <c r="D14" s="112" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="112" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B15" s="112" t="s">
         <v>5</v>
@@ -13538,7 +13541,7 @@
         <v>369</v>
       </c>
       <c r="D15" s="112" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="16">
@@ -13595,30 +13598,30 @@
     </row>
     <row r="2">
       <c r="A2" s="114" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B2" s="114" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="114" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D2" s="114" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="114" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B3" s="114" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="114" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D3" s="114" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -13647,7 +13650,7 @@
     </row>
     <row r="2">
       <c r="A2" s="116" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B2" s="116" t="s">
         <v>59</v>
@@ -13656,7 +13659,7 @@
         <v>99</v>
       </c>
       <c r="D2" s="116" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="3">
@@ -13678,7 +13681,7 @@
         <v>451</v>
       </c>
       <c r="B4" s="116" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C4" s="116" t="s">
         <v>64</v>
@@ -13716,7 +13719,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="118" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -13741,30 +13744,30 @@
     </row>
     <row r="3">
       <c r="A3" s="118" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B3" s="118" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="118" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D3" s="118" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="118" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B4" s="118" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>
@@ -13865,7 +13868,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="120" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -13890,21 +13893,21 @@
     </row>
     <row r="3">
       <c r="A3" s="120" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B3" s="120" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="120" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D3" s="120" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="120" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B4" s="120" t="s">
         <v>5</v>
@@ -13913,7 +13916,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="120" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="5">
@@ -13938,10 +13941,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="120" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D6" s="120" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
   </sheetData>
@@ -13962,7 +13965,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -13987,7 +13990,7 @@
     </row>
     <row r="3">
       <c r="A3" s="122" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B3" s="122" t="s">
         <v>5</v>
@@ -13996,21 +13999,21 @@
         <v>15</v>
       </c>
       <c r="D3" s="122" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="122" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B4" s="122" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="122" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D4" s="122" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="5">
@@ -14046,7 +14049,7 @@
         <v>453</v>
       </c>
       <c r="B7" s="122" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C7" s="122" t="s">
         <v>64</v>
@@ -14060,7 +14063,7 @@
         <v>434</v>
       </c>
       <c r="B8" s="122" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C8" s="122" t="s">
         <v>64</v>
@@ -14071,7 +14074,7 @@
     </row>
     <row r="9">
       <c r="A9" s="122" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B9" s="122" t="s">
         <v>166</v>
@@ -14099,7 +14102,7 @@
     </row>
     <row r="11">
       <c r="A11" s="122" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B11" s="122" t="s">
         <v>166</v>
@@ -14167,7 +14170,7 @@
         <v>373</v>
       </c>
       <c r="B1" s="126" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14206,7 +14209,7 @@
     </row>
     <row r="4">
       <c r="A4" s="126" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B4" s="126" t="s">
         <v>5</v>
@@ -14215,12 +14218,12 @@
         <v>15</v>
       </c>
       <c r="D4" s="126" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="126" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B5" s="126" t="s">
         <v>5</v>
@@ -14229,7 +14232,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="126" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="6">
@@ -14240,7 +14243,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="126" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D6" s="126" t="s">
         <v>464</v>
@@ -14248,7 +14251,7 @@
     </row>
     <row r="7">
       <c r="A7" s="126" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B7" s="126" t="s">
         <v>5</v>
@@ -14257,12 +14260,12 @@
         <v>139</v>
       </c>
       <c r="D7" s="126" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="126" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B8" s="126" t="s">
         <v>5</v>
@@ -14271,12 +14274,12 @@
         <v>64</v>
       </c>
       <c r="D8" s="126" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="126" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B9" s="126" t="s">
         <v>59</v>
@@ -14285,26 +14288,26 @@
         <v>99</v>
       </c>
       <c r="D9" s="126" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="126" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B10" s="126" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="126" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D10" s="126" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="126" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B11" s="126" t="s">
         <v>5</v>
@@ -14313,7 +14316,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="126" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="12">
@@ -14332,35 +14335,35 @@
     </row>
     <row r="13">
       <c r="A13" s="126" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B13" s="126" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="126" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D13" s="126" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="126" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B14" s="126" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="126" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D14" s="126" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="126" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B15" s="126" t="s">
         <v>5</v>
@@ -14369,26 +14372,26 @@
         <v>15</v>
       </c>
       <c r="D15" s="126" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="126" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B16" s="126" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="126" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D16" s="126" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="126" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B17" s="126" t="s">
         <v>5</v>
@@ -14397,63 +14400,63 @@
         <v>15</v>
       </c>
       <c r="D17" s="126" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="126" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B18" s="126" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="126" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D18" s="126" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="126" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B19" s="126" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="126" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D19" s="126" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="126" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B20" s="126" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="126" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D20" s="126" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="126" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B21" s="126" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="126" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D21" s="126" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="22">
@@ -14500,7 +14503,7 @@
     </row>
     <row r="25">
       <c r="A25" s="126" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B25" s="126" t="s">
         <v>59</v>
@@ -14509,12 +14512,12 @@
         <v>60</v>
       </c>
       <c r="D25" s="126" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="126" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B26" s="126" t="s">
         <v>5</v>
@@ -14523,7 +14526,7 @@
         <v>27</v>
       </c>
       <c r="D26" s="126" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="27">
@@ -14559,13 +14562,13 @@
         <v>403</v>
       </c>
       <c r="B29" s="126" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C29" s="126" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="126" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -14626,16 +14629,16 @@
     </row>
     <row r="4">
       <c r="A4" s="128" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B4" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="128" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D4" s="128" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="5">
@@ -14646,10 +14649,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="128" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D5" s="128" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="6">
@@ -14660,10 +14663,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="128" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D6" s="128" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7">
@@ -14677,7 +14680,7 @@
         <v>66</v>
       </c>
       <c r="D7" s="128" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -14688,7 +14691,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D8" s="128" t="s">
         <v>258</v>
@@ -14705,7 +14708,7 @@
         <v>72</v>
       </c>
       <c r="D9" s="128" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="10">
@@ -14741,7 +14744,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="130" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14794,7 +14797,7 @@
     </row>
     <row r="5">
       <c r="A5" s="130" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B5" s="130" t="s">
         <v>5</v>
@@ -14803,21 +14806,21 @@
         <v>15</v>
       </c>
       <c r="D5" s="130" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="130" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B6" s="130" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="130" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D6" s="130" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
   </sheetData>
@@ -14851,7 +14854,7 @@
     </row>
     <row r="2">
       <c r="A2" s="132" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B2" s="132" t="s">
         <v>59</v>
@@ -14860,7 +14863,7 @@
         <v>60</v>
       </c>
       <c r="D2" s="132" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="3">
@@ -14868,7 +14871,7 @@
         <v>353</v>
       </c>
       <c r="B3" s="132" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C3" s="132" t="s">
         <v>64</v>
@@ -14888,7 +14891,7 @@
         <v>356</v>
       </c>
       <c r="D4" s="132" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="5">
@@ -14907,49 +14910,49 @@
     </row>
     <row r="6">
       <c r="A6" s="132" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B6" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="132" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D6" s="132" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="132" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B7" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="132" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D7" s="132" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="132" t="s">
+        <v>945</v>
+      </c>
+      <c r="B8" s="132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="132" t="s">
+        <v>946</v>
+      </c>
+      <c r="D8" s="132" t="s">
         <v>944</v>
-      </c>
-      <c r="B8" s="132" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="132" t="s">
-        <v>945</v>
-      </c>
-      <c r="D8" s="132" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="132" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B9" s="132" t="s">
         <v>59</v>
@@ -14958,12 +14961,12 @@
         <v>60</v>
       </c>
       <c r="D9" s="132" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="132" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B10" s="132" t="s">
         <v>5</v>
@@ -14972,7 +14975,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="132" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="11">
@@ -14991,7 +14994,7 @@
     </row>
     <row r="12">
       <c r="A12" s="132" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B12" s="132" t="s">
         <v>5</v>
@@ -15000,7 +15003,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="132" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="13">
@@ -15019,7 +15022,7 @@
     </row>
     <row r="14">
       <c r="A14" s="132" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B14" s="132" t="s">
         <v>5</v>
@@ -15028,12 +15031,12 @@
         <v>15</v>
       </c>
       <c r="D14" s="132" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="132" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B15" s="132" t="s">
         <v>5</v>
@@ -15042,12 +15045,12 @@
         <v>15</v>
       </c>
       <c r="D15" s="132" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="132" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B16" s="132" t="s">
         <v>5</v>
@@ -15056,12 +15059,12 @@
         <v>72</v>
       </c>
       <c r="D16" s="132" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="132" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B17" s="132" t="s">
         <v>5</v>
@@ -15070,54 +15073,54 @@
         <v>75</v>
       </c>
       <c r="D17" s="132" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="132" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B18" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="132" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D18" s="132" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="132" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B19" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="132" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D19" s="132" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="132" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B20" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="132" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D20" s="132" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="132" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B21" s="132" t="s">
         <v>5</v>
@@ -15126,7 +15129,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="132" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="22">
@@ -15151,15 +15154,15 @@
         <v>5</v>
       </c>
       <c r="C23" s="132" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D23" s="132" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="132" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B24" s="132" t="s">
         <v>59</v>
@@ -15168,7 +15171,7 @@
         <v>60</v>
       </c>
       <c r="D24" s="132" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="25">
@@ -15187,105 +15190,105 @@
     </row>
     <row r="26">
       <c r="A26" s="132" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B26" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="132" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D26" s="132" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="132" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B27" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="132" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D27" s="132" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="132" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B28" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="132" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D28" s="132" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="132" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B29" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="132" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D29" s="132" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="132" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B30" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="132" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D30" s="132" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="132" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B31" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="132" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D31" s="132" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="132" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B32" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="132" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D32" s="132" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="132" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B33" s="132" t="s">
         <v>59</v>
@@ -15294,7 +15297,7 @@
         <v>60</v>
       </c>
       <c r="D33" s="132" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="34">
@@ -15305,7 +15308,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="132" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D34" s="132" t="s">
         <v>367</v>
@@ -15313,7 +15316,7 @@
     </row>
     <row r="35">
       <c r="A35" s="132" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B35" s="132" t="s">
         <v>5</v>
@@ -15322,12 +15325,12 @@
         <v>15</v>
       </c>
       <c r="D35" s="132" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="132" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B36" s="132" t="s">
         <v>5</v>
@@ -15336,21 +15339,21 @@
         <v>15</v>
       </c>
       <c r="D36" s="132" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="132" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B37" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="132" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D37" s="132" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="38">
@@ -15364,7 +15367,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="132" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="39">
@@ -15378,12 +15381,12 @@
         <v>15</v>
       </c>
       <c r="D39" s="132" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="132" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B40" s="132" t="s">
         <v>5</v>
@@ -15392,40 +15395,40 @@
         <v>15</v>
       </c>
       <c r="D40" s="132" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="132" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B41" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="132" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D41" s="132" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="132" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B42" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="132" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D42" s="132" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="132" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B43" s="132" t="s">
         <v>5</v>
@@ -15434,21 +15437,21 @@
         <v>15</v>
       </c>
       <c r="D43" s="132" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="132" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B44" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="132" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D44" s="132" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
   </sheetData>
@@ -15466,7 +15469,7 @@
         <v>373</v>
       </c>
       <c r="B1" s="134" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -15505,16 +15508,16 @@
     </row>
     <row r="4">
       <c r="A4" s="134" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B4" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="134" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D4" s="134" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="5">
@@ -15525,7 +15528,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D5" s="134" t="s">
         <v>473</v>
@@ -15533,7 +15536,7 @@
     </row>
     <row r="6">
       <c r="A6" s="134" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B6" s="134" t="s">
         <v>5</v>
@@ -15542,26 +15545,26 @@
         <v>64</v>
       </c>
       <c r="D6" s="134" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="134" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B7" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D7" s="134" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="134" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B8" s="134" t="s">
         <v>5</v>
@@ -15570,77 +15573,77 @@
         <v>78</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="134" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B9" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="134" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B10" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="134" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B11" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D11" s="134" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="134" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B12" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D12" s="134" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="134" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B13" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D13" s="134" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="14">
@@ -15668,12 +15671,12 @@
         <v>15</v>
       </c>
       <c r="D15" s="134" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="134" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B16" s="134" t="s">
         <v>59</v>
@@ -15682,12 +15685,12 @@
         <v>60</v>
       </c>
       <c r="D16" s="134" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="134" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B17" s="134" t="s">
         <v>59</v>
@@ -15696,7 +15699,7 @@
         <v>60</v>
       </c>
       <c r="D17" s="134" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="18">
@@ -15732,7 +15735,7 @@
         <v>373</v>
       </c>
       <c r="B1" s="136" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -15771,21 +15774,21 @@
     </row>
     <row r="4">
       <c r="A4" s="136" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B4" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="136" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D4" s="136" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="136" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B5" s="136" t="s">
         <v>5</v>
@@ -15794,7 +15797,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="136" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="6">
@@ -15886,7 +15889,7 @@
         <v>373</v>
       </c>
       <c r="B1" s="138" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -15925,16 +15928,16 @@
     </row>
     <row r="4">
       <c r="A4" s="138" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B4" s="138" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5">
@@ -16022,7 +16025,7 @@
         <v>373</v>
       </c>
       <c r="B1" s="140" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16061,7 +16064,7 @@
     </row>
     <row r="4">
       <c r="A4" s="140" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B4" s="140" t="s">
         <v>59</v>
@@ -16070,7 +16073,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="140" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="5">
@@ -16103,7 +16106,7 @@
     </row>
     <row r="7">
       <c r="A7" s="140" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B7" s="140" t="s">
         <v>5</v>
@@ -16112,35 +16115,35 @@
         <v>15</v>
       </c>
       <c r="D7" s="140" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="140" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B8" s="140" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="140" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D8" s="140" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="140" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B9" s="140" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="140" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D9" s="140" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -16162,7 +16165,7 @@
         <v>373</v>
       </c>
       <c r="B1" s="142" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16201,7 +16204,7 @@
     </row>
     <row r="4">
       <c r="A4" s="142" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B4" s="142" t="s">
         <v>5</v>
@@ -16210,21 +16213,21 @@
         <v>64</v>
       </c>
       <c r="D4" s="142" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="142" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B5" s="142" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="142" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D5" s="142" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="6">
@@ -16243,7 +16246,7 @@
     </row>
     <row r="7">
       <c r="A7" s="142" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B7" s="142" t="s">
         <v>5</v>
@@ -16252,12 +16255,12 @@
         <v>15</v>
       </c>
       <c r="D7" s="142" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="142" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B8" s="142" t="s">
         <v>59</v>
@@ -16266,35 +16269,35 @@
         <v>60</v>
       </c>
       <c r="D8" s="142" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="142" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B9" s="142" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="142" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D9" s="142" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="142" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B10" s="142" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="142" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D10" s="142" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -16327,7 +16330,7 @@
     </row>
     <row r="2">
       <c r="A2" s="144" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B2" s="144" t="s">
         <v>5</v>
@@ -16336,12 +16339,12 @@
         <v>66</v>
       </c>
       <c r="D2" s="144" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="144" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B3" s="144" t="s">
         <v>5</v>
@@ -16350,12 +16353,12 @@
         <v>69</v>
       </c>
       <c r="D3" s="144" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="144" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B4" s="144" t="s">
         <v>5</v>
@@ -16364,12 +16367,12 @@
         <v>72</v>
       </c>
       <c r="D4" s="144" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="144" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B5" s="144" t="s">
         <v>5</v>
@@ -16378,40 +16381,40 @@
         <v>72</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="144" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B6" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="144" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D6" s="144" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="144" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B7" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="144" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D7" s="144" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="144" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B8" s="144" t="s">
         <v>5</v>
@@ -16420,12 +16423,12 @@
         <v>324</v>
       </c>
       <c r="D8" s="144" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="144" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B9" s="144" t="s">
         <v>5</v>
@@ -16434,21 +16437,21 @@
         <v>327</v>
       </c>
       <c r="D9" s="144" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="144" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B10" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="144" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D10" s="144" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="11">
@@ -16505,35 +16508,35 @@
     </row>
     <row r="3">
       <c r="A3" s="146" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B3" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="146" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D3" s="146" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="146" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B4" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="146" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D4" s="146" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="146" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B5" s="146" t="s">
         <v>5</v>
@@ -16542,7 +16545,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="146" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="6">
@@ -16556,35 +16559,35 @@
         <v>15</v>
       </c>
       <c r="D6" s="146" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="146" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B7" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="146" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D7" s="146" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="146" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B8" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="146" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D8" s="146" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="9">
@@ -16617,7 +16620,7 @@
     </row>
     <row r="11">
       <c r="A11" s="146" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B11" s="146" t="s">
         <v>5</v>
@@ -16626,12 +16629,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="146" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="146" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B12" s="146" t="s">
         <v>5</v>
@@ -16640,7 +16643,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="146" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="13">
@@ -16659,7 +16662,7 @@
     </row>
     <row r="14">
       <c r="A14" s="146" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B14" s="146" t="s">
         <v>5</v>
@@ -16668,7 +16671,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="146" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="15">
@@ -16682,21 +16685,21 @@
         <v>428</v>
       </c>
       <c r="D15" s="146" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="146" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B16" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="146" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D16" s="146" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="17">
@@ -16757,7 +16760,7 @@
     </row>
     <row r="21">
       <c r="A21" s="146" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B21" s="146" t="s">
         <v>5</v>
@@ -16766,7 +16769,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="146" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="22">
@@ -16785,7 +16788,7 @@
     </row>
     <row r="23">
       <c r="A23" s="146" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B23" s="146" t="s">
         <v>59</v>
@@ -16794,15 +16797,15 @@
         <v>60</v>
       </c>
       <c r="D23" s="146" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="146" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B24" s="146" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C24" s="146" t="s">
         <v>64</v>
@@ -16813,10 +16816,10 @@
     </row>
     <row r="25">
       <c r="A25" s="146" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B25" s="146" t="s">
         <v>1098</v>
-      </c>
-      <c r="B25" s="146" t="s">
-        <v>1097</v>
       </c>
       <c r="C25" s="146" t="s">
         <v>64</v>
@@ -16827,7 +16830,7 @@
     </row>
     <row r="26">
       <c r="A26" s="146" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B26" s="146" t="s">
         <v>59</v>
@@ -16836,12 +16839,12 @@
         <v>60</v>
       </c>
       <c r="D26" s="146" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="146" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B27" s="146" t="s">
         <v>59</v>
@@ -16850,7 +16853,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="146" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="28">
@@ -16869,7 +16872,7 @@
     </row>
     <row r="29">
       <c r="A29" s="146" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B29" s="146" t="s">
         <v>59</v>
@@ -16878,12 +16881,12 @@
         <v>60</v>
       </c>
       <c r="D29" s="146" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="146" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B30" s="146" t="s">
         <v>59</v>
@@ -16892,7 +16895,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="146" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="31">
@@ -16911,7 +16914,7 @@
     </row>
     <row r="32">
       <c r="A32" s="146" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B32" s="146" t="s">
         <v>59</v>
@@ -16920,7 +16923,7 @@
         <v>60</v>
       </c>
       <c r="D32" s="146" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="33">
@@ -16939,7 +16942,7 @@
     </row>
     <row r="34">
       <c r="A34" s="146" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B34" s="146" t="s">
         <v>5</v>
@@ -16948,12 +16951,12 @@
         <v>15</v>
       </c>
       <c r="D34" s="146" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="146" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B35" s="146" t="s">
         <v>5</v>
@@ -16962,12 +16965,12 @@
         <v>27</v>
       </c>
       <c r="D35" s="146" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="146" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B36" s="146" t="s">
         <v>59</v>
@@ -16976,7 +16979,7 @@
         <v>99</v>
       </c>
       <c r="D36" s="146" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="37">
@@ -17026,7 +17029,7 @@
         <v>393</v>
       </c>
       <c r="B40" s="146" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C40" s="146" t="s">
         <v>64</v>
@@ -17065,7 +17068,7 @@
     </row>
     <row r="43">
       <c r="A43" s="146" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B43" s="146" t="s">
         <v>59</v>
@@ -17074,7 +17077,7 @@
         <v>99</v>
       </c>
       <c r="D43" s="146" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="44">
@@ -17088,12 +17091,12 @@
         <v>396</v>
       </c>
       <c r="D44" s="146" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="146" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B45" s="146" t="s">
         <v>59</v>
@@ -17102,7 +17105,7 @@
         <v>99</v>
       </c>
       <c r="D45" s="146" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="46">
@@ -17121,128 +17124,128 @@
     </row>
     <row r="47">
       <c r="A47" s="146" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B47" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C47" s="146" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D47" s="146" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="146" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B48" s="146" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="146" t="s">
+        <v>542</v>
+      </c>
+      <c r="D48" s="146" t="s">
         <v>1124</v>
-      </c>
-      <c r="B48" s="146" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="146" t="s">
-        <v>541</v>
-      </c>
-      <c r="D48" s="146" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="146" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B49" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="146" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D49" s="146" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="146" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B50" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C50" s="146" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D50" s="146" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="146" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B51" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="146" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D51" s="146" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="146" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B52" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C52" s="146" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D52" s="146" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="146" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B53" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="146" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D53" s="146" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="146" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B54" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C54" s="146" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D54" s="146" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="146" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B55" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C55" s="146" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D55" s="146" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="56">
@@ -17261,7 +17264,7 @@
     </row>
     <row r="57">
       <c r="A57" s="146" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B57" s="146" t="s">
         <v>5</v>
@@ -17270,12 +17273,12 @@
         <v>64</v>
       </c>
       <c r="D57" s="146" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="146" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B58" s="146" t="s">
         <v>59</v>
@@ -17284,12 +17287,12 @@
         <v>99</v>
       </c>
       <c r="D58" s="146" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="146" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B59" s="146" t="s">
         <v>5</v>
@@ -17298,7 +17301,7 @@
         <v>15</v>
       </c>
       <c r="D59" s="146" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="60">
@@ -17312,7 +17315,7 @@
         <v>64</v>
       </c>
       <c r="D60" s="146" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="61">
@@ -17326,7 +17329,7 @@
         <v>64</v>
       </c>
       <c r="D61" s="146" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="62">
@@ -17334,7 +17337,7 @@
         <v>114</v>
       </c>
       <c r="B62" s="146" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C62" s="146" t="s">
         <v>64</v>
@@ -17365,15 +17368,15 @@
         <v>5</v>
       </c>
       <c r="C64" s="146" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D64" s="146" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="146" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B65" s="146" t="s">
         <v>59</v>
@@ -17382,7 +17385,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="146" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="66">
@@ -17404,7 +17407,7 @@
         <v>412</v>
       </c>
       <c r="B67" s="146" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C67" s="146" t="s">
         <v>64</v>
@@ -17418,7 +17421,7 @@
         <v>414</v>
       </c>
       <c r="B68" s="146" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C68" s="146" t="s">
         <v>64</v>
@@ -17429,7 +17432,7 @@
     </row>
     <row r="69">
       <c r="A69" s="146" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B69" s="146" t="s">
         <v>5</v>
@@ -17438,12 +17441,12 @@
         <v>27</v>
       </c>
       <c r="D69" s="146" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="146" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B70" s="146" t="s">
         <v>5</v>
@@ -17452,7 +17455,7 @@
         <v>27</v>
       </c>
       <c r="D70" s="146" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="71">
@@ -17635,35 +17638,35 @@
     </row>
     <row r="3">
       <c r="A3" s="148" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="148" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D3" s="148" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="148" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B4" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="148" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D4" s="148" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="148" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B5" s="148" t="s">
         <v>5</v>
@@ -17672,7 +17675,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="6">
@@ -17683,10 +17686,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="148" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D6" s="148" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7">
@@ -17705,38 +17708,38 @@
     </row>
     <row r="8">
       <c r="A8" s="148" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B8" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="148" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="148" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="148" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D9" s="148" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="148" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B10" s="148" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C10" s="148" t="s">
         <v>64</v>
@@ -17747,10 +17750,10 @@
     </row>
     <row r="11">
       <c r="A11" s="148" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B11" s="148" t="s">
         <v>1162</v>
-      </c>
-      <c r="B11" s="148" t="s">
-        <v>1161</v>
       </c>
       <c r="C11" s="148" t="s">
         <v>64</v>
@@ -17761,7 +17764,7 @@
     </row>
     <row r="12">
       <c r="A12" s="148" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B12" s="148" t="s">
         <v>5</v>
@@ -17770,7 +17773,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="13">
@@ -17789,7 +17792,7 @@
     </row>
     <row r="14">
       <c r="A14" s="148" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B14" s="148" t="s">
         <v>5</v>
@@ -17798,7 +17801,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="148" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="15">
@@ -17817,16 +17820,16 @@
     </row>
     <row r="16">
       <c r="A16" s="148" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B16" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="148" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D16" s="148" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="17">
@@ -17887,7 +17890,7 @@
     </row>
     <row r="21">
       <c r="A21" s="148" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B21" s="148" t="s">
         <v>5</v>
@@ -17896,7 +17899,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="148" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="22">
@@ -17943,7 +17946,7 @@
     </row>
     <row r="25">
       <c r="A25" s="148" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B25" s="148" t="s">
         <v>59</v>
@@ -17952,7 +17955,7 @@
         <v>60</v>
       </c>
       <c r="D25" s="148" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="26">
@@ -17971,7 +17974,7 @@
     </row>
     <row r="27">
       <c r="A27" s="148" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B27" s="148" t="s">
         <v>59</v>
@@ -17980,7 +17983,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="148" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="28">
@@ -18030,7 +18033,7 @@
         <v>393</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C31" s="148" t="s">
         <v>64</v>
@@ -18041,7 +18044,7 @@
     </row>
     <row r="32">
       <c r="A32" s="148" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B32" s="148" t="s">
         <v>59</v>
@@ -18050,7 +18053,7 @@
         <v>99</v>
       </c>
       <c r="D32" s="148" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="33">
@@ -18069,7 +18072,7 @@
     </row>
     <row r="34">
       <c r="A34" s="148" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B34" s="148" t="s">
         <v>59</v>
@@ -18078,7 +18081,7 @@
         <v>99</v>
       </c>
       <c r="D34" s="148" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="35">
@@ -18097,128 +18100,128 @@
     </row>
     <row r="36">
       <c r="A36" s="148" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B36" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="148" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D36" s="148" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="148" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B37" s="148" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="148" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D37" s="148" t="s">
         <v>1124</v>
-      </c>
-      <c r="B37" s="148" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="148" t="s">
-        <v>1173</v>
-      </c>
-      <c r="D37" s="148" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="148" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B38" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="148" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D38" s="148" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="148" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B39" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="148" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D39" s="148" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="148" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B40" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="148" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D40" s="148" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="148" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B41" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="148" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D41" s="148" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="148" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B42" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="148" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D42" s="148" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="148" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B43" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="148" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D43" s="148" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="148" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B44" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="148" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D44" s="148" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="45">
@@ -18246,7 +18249,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="148" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="47">
@@ -18254,7 +18257,7 @@
         <v>412</v>
       </c>
       <c r="B47" s="148" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C47" s="148" t="s">
         <v>64</v>
@@ -18268,7 +18271,7 @@
         <v>414</v>
       </c>
       <c r="B48" s="148" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C48" s="148" t="s">
         <v>64</v>
@@ -18279,7 +18282,7 @@
     </row>
     <row r="49">
       <c r="A49" s="148" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B49" s="148" t="s">
         <v>5</v>
@@ -18288,7 +18291,7 @@
         <v>27</v>
       </c>
       <c r="D49" s="148" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="50">
@@ -18296,7 +18299,7 @@
         <v>449</v>
       </c>
       <c r="B50" s="148" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C50" s="148" t="s">
         <v>64</v>
@@ -18331,35 +18334,35 @@
     </row>
     <row r="2">
       <c r="A2" s="150" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B2" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="150" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D2" s="150" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="150" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B3" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="150" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D3" s="150" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="150" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B4" s="150" t="s">
         <v>5</v>
@@ -18368,35 +18371,35 @@
         <v>15</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="150" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B5" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="150" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D5" s="150" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="150" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B6" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="150" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D6" s="150" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
   </sheetData>
@@ -18425,7 +18428,7 @@
     </row>
     <row r="2">
       <c r="A2" s="152" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B2" s="152" t="s">
         <v>5</v>
@@ -18434,12 +18437,12 @@
         <v>72</v>
       </c>
       <c r="D2" s="152" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="152" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B3" s="152" t="s">
         <v>5</v>
@@ -18448,12 +18451,12 @@
         <v>75</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="152" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B4" s="152" t="s">
         <v>5</v>
@@ -18462,12 +18465,12 @@
         <v>66</v>
       </c>
       <c r="D4" s="152" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="152" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B5" s="152" t="s">
         <v>5</v>
@@ -18476,91 +18479,91 @@
         <v>69</v>
       </c>
       <c r="D5" s="152" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="152" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B6" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="152" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D6" s="152" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="152" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B7" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="152" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D7" s="152" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="152" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B8" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="152" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D8" s="152" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="152" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B9" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="152" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D9" s="152" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="152" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B10" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="152" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D10" s="152" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="152" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B11" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="152" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D11" s="152" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -18589,7 +18592,7 @@
     </row>
     <row r="2">
       <c r="A2" s="154" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B2" s="154" t="s">
         <v>5</v>
@@ -18598,12 +18601,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="154" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="154" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B3" s="154" t="s">
         <v>59</v>
@@ -18612,91 +18615,91 @@
         <v>60</v>
       </c>
       <c r="D3" s="154" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="154" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B4" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="154" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D4" s="154" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="154" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B5" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="154" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D5" s="154" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="154" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B6" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="154" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D6" s="154" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="154" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B7" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="154" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D7" s="154" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="154" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B8" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="154" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D8" s="154" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="154" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B9" s="154" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C9" s="154" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="154" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
   </sheetData>
@@ -18809,16 +18812,16 @@
     </row>
     <row r="8">
       <c r="A8" s="156" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B8" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="156" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D8" s="156" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="9">
@@ -18837,16 +18840,16 @@
     </row>
     <row r="10">
       <c r="A10" s="156" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B10" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="156" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D10" s="156" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
   </sheetData>
@@ -18875,7 +18878,7 @@
     </row>
     <row r="2">
       <c r="A2" s="158" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B2" s="158" t="s">
         <v>5</v>
@@ -18884,12 +18887,12 @@
         <v>27</v>
       </c>
       <c r="D2" s="158" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="158" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B3" s="158" t="s">
         <v>128</v>
@@ -18898,12 +18901,12 @@
         <v>64</v>
       </c>
       <c r="D3" s="158" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="158" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B4" s="158" t="s">
         <v>171</v>
@@ -19035,7 +19038,7 @@
     </row>
     <row r="2">
       <c r="A2" s="160" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B2" s="160" t="s">
         <v>5</v>
@@ -19044,12 +19047,12 @@
         <v>64</v>
       </c>
       <c r="D2" s="160" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="160" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B3" s="160" t="s">
         <v>59</v>
@@ -19058,12 +19061,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="160" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="160" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B4" s="160" t="s">
         <v>59</v>
@@ -19072,7 +19075,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="160" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="5">
@@ -19105,7 +19108,7 @@
     </row>
     <row r="7">
       <c r="A7" s="160" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B7" s="160" t="s">
         <v>59</v>
@@ -19114,12 +19117,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="160" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="160" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B8" s="160" t="s">
         <v>59</v>
@@ -19128,7 +19131,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="160" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="9">
@@ -19175,7 +19178,7 @@
     </row>
     <row r="12">
       <c r="A12" s="160" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B12" s="160" t="s">
         <v>59</v>
@@ -19184,7 +19187,7 @@
         <v>99</v>
       </c>
       <c r="D12" s="160" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="13">
@@ -19203,16 +19206,16 @@
     </row>
     <row r="14">
       <c r="A14" s="160" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B14" s="160" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="160" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D14" s="160" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="15">
@@ -19273,21 +19276,21 @@
     </row>
     <row r="19">
       <c r="A19" s="160" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B19" s="160" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="160" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D19" s="160" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="160" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B20" s="160" t="s">
         <v>5</v>
@@ -19296,7 +19299,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="160" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="21">
@@ -19329,7 +19332,7 @@
     </row>
     <row r="23">
       <c r="A23" s="160" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B23" s="160" t="s">
         <v>59</v>
@@ -19338,7 +19341,7 @@
         <v>99</v>
       </c>
       <c r="D23" s="160" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="24">
@@ -19349,15 +19352,15 @@
         <v>5</v>
       </c>
       <c r="C24" s="160" t="s">
-        <v>64</v>
+        <v>509</v>
       </c>
       <c r="D24" s="160" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="160" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B25" s="160" t="s">
         <v>5</v>
@@ -19366,12 +19369,12 @@
         <v>64</v>
       </c>
       <c r="D25" s="160" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="160" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B26" s="160" t="s">
         <v>59</v>
@@ -19380,7 +19383,7 @@
         <v>60</v>
       </c>
       <c r="D26" s="160" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
   </sheetData>
@@ -19409,7 +19412,7 @@
     </row>
     <row r="2">
       <c r="A2" s="162" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B2" s="162" t="s">
         <v>5</v>
@@ -19418,12 +19421,12 @@
         <v>64</v>
       </c>
       <c r="D2" s="162" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="162" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B3" s="162" t="s">
         <v>59</v>
@@ -19432,12 +19435,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="162" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="162" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B4" s="162" t="s">
         <v>59</v>
@@ -19446,7 +19449,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="162" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="5">
@@ -19479,7 +19482,7 @@
     </row>
     <row r="7">
       <c r="A7" s="162" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B7" s="162" t="s">
         <v>59</v>
@@ -19488,12 +19491,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="162" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="162" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B8" s="162" t="s">
         <v>59</v>
@@ -19502,7 +19505,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="162" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="9">
@@ -19563,7 +19566,7 @@
     </row>
     <row r="13">
       <c r="A13" s="162" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B13" s="162" t="s">
         <v>171</v>
@@ -19577,63 +19580,63 @@
     </row>
     <row r="14">
       <c r="A14" s="162" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B14" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="162" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D14" s="162" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="162" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B15" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="162" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D15" s="162" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="162" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B16" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="162" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D16" s="162" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="162" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B17" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="162" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D17" s="162" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="162" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B18" s="162" t="s">
         <v>5</v>
@@ -19642,12 +19645,12 @@
         <v>64</v>
       </c>
       <c r="D18" s="162" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="162" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B19" s="162" t="s">
         <v>171</v>
@@ -19661,63 +19664,63 @@
     </row>
     <row r="20">
       <c r="A20" s="162" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B20" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="162" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D20" s="162" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="162" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B21" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="162" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D21" s="162" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="162" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B22" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="162" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D22" s="162" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="162" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B23" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="162" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D23" s="162" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="162" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B24" s="162" t="s">
         <v>5</v>
@@ -19726,12 +19729,12 @@
         <v>359</v>
       </c>
       <c r="D24" s="162" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="162" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B25" s="162" t="s">
         <v>5</v>
@@ -19740,21 +19743,21 @@
         <v>15</v>
       </c>
       <c r="D25" s="162" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="162" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B26" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="162" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D26" s="162" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
   </sheetData>
@@ -19797,7 +19800,7 @@
     </row>
     <row r="3">
       <c r="A3" s="164" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B3" s="164" t="s">
         <v>5</v>
@@ -19806,7 +19809,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="164" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="4">
@@ -19825,7 +19828,7 @@
     </row>
     <row r="5">
       <c r="A5" s="164" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B5" s="164" t="s">
         <v>5</v>
@@ -19834,7 +19837,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="164" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="6">
@@ -19853,35 +19856,35 @@
     </row>
     <row r="7">
       <c r="A7" s="164" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B7" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="164" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D7" s="164" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="164" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B8" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="164" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D8" s="164" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="164" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B9" s="164" t="s">
         <v>59</v>
@@ -19890,26 +19893,26 @@
         <v>60</v>
       </c>
       <c r="D9" s="164" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="164" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B10" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="164" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D10" s="164" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="164" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B11" s="164" t="s">
         <v>5</v>
@@ -19918,12 +19921,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="164" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="164" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B12" s="164" t="s">
         <v>59</v>
@@ -19932,7 +19935,7 @@
         <v>99</v>
       </c>
       <c r="D12" s="164" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="13">
@@ -19951,7 +19954,7 @@
     </row>
     <row r="14">
       <c r="A14" s="164" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B14" s="164" t="s">
         <v>59</v>
@@ -19960,7 +19963,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="164" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="15">
@@ -19993,7 +19996,7 @@
     </row>
     <row r="17">
       <c r="A17" s="164" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B17" s="164" t="s">
         <v>59</v>
@@ -20002,12 +20005,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="164" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="164" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B18" s="164" t="s">
         <v>59</v>
@@ -20016,12 +20019,12 @@
         <v>60</v>
       </c>
       <c r="D18" s="164" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="164" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B19" s="164" t="s">
         <v>59</v>
@@ -20030,7 +20033,7 @@
         <v>60</v>
       </c>
       <c r="D19" s="164" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="20">
@@ -20063,21 +20066,21 @@
     </row>
     <row r="22">
       <c r="A22" s="164" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B22" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="164" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D22" s="164" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="164" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B23" s="164" t="s">
         <v>166</v>
@@ -20091,7 +20094,7 @@
     </row>
     <row r="24">
       <c r="A24" s="164" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B24" s="164" t="s">
         <v>59</v>
@@ -20100,7 +20103,7 @@
         <v>99</v>
       </c>
       <c r="D24" s="164" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="25">
@@ -20111,29 +20114,29 @@
         <v>5</v>
       </c>
       <c r="C25" s="164" t="s">
-        <v>64</v>
+        <v>509</v>
       </c>
       <c r="D25" s="164" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="164" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B26" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D26" s="164" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="164" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B27" s="164" t="s">
         <v>63</v>
@@ -20147,16 +20150,16 @@
     </row>
     <row r="28">
       <c r="A28" s="164" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B28" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="164" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D28" s="164" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="29">
@@ -20170,12 +20173,12 @@
         <v>503</v>
       </c>
       <c r="D29" s="164" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="164" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B30" s="164" t="s">
         <v>5</v>
@@ -20184,12 +20187,12 @@
         <v>15</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="164" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B31" s="164" t="s">
         <v>171</v>
@@ -20203,7 +20206,7 @@
     </row>
     <row r="32">
       <c r="A32" s="164" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B32" s="164" t="s">
         <v>59</v>
@@ -20212,12 +20215,12 @@
         <v>60</v>
       </c>
       <c r="D32" s="164" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="164" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B33" s="164" t="s">
         <v>166</v>
@@ -20255,7 +20258,7 @@
     </row>
     <row r="2">
       <c r="A2" s="166" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B2" s="166" t="s">
         <v>5</v>
@@ -20264,7 +20267,7 @@
         <v>64</v>
       </c>
       <c r="D2" s="166" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="3">
@@ -20297,7 +20300,7 @@
     </row>
     <row r="5">
       <c r="A5" s="166" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B5" s="166" t="s">
         <v>5</v>
@@ -20306,7 +20309,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="166" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="6">
@@ -20317,24 +20320,24 @@
         <v>5</v>
       </c>
       <c r="C6" s="166" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D6" s="166" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="166" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B7" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="166" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="D7" s="166" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="8">
@@ -20391,16 +20394,16 @@
     </row>
     <row r="3">
       <c r="A3" s="168" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B3" s="168" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="168" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D3" s="168" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
   </sheetData>
@@ -20443,21 +20446,21 @@
     </row>
     <row r="3">
       <c r="A3" s="170" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B3" s="170" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="D3" s="170" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="170" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B4" s="170" t="s">
         <v>5</v>
@@ -20466,7 +20469,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="170" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
   </sheetData>
@@ -20484,7 +20487,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="172" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -20509,16 +20512,16 @@
     </row>
     <row r="3">
       <c r="A3" s="172" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B3" s="172" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="172" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D3" s="172" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="4">
@@ -20529,10 +20532,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="172" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D4" s="172" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="5">
@@ -20543,10 +20546,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="172" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D5" s="172" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -20574,7 +20577,7 @@
         <v>64</v>
       </c>
       <c r="D7" s="172" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="8">
@@ -20588,12 +20591,12 @@
         <v>64</v>
       </c>
       <c r="D8" s="172" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="172" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B9" s="172" t="s">
         <v>224</v>
@@ -20616,7 +20619,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="172" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="11">
@@ -20750,7 +20753,7 @@
         <v>145</v>
       </c>
       <c r="B20" s="172" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C20" s="172" t="s">
         <v>64</v>
@@ -20764,7 +20767,7 @@
         <v>147</v>
       </c>
       <c r="B21" s="172" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C21" s="172" t="s">
         <v>64</v>
@@ -20778,7 +20781,7 @@
         <v>149</v>
       </c>
       <c r="B22" s="172" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C22" s="172" t="s">
         <v>64</v>
@@ -20792,7 +20795,7 @@
         <v>151</v>
       </c>
       <c r="B23" s="172" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C23" s="172" t="s">
         <v>64</v>
@@ -20806,7 +20809,7 @@
         <v>153</v>
       </c>
       <c r="B24" s="172" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C24" s="172" t="s">
         <v>64</v>
@@ -20820,7 +20823,7 @@
         <v>155</v>
       </c>
       <c r="B25" s="172" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C25" s="172" t="s">
         <v>64</v>
@@ -20834,7 +20837,7 @@
         <v>199</v>
       </c>
       <c r="B26" s="172" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C26" s="172" t="s">
         <v>64</v>
@@ -20848,7 +20851,7 @@
         <v>157</v>
       </c>
       <c r="B27" s="172" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C27" s="172" t="s">
         <v>64</v>
@@ -20862,7 +20865,7 @@
         <v>159</v>
       </c>
       <c r="B28" s="172" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C28" s="172" t="s">
         <v>64</v>
@@ -20876,7 +20879,7 @@
         <v>161</v>
       </c>
       <c r="B29" s="172" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C29" s="172" t="s">
         <v>64</v>
@@ -20890,7 +20893,7 @@
         <v>163</v>
       </c>
       <c r="B30" s="172" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C30" s="172" t="s">
         <v>64</v>
@@ -20904,7 +20907,7 @@
         <v>164</v>
       </c>
       <c r="B31" s="172" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C31" s="172" t="s">
         <v>64</v>
@@ -20960,7 +20963,7 @@
         <v>173</v>
       </c>
       <c r="B35" s="172" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C35" s="172" t="s">
         <v>64</v>
@@ -20974,7 +20977,7 @@
         <v>175</v>
       </c>
       <c r="B36" s="172" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C36" s="172" t="s">
         <v>64</v>
@@ -20988,7 +20991,7 @@
         <v>177</v>
       </c>
       <c r="B37" s="172" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C37" s="172" t="s">
         <v>64</v>
@@ -21002,7 +21005,7 @@
         <v>179</v>
       </c>
       <c r="B38" s="172" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C38" s="172" t="s">
         <v>64</v>
@@ -21016,7 +21019,7 @@
         <v>181</v>
       </c>
       <c r="B39" s="172" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C39" s="172" t="s">
         <v>64</v>
@@ -21030,7 +21033,7 @@
         <v>183</v>
       </c>
       <c r="B40" s="172" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C40" s="172" t="s">
         <v>64</v>
@@ -21044,7 +21047,7 @@
         <v>185</v>
       </c>
       <c r="B41" s="172" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C41" s="172" t="s">
         <v>64</v>
@@ -21058,7 +21061,7 @@
         <v>187</v>
       </c>
       <c r="B42" s="172" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C42" s="172" t="s">
         <v>64</v>
@@ -21072,7 +21075,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="172" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C43" s="172" t="s">
         <v>64</v>
@@ -21086,7 +21089,7 @@
         <v>191</v>
       </c>
       <c r="B44" s="172" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C44" s="172" t="s">
         <v>64</v>
@@ -21128,7 +21131,7 @@
         <v>215</v>
       </c>
       <c r="B47" s="172" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C47" s="172" t="s">
         <v>64</v>
@@ -21142,7 +21145,7 @@
         <v>203</v>
       </c>
       <c r="B48" s="172" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C48" s="172" t="s">
         <v>64</v>
@@ -21198,7 +21201,7 @@
         <v>233</v>
       </c>
       <c r="B52" s="172" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C52" s="172" t="s">
         <v>64</v>
@@ -21212,7 +21215,7 @@
         <v>196</v>
       </c>
       <c r="B53" s="172" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C53" s="172" t="s">
         <v>64</v>
@@ -21226,7 +21229,7 @@
         <v>231</v>
       </c>
       <c r="B54" s="172" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C54" s="172" t="s">
         <v>64</v>
@@ -21253,7 +21256,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="174" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -21278,7 +21281,7 @@
     </row>
     <row r="3">
       <c r="A3" s="174" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B3" s="174" t="s">
         <v>166</v>
@@ -21292,7 +21295,7 @@
     </row>
     <row r="4">
       <c r="A4" s="174" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B4" s="174" t="s">
         <v>166</v>
@@ -21306,7 +21309,7 @@
     </row>
     <row r="5">
       <c r="A5" s="174" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B5" s="174" t="s">
         <v>241</v>
@@ -21315,12 +21318,12 @@
         <v>15</v>
       </c>
       <c r="D5" s="174" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="174" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B6" s="174" t="s">
         <v>241</v>
@@ -21329,124 +21332,124 @@
         <v>15</v>
       </c>
       <c r="D6" s="174" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="174" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B7" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="174" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D7" s="174" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="174" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B8" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="174" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D8" s="174" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="174" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B9" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="174" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D9" s="174" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="174" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B10" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="174" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D10" s="174" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="174" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B11" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="174" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D11" s="174" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="174" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B12" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="174" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D12" s="174" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="174" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B13" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="174" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D13" s="174" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="174" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B14" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="174" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D14" s="174" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="174" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B15" s="174" t="s">
         <v>138</v>
@@ -21460,21 +21463,21 @@
     </row>
     <row r="16">
       <c r="A16" s="174" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B16" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="174" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D16" s="174" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="174" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B17" s="174" t="s">
         <v>59</v>
@@ -21483,12 +21486,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="174" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="174" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B18" s="174" t="s">
         <v>5</v>
@@ -21497,7 +21500,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="174" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
   </sheetData>
@@ -21518,7 +21521,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -21557,7 +21560,7 @@
     </row>
     <row r="4">
       <c r="A4" s="176" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B4" s="176" t="s">
         <v>166</v>
@@ -21580,7 +21583,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="176" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="6">
@@ -21599,30 +21602,30 @@
     </row>
     <row r="7">
       <c r="A7" s="176" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B7" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="176" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D7" s="176" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="176" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B8" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="176" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D8" s="176" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
   </sheetData>
@@ -21643,7 +21646,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="178" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -21682,7 +21685,7 @@
     </row>
     <row r="4">
       <c r="A4" s="178" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B4" s="178" t="s">
         <v>166</v>
@@ -21705,12 +21708,12 @@
         <v>15</v>
       </c>
       <c r="D5" s="178" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="178" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B6" s="178" t="s">
         <v>5</v>
@@ -21719,7 +21722,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="178" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
+++ b/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4496" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4540" uniqueCount="1417">
   <si>
     <t>Campo</t>
   </si>
@@ -1475,6 +1475,18 @@
     <t>soggettoImpedimentoGenerico</t>
   </si>
   <si>
+    <t>appartenenzaCognomeComune</t>
+  </si>
+  <si>
+    <t>scelta del cognome comune tra gli uniti civilmente (dec ANSC_175)</t>
+  </si>
+  <si>
+    <t>posizioneCognomeComune</t>
+  </si>
+  <si>
+    <t>modo di comporre il cognome comune  (dec ANSC_176)</t>
+  </si>
+  <si>
     <t>autorizzazione</t>
   </si>
   <si>
@@ -2087,6 +2099,12 @@
     <t>Età espessa in anni, numerico, per matrimonio da estero</t>
   </si>
   <si>
+    <t>dataValidita</t>
+  </si>
+  <si>
+    <t>Data Di Validità (Utilizzato solo nel caso d'uso 52821 Trascrizione atti multipli cittadinanza. Per i soggetti privi di Data Validità sarà utilizzata, ai fini dell’invio in anagrafica, la Data Validità dell’evento, ove presente.)</t>
+  </si>
+  <si>
     <t>tipologiaTrascrizione</t>
   </si>
   <si>
@@ -3248,6 +3266,12 @@
     <t>Indica se il documento sia stato o meno ricevuto a mezzo posta</t>
   </si>
   <si>
+    <t>estremiDichiarazioneConsolare</t>
+  </si>
+  <si>
+    <t>Estremi relativi alla dichiarazione consolare</t>
+  </si>
+  <si>
     <t>dataUltimoLuogo</t>
   </si>
   <si>
@@ -3293,6 +3317,12 @@
     <t>Data di decorrenza della sentenza</t>
   </si>
   <si>
+    <t>tipoProcedimento</t>
+  </si>
+  <si>
+    <t>Tipo procedimento (decodifica ANSC_174)</t>
+  </si>
+  <si>
     <t>tipoTrascrizione</t>
   </si>
   <si>
@@ -3755,7 +3785,7 @@
     <t>tipo</t>
   </si>
   <si>
-    <t>Tipo di regime patrimoniale (decodifica ANSC_49)</t>
+    <t>Tipo di regime patrimoniale (decodifica ANSC_49) (per caso d'uso 52821 deve usata la decodifica ANSC_181)</t>
   </si>
   <si>
     <t>attoNotarile</t>
@@ -3785,10 +3815,52 @@
     <t>Data dell'atto notarile di scelta del regime patrimoniale</t>
   </si>
   <si>
+    <t>Numero della legga cui gli sposi si avvalgono per definire il regime patrimoniale (per caso d'uso 52821 deve usata la decodifica ANSC_182)</t>
+  </si>
+  <si>
     <t>array[#/components/schemas/ModelAssistenzaMinori]</t>
   </si>
   <si>
     <t>lista contenente i dati degli assistenti dei minori (0=Sposo,1=Sposa) (Deprecato)</t>
+  </si>
+  <si>
+    <t>idTipoConvenzioneMatr</t>
+  </si>
+  <si>
+    <t>Tipo convenzione matrimoniale (decodifica ANSC_179)</t>
+  </si>
+  <si>
+    <t>tipoAttoNotarile</t>
+  </si>
+  <si>
+    <t>Tipo convenzione matrimoniale con Atto notarile (decodifica ANSC_180)</t>
+  </si>
+  <si>
+    <t>nazioneLegge</t>
+  </si>
+  <si>
+    <t>britannica</t>
+  </si>
+  <si>
+    <t>Nazionalità della legge che si vuole applicare (dove almeno uno dei coniugi è residente)</t>
+  </si>
+  <si>
+    <t>idTipoMutamentoConvenzioneMatr</t>
+  </si>
+  <si>
+    <t>Tipo mutazione convenzione matrimoniale (decodifica ANSC_183)</t>
+  </si>
+  <si>
+    <t>dataProvvedimento</t>
+  </si>
+  <si>
+    <t>Data provvedimento di omologazione/mutazione</t>
+  </si>
+  <si>
+    <t>omologazione</t>
+  </si>
+  <si>
+    <t>Nel caso di omologazione oppure mutamento tramite autorizzazione del giudice</t>
   </si>
   <si>
     <t>dataRiconciliazione</t>
@@ -8008,7 +8080,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -8345,6 +8417,34 @@
       </c>
       <c r="D24" s="36" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="36" t="s">
+        <v>457</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -8373,7 +8473,7 @@
     </row>
     <row r="2">
       <c r="A2" s="38" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>396</v>
@@ -8387,10 +8487,10 @@
     </row>
     <row r="3">
       <c r="A3" s="38" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>64</v>
@@ -8401,7 +8501,7 @@
     </row>
     <row r="4">
       <c r="A4" s="38" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>356</v>
@@ -8505,7 +8605,7 @@
     </row>
     <row r="2">
       <c r="A2" s="40" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>356</v>
@@ -8519,7 +8619,7 @@
     </row>
     <row r="3">
       <c r="A3" s="40" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B3" s="40" t="s">
         <v>396</v>
@@ -8533,7 +8633,7 @@
     </row>
     <row r="4">
       <c r="A4" s="40" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>396</v>
@@ -8571,7 +8671,7 @@
     </row>
     <row r="2">
       <c r="A2" s="42" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>5</v>
@@ -8580,12 +8680,12 @@
         <v>368</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="42" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>396</v>
@@ -8599,10 +8699,10 @@
     </row>
     <row r="4">
       <c r="A4" s="42" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C4" s="42" t="s">
         <v>64</v>
@@ -8616,7 +8716,7 @@
         <v>441</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>64</v>
@@ -8640,7 +8740,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -8651,10 +8751,10 @@
     </row>
     <row r="2">
       <c r="A2" s="43" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -8679,7 +8779,7 @@
     </row>
     <row r="4">
       <c r="A4" s="44" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B4" s="44" t="s">
         <v>5</v>
@@ -8688,12 +8788,12 @@
         <v>64</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="44" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B5" s="44" t="s">
         <v>396</v>
@@ -8707,7 +8807,7 @@
     </row>
     <row r="6">
       <c r="A6" s="44" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B6" s="44" t="s">
         <v>5</v>
@@ -8716,12 +8816,12 @@
         <v>368</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="44" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B7" s="44" t="s">
         <v>396</v>
@@ -8735,7 +8835,7 @@
     </row>
     <row r="8">
       <c r="A8" s="44" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B8" s="44" t="s">
         <v>356</v>
@@ -8749,7 +8849,7 @@
     </row>
     <row r="9">
       <c r="A9" s="44" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B9" s="44" t="s">
         <v>356</v>
@@ -8763,7 +8863,7 @@
     </row>
     <row r="10">
       <c r="A10" s="44" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>356</v>
@@ -8794,7 +8894,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -8805,10 +8905,10 @@
     </row>
     <row r="2">
       <c r="A2" s="45" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -8833,7 +8933,7 @@
     </row>
     <row r="4">
       <c r="A4" s="46" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B4" s="46" t="s">
         <v>5</v>
@@ -8842,12 +8942,12 @@
         <v>64</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="46" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B5" s="46" t="s">
         <v>396</v>
@@ -8861,7 +8961,7 @@
     </row>
     <row r="6">
       <c r="A6" s="46" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B6" s="46" t="s">
         <v>5</v>
@@ -8870,12 +8970,12 @@
         <v>64</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="46" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B7" s="46" t="s">
         <v>370</v>
@@ -8906,7 +9006,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="48" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -8917,10 +9017,10 @@
     </row>
     <row r="2">
       <c r="A2" s="47" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -8945,7 +9045,7 @@
     </row>
     <row r="4">
       <c r="A4" s="48" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B4" s="48" t="s">
         <v>361</v>
@@ -8959,7 +9059,7 @@
     </row>
     <row r="5">
       <c r="A5" s="48" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B5" s="48" t="s">
         <v>396</v>
@@ -8973,7 +9073,7 @@
     </row>
     <row r="6">
       <c r="A6" s="48" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B6" s="48" t="s">
         <v>356</v>
@@ -8987,7 +9087,7 @@
     </row>
     <row r="7">
       <c r="A7" s="48" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B7" s="48" t="s">
         <v>356</v>
@@ -9001,7 +9101,7 @@
     </row>
     <row r="8">
       <c r="A8" s="48" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B8" s="48" t="s">
         <v>356</v>
@@ -9015,7 +9115,7 @@
     </row>
     <row r="9">
       <c r="A9" s="48" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B9" s="48" t="s">
         <v>356</v>
@@ -9046,7 +9146,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -9057,10 +9157,10 @@
     </row>
     <row r="2">
       <c r="A2" s="49" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -9085,7 +9185,7 @@
     </row>
     <row r="4">
       <c r="A4" s="50" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B4" s="50" t="s">
         <v>370</v>
@@ -9116,7 +9216,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -9127,10 +9227,10 @@
     </row>
     <row r="2">
       <c r="A2" s="51" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -9155,7 +9255,7 @@
     </row>
     <row r="4">
       <c r="A4" s="52" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B4" s="52" t="s">
         <v>370</v>
@@ -9186,7 +9286,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -9197,10 +9297,10 @@
     </row>
     <row r="2">
       <c r="A2" s="53" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -9225,7 +9325,7 @@
     </row>
     <row r="4">
       <c r="A4" s="54" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B4" s="54" t="s">
         <v>356</v>
@@ -9239,7 +9339,7 @@
     </row>
     <row r="5">
       <c r="A5" s="54" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B5" s="54" t="s">
         <v>396</v>
@@ -9281,7 +9381,7 @@
     </row>
     <row r="2">
       <c r="A2" s="56" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B2" s="56" t="s">
         <v>356</v>
@@ -9295,7 +9395,7 @@
     </row>
     <row r="3">
       <c r="A3" s="56" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B3" s="56" t="s">
         <v>396</v>
@@ -9309,7 +9409,7 @@
     </row>
     <row r="4">
       <c r="A4" s="56" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B4" s="56" t="s">
         <v>361</v>
@@ -9323,7 +9423,7 @@
     </row>
     <row r="5">
       <c r="A5" s="56" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B5" s="56" t="s">
         <v>356</v>
@@ -9337,7 +9437,7 @@
     </row>
     <row r="6">
       <c r="A6" s="56" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B6" s="56" t="s">
         <v>356</v>
@@ -9351,7 +9451,7 @@
     </row>
     <row r="7">
       <c r="A7" s="56" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B7" s="56" t="s">
         <v>356</v>
@@ -9365,16 +9465,16 @@
     </row>
     <row r="8">
       <c r="A8" s="56" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B8" s="56" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -9403,7 +9503,7 @@
     </row>
     <row r="2">
       <c r="A2" s="58" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B2" s="58" t="s">
         <v>370</v>
@@ -9417,21 +9517,21 @@
     </row>
     <row r="3">
       <c r="A3" s="58" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B3" s="58" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="58" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>370</v>
@@ -9445,21 +9545,21 @@
     </row>
     <row r="5">
       <c r="A5" s="58" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B5" s="58" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="58" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B6" s="58" t="s">
         <v>356</v>
@@ -9473,7 +9573,7 @@
     </row>
     <row r="7">
       <c r="A7" s="58" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B7" s="58" t="s">
         <v>5</v>
@@ -9482,12 +9582,12 @@
         <v>64</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="58" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>356</v>
@@ -9501,7 +9601,7 @@
     </row>
     <row r="9">
       <c r="A9" s="58" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B9" s="58" t="s">
         <v>396</v>
@@ -9515,21 +9615,21 @@
     </row>
     <row r="10">
       <c r="A10" s="58" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B10" s="58" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="58" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B11" s="58" t="s">
         <v>361</v>
@@ -9543,21 +9643,21 @@
     </row>
     <row r="12">
       <c r="A12" s="58" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="58" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B13" s="58" t="s">
         <v>356</v>
@@ -9571,16 +9671,16 @@
     </row>
     <row r="14">
       <c r="A14" s="58" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B14" s="58" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -9703,7 +9803,7 @@
     </row>
     <row r="2">
       <c r="A2" s="60" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B2" s="60" t="s">
         <v>370</v>
@@ -9717,21 +9817,21 @@
     </row>
     <row r="3">
       <c r="A3" s="60" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B3" s="60" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="60" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D3" s="60" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="60" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B4" s="60" t="s">
         <v>370</v>
@@ -9745,21 +9845,21 @@
     </row>
     <row r="5">
       <c r="A5" s="60" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B5" s="60" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="60" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B6" s="60" t="s">
         <v>356</v>
@@ -9773,7 +9873,7 @@
     </row>
     <row r="7">
       <c r="A7" s="60" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B7" s="60" t="s">
         <v>356</v>
@@ -9787,7 +9887,7 @@
     </row>
     <row r="8">
       <c r="A8" s="60" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B8" s="60" t="s">
         <v>396</v>
@@ -9801,7 +9901,7 @@
     </row>
     <row r="9">
       <c r="A9" s="60" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B9" s="60" t="s">
         <v>5</v>
@@ -9815,7 +9915,7 @@
     </row>
     <row r="10">
       <c r="A10" s="60" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B10" s="60" t="s">
         <v>396</v>
@@ -9853,7 +9953,7 @@
     </row>
     <row r="2">
       <c r="A2" s="62" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B2" s="62" t="s">
         <v>356</v>
@@ -9895,35 +9995,35 @@
     </row>
     <row r="5">
       <c r="A5" s="62" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B5" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D5" s="62" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="62" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B6" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="62" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B7" s="62" t="s">
         <v>370</v>
@@ -9937,21 +10037,21 @@
     </row>
     <row r="8">
       <c r="A8" s="62" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B8" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="62" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B9" s="62" t="s">
         <v>370</v>
@@ -9965,21 +10065,21 @@
     </row>
     <row r="10">
       <c r="A10" s="62" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B10" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="62" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="62" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B11" s="62" t="s">
         <v>356</v>
@@ -9993,35 +10093,35 @@
     </row>
     <row r="12">
       <c r="A12" s="62" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B12" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D12" s="62" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="62" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B13" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="62" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="62" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B14" s="62" t="s">
         <v>396</v>
@@ -10035,7 +10135,7 @@
     </row>
     <row r="15">
       <c r="A15" s="62" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B15" s="62" t="s">
         <v>356</v>
@@ -10073,7 +10173,7 @@
     </row>
     <row r="2">
       <c r="A2" s="64" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B2" s="64" t="s">
         <v>356</v>
@@ -10087,7 +10187,7 @@
     </row>
     <row r="3">
       <c r="A3" s="64" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B3" s="64" t="s">
         <v>356</v>
@@ -10101,7 +10201,7 @@
     </row>
     <row r="4">
       <c r="A4" s="64" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B4" s="64" t="s">
         <v>370</v>
@@ -10153,7 +10253,7 @@
     </row>
     <row r="3">
       <c r="A3" s="66" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B3" s="66" t="s">
         <v>5</v>
@@ -10162,7 +10262,7 @@
         <v>64</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -10191,7 +10291,7 @@
     </row>
     <row r="2">
       <c r="A2" s="68" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B2" s="68" t="s">
         <v>5</v>
@@ -10200,12 +10300,12 @@
         <v>193</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="68" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B3" s="68" t="s">
         <v>5</v>
@@ -10214,26 +10314,26 @@
         <v>193</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="68" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B4" s="68" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="68" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B5" s="68" t="s">
         <v>5</v>
@@ -10242,7 +10342,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -10271,7 +10371,7 @@
     </row>
     <row r="2">
       <c r="A2" s="70" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B2" s="70" t="s">
         <v>5</v>
@@ -10285,7 +10385,7 @@
     </row>
     <row r="3">
       <c r="A3" s="70" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B3" s="70" t="s">
         <v>5</v>
@@ -10308,7 +10408,7 @@
         <v>342</v>
       </c>
       <c r="D4" s="70" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -10337,16 +10437,16 @@
     </row>
     <row r="2">
       <c r="A2" s="72" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B2" s="72" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D2" s="72" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -10375,24 +10475,24 @@
     </row>
     <row r="2">
       <c r="A2" s="74" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B2" s="74" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D2" s="74" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="74" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C3" s="74" t="s">
         <v>64</v>
@@ -10403,16 +10503,16 @@
     </row>
     <row r="4">
       <c r="A4" s="74" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B4" s="74" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D4" s="74" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -10441,7 +10541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="76" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B2" s="76" t="s">
         <v>396</v>
@@ -10455,7 +10555,7 @@
     </row>
     <row r="3">
       <c r="A3" s="76" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B3" s="76" t="s">
         <v>5</v>
@@ -10493,16 +10593,16 @@
     </row>
     <row r="2">
       <c r="A2" s="78" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B2" s="78" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D2" s="78" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -10583,7 +10683,7 @@
     </row>
     <row r="2">
       <c r="A2" s="80" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B2" s="80" t="s">
         <v>64</v>
@@ -10635,7 +10735,7 @@
     </row>
     <row r="2">
       <c r="A2" s="82" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B2" s="82" t="s">
         <v>354</v>
@@ -10649,7 +10749,7 @@
     </row>
     <row r="3">
       <c r="A3" s="82" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B3" s="82" t="s">
         <v>396</v>
@@ -10687,10 +10787,10 @@
     </row>
     <row r="2">
       <c r="A2" s="83" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="84" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -10724,7 +10824,7 @@
         <v>64</v>
       </c>
       <c r="D4" s="84" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -10842,7 +10942,7 @@
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10867,113 +10967,113 @@
         <v>5</v>
       </c>
       <c r="C2" s="90" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D2" s="90" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="90" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B3" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="90" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D3" s="90" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="90" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B4" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="90" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B5" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="90" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D5" s="90" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="90" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B6" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="90" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D6" s="90" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="90" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B7" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="90" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D7" s="90" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="90" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B8" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="90" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D8" s="90" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="90" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B9" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="90" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D9" s="90" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="90" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B10" s="90" t="s">
         <v>5</v>
@@ -10982,68 +11082,68 @@
         <v>15</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="90" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B11" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="90" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D11" s="90" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="90" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B12" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="90" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D12" s="90" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="90" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B13" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="90" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D13" s="90" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="90" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B14" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="90" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D14" s="90" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="90" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B15" s="90" t="s">
         <v>5</v>
@@ -11052,82 +11152,82 @@
         <v>72</v>
       </c>
       <c r="D15" s="90" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="90" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B16" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="90" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D16" s="90" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="90" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B17" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="90" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D17" s="90" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="90" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B18" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="90" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D18" s="90" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="90" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B19" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="90" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D19" s="90" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="90" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B20" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="90" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D20" s="90" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="90" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B21" s="90" t="s">
         <v>5</v>
@@ -11136,49 +11236,49 @@
         <v>72</v>
       </c>
       <c r="D21" s="90" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="90" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B22" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="90" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D22" s="90" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="90" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B23" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D23" s="90" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="90" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B24" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="90" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D24" s="90" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="25">
@@ -11192,12 +11292,12 @@
         <v>323</v>
       </c>
       <c r="D25" s="90" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="90" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B26" s="90" t="s">
         <v>5</v>
@@ -11206,26 +11306,26 @@
         <v>15</v>
       </c>
       <c r="D26" s="90" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="90" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B27" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="90" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D27" s="90" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="90" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B28" s="90" t="s">
         <v>5</v>
@@ -11234,12 +11334,12 @@
         <v>64</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="90" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B29" s="90" t="s">
         <v>5</v>
@@ -11248,21 +11348,21 @@
         <v>15</v>
       </c>
       <c r="D29" s="90" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="90" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B30" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="90" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D30" s="90" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="31">
@@ -11281,7 +11381,7 @@
     </row>
     <row r="32">
       <c r="A32" s="90" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B32" s="90" t="s">
         <v>59</v>
@@ -11290,12 +11390,12 @@
         <v>99</v>
       </c>
       <c r="D32" s="90" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="90" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B33" s="90" t="s">
         <v>59</v>
@@ -11304,12 +11404,12 @@
         <v>99</v>
       </c>
       <c r="D33" s="90" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="90" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B34" s="90" t="s">
         <v>59</v>
@@ -11318,40 +11418,40 @@
         <v>99</v>
       </c>
       <c r="D34" s="90" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="90" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B35" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="90" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D35" s="90" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="90" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B36" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="90" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D36" s="90" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="90" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B37" s="90" t="s">
         <v>5</v>
@@ -11360,29 +11460,29 @@
         <v>72</v>
       </c>
       <c r="D37" s="90" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="90" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B38" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="90" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D38" s="90" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="90" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B39" s="90" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C39" s="90" t="s">
         <v>64</v>
@@ -11393,10 +11493,10 @@
     </row>
     <row r="40">
       <c r="A40" s="90" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B40" s="90" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C40" s="90" t="s">
         <v>64</v>
@@ -11416,12 +11516,12 @@
         <v>308</v>
       </c>
       <c r="D41" s="90" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="90" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B42" s="90" t="s">
         <v>59</v>
@@ -11430,12 +11530,12 @@
         <v>99</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="90" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B43" s="90" t="s">
         <v>59</v>
@@ -11444,7 +11544,7 @@
         <v>99</v>
       </c>
       <c r="D43" s="90" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="44">
@@ -11463,7 +11563,7 @@
     </row>
     <row r="45">
       <c r="A45" s="90" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B45" s="90" t="s">
         <v>5</v>
@@ -11472,7 +11572,21 @@
         <v>83</v>
       </c>
       <c r="D45" s="90" t="s">
-        <v>660</v>
+        <v>664</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="90" t="s">
+        <v>665</v>
+      </c>
+      <c r="B46" s="90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="90" t="s">
+        <v>596</v>
+      </c>
+      <c r="D46" s="90" t="s">
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -11501,7 +11615,7 @@
     </row>
     <row r="2">
       <c r="A2" s="92" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B2" s="92" t="s">
         <v>5</v>
@@ -11510,12 +11624,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="92" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="92" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B3" s="92" t="s">
         <v>5</v>
@@ -11524,12 +11638,12 @@
         <v>193</v>
       </c>
       <c r="D3" s="92" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="92" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B4" s="92" t="s">
         <v>5</v>
@@ -11538,40 +11652,40 @@
         <v>193</v>
       </c>
       <c r="D4" s="92" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="92" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="B5" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="92" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D5" s="92" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="92" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B6" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D6" s="92" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="92" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="B7" s="92" t="s">
         <v>5</v>
@@ -11580,12 +11694,12 @@
         <v>72</v>
       </c>
       <c r="D7" s="92" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="92" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="B8" s="92" t="s">
         <v>5</v>
@@ -11594,96 +11708,96 @@
         <v>72</v>
       </c>
       <c r="D8" s="92" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="92" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="B9" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="92" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D9" s="92" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="92" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B10" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D10" s="92" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="92" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="B11" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="92" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D11" s="92" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="92" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B12" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="92" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D12" s="92" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="92" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B13" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="92" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D13" s="92" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="92" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B14" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="92" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="D14" s="92" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="92" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B15" s="92" t="s">
         <v>5</v>
@@ -11692,21 +11806,21 @@
         <v>3</v>
       </c>
       <c r="D15" s="92" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="92" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="B16" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="92" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -11735,10 +11849,10 @@
     </row>
     <row r="2">
       <c r="A2" s="93" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -11769,10 +11883,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -11811,15 +11925,15 @@
         <v>5</v>
       </c>
       <c r="C2" s="96" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="96" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B3" s="96" t="s">
         <v>5</v>
@@ -11828,40 +11942,40 @@
         <v>15</v>
       </c>
       <c r="D3" s="96" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="96" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B4" s="96" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="96" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="96" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B5" s="96" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="96" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="D5" s="96" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="96" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B6" s="96" t="s">
         <v>5</v>
@@ -11870,12 +11984,12 @@
         <v>378</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="96" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="B7" s="96" t="s">
         <v>5</v>
@@ -11884,12 +11998,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="96" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="96" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="B8" s="96" t="s">
         <v>5</v>
@@ -11898,7 +12012,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
     </row>
   </sheetData>
@@ -11916,7 +12030,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="98" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -11964,12 +12078,12 @@
         <v>323</v>
       </c>
       <c r="D4" s="98" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="98" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="B5" s="98" t="s">
         <v>5</v>
@@ -11978,26 +12092,26 @@
         <v>64</v>
       </c>
       <c r="D5" s="98" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="98" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="B6" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="98" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D6" s="98" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="98" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="B7" s="98" t="s">
         <v>5</v>
@@ -12006,7 +12120,7 @@
         <v>40</v>
       </c>
       <c r="D7" s="98" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8">
@@ -12025,7 +12139,7 @@
     </row>
     <row r="9">
       <c r="A9" s="98" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B9" s="98" t="s">
         <v>5</v>
@@ -12034,12 +12148,12 @@
         <v>102</v>
       </c>
       <c r="D9" s="98" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="98" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="B10" s="98" t="s">
         <v>5</v>
@@ -12048,26 +12162,26 @@
         <v>64</v>
       </c>
       <c r="D10" s="98" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="98" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="B11" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D11" s="98" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="98" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="B12" s="98" t="s">
         <v>5</v>
@@ -12076,12 +12190,12 @@
         <v>102</v>
       </c>
       <c r="D12" s="98" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="98" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="B13" s="98" t="s">
         <v>5</v>
@@ -12090,7 +12204,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="98" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
     </row>
     <row r="14">
@@ -12123,7 +12237,7 @@
     </row>
     <row r="16">
       <c r="A16" s="98" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="B16" s="98" t="s">
         <v>5</v>
@@ -12132,12 +12246,12 @@
         <v>15</v>
       </c>
       <c r="D16" s="98" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="98" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="B17" s="98" t="s">
         <v>5</v>
@@ -12146,40 +12260,40 @@
         <v>15</v>
       </c>
       <c r="D17" s="98" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="98" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="B18" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="98" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D18" s="98" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="98" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="B19" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="98" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D19" s="98" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="98" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="B20" s="98" t="s">
         <v>5</v>
@@ -12188,7 +12302,7 @@
         <v>40</v>
       </c>
       <c r="D20" s="98" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>
@@ -12625,7 +12739,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="100" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -12650,21 +12764,21 @@
     </row>
     <row r="3">
       <c r="A3" s="100" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="B3" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="100" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="D3" s="100" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="100" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="B4" s="100" t="s">
         <v>5</v>
@@ -12673,26 +12787,26 @@
         <v>15</v>
       </c>
       <c r="D4" s="100" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="100" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="B5" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="100" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="D5" s="100" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="100" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="B6" s="100" t="s">
         <v>5</v>
@@ -12701,21 +12815,21 @@
         <v>15</v>
       </c>
       <c r="D6" s="100" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="100" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="B7" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="100" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="D7" s="100" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -12747,58 +12861,58 @@
     </row>
     <row r="2">
       <c r="A2" s="102" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="B2" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="102" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="D2" s="102" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="102" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="B3" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="102" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="D3" s="102" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="102" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="B4" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="102" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="B5" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="102" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="D5" s="102" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="6">
@@ -12812,7 +12926,7 @@
         <v>333</v>
       </c>
       <c r="D6" s="102" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7">
@@ -12823,10 +12937,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="102" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="D7" s="102" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="8">
@@ -12837,24 +12951,24 @@
         <v>5</v>
       </c>
       <c r="C8" s="102" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="D8" s="102" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="102" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B9" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="102" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="D9" s="102" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
     </row>
     <row r="10">
@@ -12868,7 +12982,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="102" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
     </row>
   </sheetData>
@@ -12897,30 +13011,30 @@
     </row>
     <row r="2">
       <c r="A2" s="104" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="B2" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="104" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D2" s="104" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="104" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="B3" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="104" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D3" s="104" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
     </row>
     <row r="4">
@@ -12939,21 +13053,21 @@
     </row>
     <row r="5">
       <c r="A5" s="104" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="B5" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="104" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D5" s="104" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="104" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B6" s="104" t="s">
         <v>5</v>
@@ -12962,12 +13076,12 @@
         <v>64</v>
       </c>
       <c r="D6" s="104" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="104" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="B7" s="104" t="s">
         <v>5</v>
@@ -12976,7 +13090,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="104" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -13033,7 +13147,7 @@
     </row>
     <row r="3">
       <c r="A3" s="106" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="B3" s="106" t="s">
         <v>5</v>
@@ -13042,12 +13156,12 @@
         <v>66</v>
       </c>
       <c r="D3" s="106" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="106" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="B4" s="106" t="s">
         <v>5</v>
@@ -13056,12 +13170,12 @@
         <v>69</v>
       </c>
       <c r="D4" s="106" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="106" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="B5" s="106" t="s">
         <v>5</v>
@@ -13070,12 +13184,12 @@
         <v>72</v>
       </c>
       <c r="D5" s="106" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="106" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="B6" s="106" t="s">
         <v>5</v>
@@ -13084,35 +13198,35 @@
         <v>72</v>
       </c>
       <c r="D6" s="106" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="106" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="B7" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="106" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D7" s="106" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="106" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="B8" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="106" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="D8" s="106" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -13145,72 +13259,72 @@
     </row>
     <row r="11">
       <c r="A11" s="106" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="B11" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="106" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="D11" s="106" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="106" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B12" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="106" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="D12" s="106" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="106" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="B13" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="106" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="D13" s="106" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="106" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="B14" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="106" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="D14" s="106" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="106" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B15" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="106" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="D15" s="106" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
     </row>
     <row r="16">
@@ -13221,15 +13335,15 @@
         <v>5</v>
       </c>
       <c r="C16" s="106" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="D16" s="106" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="106" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="B17" s="106" t="s">
         <v>5</v>
@@ -13238,40 +13352,40 @@
         <v>35</v>
       </c>
       <c r="D17" s="106" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="106" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="B18" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="106" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="D18" s="106" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="106" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="B19" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D19" s="106" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="106" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B20" s="106" t="s">
         <v>5</v>
@@ -13280,21 +13394,21 @@
         <v>45</v>
       </c>
       <c r="D20" s="106" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="106" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="B21" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="106" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="D21" s="106" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
     </row>
     <row r="22">
@@ -13313,16 +13427,16 @@
     </row>
     <row r="23">
       <c r="A23" s="106" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B23" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="106" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="D23" s="106" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -13351,49 +13465,49 @@
     </row>
     <row r="2">
       <c r="A2" s="108" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="B2" s="108" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="108" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D2" s="108" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="108" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="B3" s="108" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="108" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D3" s="108" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="108" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="B4" s="108" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="108" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="108" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="B5" s="108" t="s">
         <v>5</v>
@@ -13402,7 +13516,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="108" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -13431,7 +13545,7 @@
     </row>
     <row r="2">
       <c r="A2" s="110" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="B2" s="110" t="s">
         <v>5</v>
@@ -13440,12 +13554,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="110" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="110" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="B3" s="110" t="s">
         <v>5</v>
@@ -13454,7 +13568,7 @@
         <v>137</v>
       </c>
       <c r="D3" s="110" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
     </row>
   </sheetData>
@@ -13492,21 +13606,21 @@
         <v>15</v>
       </c>
       <c r="D2" s="112" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="112" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="B3" s="112" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="112" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D3" s="112" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4">
@@ -13525,7 +13639,7 @@
     </row>
     <row r="5">
       <c r="A5" s="112" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B5" s="112" t="s">
         <v>166</v>
@@ -13539,7 +13653,7 @@
     </row>
     <row r="6">
       <c r="A6" s="112" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B6" s="112" t="s">
         <v>171</v>
@@ -13553,7 +13667,7 @@
     </row>
     <row r="7">
       <c r="A7" s="112" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B7" s="112" t="s">
         <v>171</v>
@@ -13605,7 +13719,7 @@
     </row>
     <row r="3">
       <c r="A3" s="114" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="B3" s="114" t="s">
         <v>5</v>
@@ -13614,12 +13728,12 @@
         <v>15</v>
       </c>
       <c r="D3" s="114" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="114" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="B4" s="114" t="s">
         <v>5</v>
@@ -13628,21 +13742,21 @@
         <v>15</v>
       </c>
       <c r="D4" s="114" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="114" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B5" s="114" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D5" s="114" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6">
@@ -13675,21 +13789,21 @@
     </row>
     <row r="8">
       <c r="A8" s="114" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="B8" s="114" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="114" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="D8" s="114" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="114" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="B9" s="114" t="s">
         <v>5</v>
@@ -13698,12 +13812,12 @@
         <v>78</v>
       </c>
       <c r="D9" s="114" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="114" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="B10" s="114" t="s">
         <v>59</v>
@@ -13712,12 +13826,12 @@
         <v>99</v>
       </c>
       <c r="D10" s="114" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="114" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="B11" s="114" t="s">
         <v>59</v>
@@ -13726,12 +13840,12 @@
         <v>99</v>
       </c>
       <c r="D11" s="114" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="114" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="B12" s="114" t="s">
         <v>59</v>
@@ -13740,12 +13854,12 @@
         <v>99</v>
       </c>
       <c r="D12" s="114" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="114" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="B13" s="114" t="s">
         <v>59</v>
@@ -13754,12 +13868,12 @@
         <v>99</v>
       </c>
       <c r="D13" s="114" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="114" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="B14" s="114" t="s">
         <v>59</v>
@@ -13768,12 +13882,12 @@
         <v>60</v>
       </c>
       <c r="D14" s="114" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="114" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="B15" s="114" t="s">
         <v>5</v>
@@ -13782,7 +13896,7 @@
         <v>378</v>
       </c>
       <c r="D15" s="114" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
     </row>
     <row r="16">
@@ -13839,30 +13953,30 @@
     </row>
     <row r="2">
       <c r="A2" s="116" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B2" s="116" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="116" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D2" s="116" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="116" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="B3" s="116" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="116" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D3" s="116" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
     </row>
   </sheetData>
@@ -13891,7 +14005,7 @@
     </row>
     <row r="2">
       <c r="A2" s="118" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="B2" s="118" t="s">
         <v>59</v>
@@ -13900,12 +14014,12 @@
         <v>99</v>
       </c>
       <c r="D2" s="118" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="118" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B3" s="118" t="s">
         <v>171</v>
@@ -13919,10 +14033,10 @@
     </row>
     <row r="4">
       <c r="A4" s="118" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="C4" s="118" t="s">
         <v>64</v>
@@ -13933,7 +14047,7 @@
     </row>
     <row r="5">
       <c r="A5" s="118" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B5" s="118" t="s">
         <v>166</v>
@@ -14012,7 +14126,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="120" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14037,30 +14151,30 @@
     </row>
     <row r="3">
       <c r="A3" s="120" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="B3" s="120" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="120" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="D3" s="120" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="120" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="B4" s="120" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="120" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="D4" s="120" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
   </sheetData>
@@ -14081,7 +14195,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14106,21 +14220,21 @@
     </row>
     <row r="3">
       <c r="A3" s="122" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B3" s="122" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="122" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="D3" s="122" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="122" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="B4" s="122" t="s">
         <v>5</v>
@@ -14129,7 +14243,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="122" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
     </row>
     <row r="5">
@@ -14154,10 +14268,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="122" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="D6" s="122" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -14178,7 +14292,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="124" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14203,7 +14317,7 @@
     </row>
     <row r="3">
       <c r="A3" s="124" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="B3" s="124" t="s">
         <v>5</v>
@@ -14212,26 +14326,26 @@
         <v>15</v>
       </c>
       <c r="D3" s="124" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="124" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="B4" s="124" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="124" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D4" s="124" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="124" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B5" s="124" t="s">
         <v>5</v>
@@ -14240,12 +14354,12 @@
         <v>368</v>
       </c>
       <c r="D5" s="124" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="124" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B6" s="124" t="s">
         <v>171</v>
@@ -14259,10 +14373,10 @@
     </row>
     <row r="7">
       <c r="A7" s="124" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B7" s="124" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C7" s="124" t="s">
         <v>64</v>
@@ -14276,7 +14390,7 @@
         <v>441</v>
       </c>
       <c r="B8" s="124" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C8" s="124" t="s">
         <v>64</v>
@@ -14287,7 +14401,7 @@
     </row>
     <row r="9">
       <c r="A9" s="124" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B9" s="124" t="s">
         <v>166</v>
@@ -14315,7 +14429,7 @@
     </row>
     <row r="11">
       <c r="A11" s="124" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B11" s="124" t="s">
         <v>166</v>
@@ -14383,7 +14497,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="128" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14394,10 +14508,10 @@
     </row>
     <row r="2">
       <c r="A2" s="127" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="128" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -14422,7 +14536,7 @@
     </row>
     <row r="4">
       <c r="A4" s="128" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="B4" s="128" t="s">
         <v>5</v>
@@ -14431,12 +14545,12 @@
         <v>15</v>
       </c>
       <c r="D4" s="128" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="128" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="B5" s="128" t="s">
         <v>5</v>
@@ -14445,26 +14559,26 @@
         <v>15</v>
       </c>
       <c r="D5" s="128" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="128" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B6" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="128" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="D6" s="128" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="128" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="B7" s="128" t="s">
         <v>5</v>
@@ -14473,12 +14587,12 @@
         <v>139</v>
       </c>
       <c r="D7" s="128" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="128" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="B8" s="128" t="s">
         <v>5</v>
@@ -14487,12 +14601,12 @@
         <v>64</v>
       </c>
       <c r="D8" s="128" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="128" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="B9" s="128" t="s">
         <v>59</v>
@@ -14501,26 +14615,26 @@
         <v>99</v>
       </c>
       <c r="D9" s="128" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="128" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="B10" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="128" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D10" s="128" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="128" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="B11" s="128" t="s">
         <v>5</v>
@@ -14529,12 +14643,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="128" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="128" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B12" s="128" t="s">
         <v>171</v>
@@ -14548,35 +14662,35 @@
     </row>
     <row r="13">
       <c r="A13" s="128" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="B13" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="128" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="D13" s="128" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="128" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="B14" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="128" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="D14" s="128" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="128" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="B15" s="128" t="s">
         <v>5</v>
@@ -14585,26 +14699,26 @@
         <v>15</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="128" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="B16" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="128" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D16" s="128" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="128" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="B17" s="128" t="s">
         <v>5</v>
@@ -14613,68 +14727,68 @@
         <v>15</v>
       </c>
       <c r="D17" s="128" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="128" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B18" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="128" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D18" s="128" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="128" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B19" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="128" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D19" s="128" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="128" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="B20" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="128" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="128" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="B21" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="128" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="D21" s="128" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="128" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B22" s="128" t="s">
         <v>5</v>
@@ -14683,12 +14797,12 @@
         <v>368</v>
       </c>
       <c r="D22" s="128" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="128" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B23" s="128" t="s">
         <v>171</v>
@@ -14702,7 +14816,7 @@
     </row>
     <row r="24">
       <c r="A24" s="128" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B24" s="128" t="s">
         <v>166</v>
@@ -14716,7 +14830,7 @@
     </row>
     <row r="25">
       <c r="A25" s="128" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="B25" s="128" t="s">
         <v>59</v>
@@ -14725,12 +14839,12 @@
         <v>60</v>
       </c>
       <c r="D25" s="128" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="128" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B26" s="128" t="s">
         <v>5</v>
@@ -14739,12 +14853,12 @@
         <v>27</v>
       </c>
       <c r="D26" s="128" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="128" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B27" s="128" t="s">
         <v>166</v>
@@ -14758,7 +14872,7 @@
     </row>
     <row r="28">
       <c r="A28" s="128" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B28" s="128" t="s">
         <v>166</v>
@@ -14775,13 +14889,13 @@
         <v>412</v>
       </c>
       <c r="B29" s="128" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C29" s="128" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="128" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -14814,10 +14928,10 @@
     </row>
     <row r="2">
       <c r="A2" s="129" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="130" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -14842,16 +14956,16 @@
     </row>
     <row r="4">
       <c r="A4" s="130" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B4" s="130" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="130" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D4" s="130" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
     </row>
     <row r="5">
@@ -14862,10 +14976,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="130" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="D5" s="130" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
     </row>
     <row r="6">
@@ -14876,10 +14990,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="130" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D6" s="130" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -14893,7 +15007,7 @@
         <v>66</v>
       </c>
       <c r="D7" s="130" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
     </row>
     <row r="8">
@@ -14904,7 +15018,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="130" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="D8" s="130" t="s">
         <v>264</v>
@@ -14921,7 +15035,7 @@
         <v>72</v>
       </c>
       <c r="D9" s="130" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
     </row>
     <row r="10">
@@ -14957,7 +15071,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="132" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14982,10 +15096,10 @@
     </row>
     <row r="3">
       <c r="A3" s="131" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B3" s="132" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C3" t="s">
         <v>64</v>
@@ -15010,7 +15124,7 @@
     </row>
     <row r="5">
       <c r="A5" s="132" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="B5" s="132" t="s">
         <v>5</v>
@@ -15019,21 +15133,21 @@
         <v>15</v>
       </c>
       <c r="D5" s="132" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="132" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="B6" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="132" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="D6" s="132" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -15067,7 +15181,7 @@
     </row>
     <row r="2">
       <c r="A2" s="134" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="B2" s="134" t="s">
         <v>59</v>
@@ -15076,7 +15190,7 @@
         <v>60</v>
       </c>
       <c r="D2" s="134" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
     </row>
     <row r="3">
@@ -15084,7 +15198,7 @@
         <v>362</v>
       </c>
       <c r="B3" s="134" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="C3" s="134" t="s">
         <v>64</v>
@@ -15104,7 +15218,7 @@
         <v>365</v>
       </c>
       <c r="D4" s="134" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
     </row>
     <row r="5">
@@ -15123,49 +15237,49 @@
     </row>
     <row r="6">
       <c r="A6" s="134" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="B6" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D6" s="134" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="134" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B7" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D7" s="134" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="134" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="B8" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="134" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="B9" s="134" t="s">
         <v>59</v>
@@ -15174,12 +15288,12 @@
         <v>60</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="134" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="B10" s="134" t="s">
         <v>5</v>
@@ -15188,7 +15302,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
     </row>
     <row r="11">
@@ -15207,7 +15321,7 @@
     </row>
     <row r="12">
       <c r="A12" s="134" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="B12" s="134" t="s">
         <v>5</v>
@@ -15216,7 +15330,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="134" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
     </row>
     <row r="13">
@@ -15235,7 +15349,7 @@
     </row>
     <row r="14">
       <c r="A14" s="134" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="B14" s="134" t="s">
         <v>5</v>
@@ -15244,12 +15358,12 @@
         <v>15</v>
       </c>
       <c r="D14" s="134" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="134" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="B15" s="134" t="s">
         <v>5</v>
@@ -15258,12 +15372,12 @@
         <v>15</v>
       </c>
       <c r="D15" s="134" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="134" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B16" s="134" t="s">
         <v>5</v>
@@ -15272,12 +15386,12 @@
         <v>72</v>
       </c>
       <c r="D16" s="134" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="134" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="B17" s="134" t="s">
         <v>5</v>
@@ -15286,54 +15400,54 @@
         <v>75</v>
       </c>
       <c r="D17" s="134" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="134" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B18" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="134" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="D18" s="134" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="134" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B19" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="134" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="134" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="B20" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="134" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D20" s="134" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="134" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="B21" s="134" t="s">
         <v>5</v>
@@ -15342,7 +15456,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="134" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
     </row>
     <row r="22">
@@ -15367,15 +15481,15 @@
         <v>5</v>
       </c>
       <c r="C23" s="134" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="D23" s="134" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="134" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="B24" s="134" t="s">
         <v>59</v>
@@ -15384,7 +15498,7 @@
         <v>60</v>
       </c>
       <c r="D24" s="134" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
     </row>
     <row r="25">
@@ -15403,105 +15517,105 @@
     </row>
     <row r="26">
       <c r="A26" s="134" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="B26" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="134" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="D26" s="134" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="134" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="B27" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="134" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D27" s="134" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="134" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="B28" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="134" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D28" s="134" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="134" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="B29" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="134" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D29" s="134" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="134" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="B30" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="134" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D30" s="134" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="134" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="B31" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="134" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="D31" s="134" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="134" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="B32" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="134" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D32" s="134" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="134" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B33" s="134" t="s">
         <v>59</v>
@@ -15510,7 +15624,7 @@
         <v>60</v>
       </c>
       <c r="D33" s="134" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="34">
@@ -15521,7 +15635,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="134" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="D34" s="134" t="s">
         <v>376</v>
@@ -15529,7 +15643,7 @@
     </row>
     <row r="35">
       <c r="A35" s="134" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="B35" s="134" t="s">
         <v>5</v>
@@ -15538,12 +15652,12 @@
         <v>15</v>
       </c>
       <c r="D35" s="134" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="134" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="B36" s="134" t="s">
         <v>5</v>
@@ -15552,26 +15666,26 @@
         <v>15</v>
       </c>
       <c r="D36" s="134" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="134" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="B37" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="134" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D37" s="134" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="134" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B38" s="134" t="s">
         <v>5</v>
@@ -15580,7 +15694,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="134" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="39">
@@ -15594,12 +15708,12 @@
         <v>15</v>
       </c>
       <c r="D39" s="134" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="134" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="B40" s="134" t="s">
         <v>5</v>
@@ -15608,40 +15722,40 @@
         <v>15</v>
       </c>
       <c r="D40" s="134" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="134" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="B41" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="134" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D41" s="134" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="134" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="B42" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="134" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D42" s="134" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="134" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="B43" s="134" t="s">
         <v>5</v>
@@ -15650,21 +15764,21 @@
         <v>15</v>
       </c>
       <c r="D43" s="134" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="134" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="B44" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="134" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D44" s="134" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
@@ -15674,7 +15788,7 @@
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -15682,7 +15796,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="136" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -15693,10 +15807,10 @@
     </row>
     <row r="2">
       <c r="A2" s="135" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="136" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -15721,35 +15835,35 @@
     </row>
     <row r="4">
       <c r="A4" s="136" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="B4" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="136" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="D4" s="136" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="136" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B5" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="136" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="D5" s="136" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="136" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="B6" s="136" t="s">
         <v>5</v>
@@ -15758,26 +15872,26 @@
         <v>64</v>
       </c>
       <c r="D6" s="136" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="136" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="136" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D7" s="136" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="136" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="B8" s="136" t="s">
         <v>5</v>
@@ -15786,82 +15900,82 @@
         <v>78</v>
       </c>
       <c r="D8" s="136" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="136" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="B9" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="136" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="D9" s="136" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="136" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="B10" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="136" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D10" s="136" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="136" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="B11" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="136" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="D11" s="136" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="136" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B12" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="136" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D12" s="136" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="136" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="B13" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="136" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D13" s="136" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="136" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B14" s="136" t="s">
         <v>171</v>
@@ -15875,7 +15989,7 @@
     </row>
     <row r="15">
       <c r="A15" s="136" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B15" s="136" t="s">
         <v>5</v>
@@ -15884,12 +15998,12 @@
         <v>15</v>
       </c>
       <c r="D15" s="136" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="136" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="B16" s="136" t="s">
         <v>59</v>
@@ -15898,12 +16012,12 @@
         <v>60</v>
       </c>
       <c r="D16" s="136" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="136" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="B17" s="136" t="s">
         <v>59</v>
@@ -15912,20 +16026,34 @@
         <v>60</v>
       </c>
       <c r="D17" s="136" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="136" t="s">
-        <v>484</v>
+        <v>1054</v>
       </c>
       <c r="B18" s="136" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="136" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="136" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="136" t="s">
+        <v>488</v>
+      </c>
+      <c r="B19" s="136" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="136" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="136" t="s">
+      <c r="C19" s="136" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="136" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15948,7 +16076,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="138" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -15959,10 +16087,10 @@
     </row>
     <row r="2">
       <c r="A2" s="137" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="138" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -15987,21 +16115,21 @@
     </row>
     <row r="4">
       <c r="A4" s="138" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="B4" s="138" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="138" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="B5" s="138" t="s">
         <v>5</v>
@@ -16010,12 +16138,12 @@
         <v>15</v>
       </c>
       <c r="D5" s="138" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="138" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B6" s="138" t="s">
         <v>63</v>
@@ -16029,7 +16157,7 @@
     </row>
     <row r="7">
       <c r="A7" s="138" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B7" s="138" t="s">
         <v>166</v>
@@ -16043,7 +16171,7 @@
     </row>
     <row r="8">
       <c r="A8" s="138" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B8" s="138" t="s">
         <v>166</v>
@@ -16057,7 +16185,7 @@
     </row>
     <row r="9">
       <c r="A9" s="138" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B9" s="138" t="s">
         <v>166</v>
@@ -16071,7 +16199,7 @@
     </row>
     <row r="10">
       <c r="A10" s="138" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B10" s="138" t="s">
         <v>166</v>
@@ -16182,7 +16310,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="140" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16193,10 +16321,10 @@
     </row>
     <row r="2">
       <c r="A2" s="139" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="140" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -16221,21 +16349,21 @@
     </row>
     <row r="4">
       <c r="A4" s="140" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="B4" s="140" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="140" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="D4" s="140" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="140" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B5" s="140" t="s">
         <v>138</v>
@@ -16258,7 +16386,7 @@
 
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16266,7 +16394,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="142" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16277,10 +16405,10 @@
     </row>
     <row r="2">
       <c r="A2" s="141" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -16305,7 +16433,7 @@
     </row>
     <row r="4">
       <c r="A4" s="142" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="B4" s="142" t="s">
         <v>59</v>
@@ -16314,12 +16442,12 @@
         <v>60</v>
       </c>
       <c r="D4" s="142" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="142" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B5" s="142" t="s">
         <v>166</v>
@@ -16333,7 +16461,7 @@
     </row>
     <row r="6">
       <c r="A6" s="142" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B6" s="142" t="s">
         <v>171</v>
@@ -16347,7 +16475,7 @@
     </row>
     <row r="7">
       <c r="A7" s="142" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="B7" s="142" t="s">
         <v>5</v>
@@ -16356,35 +16484,49 @@
         <v>15</v>
       </c>
       <c r="D7" s="142" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="142" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="B8" s="142" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="142" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D8" s="142" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="142" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="B9" s="142" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="142" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D9" s="142" t="s">
-        <v>1062</v>
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="142" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B10" s="142" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="142" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="142" t="s">
+        <v>1072</v>
       </c>
     </row>
   </sheetData>
@@ -16406,7 +16548,7 @@
         <v>382</v>
       </c>
       <c r="B1" s="144" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16417,10 +16559,10 @@
     </row>
     <row r="2">
       <c r="A2" s="143" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B2" s="144" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -16445,7 +16587,7 @@
     </row>
     <row r="4">
       <c r="A4" s="144" t="s">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="B4" s="144" t="s">
         <v>5</v>
@@ -16454,26 +16596,26 @@
         <v>64</v>
       </c>
       <c r="D4" s="144" t="s">
-        <v>1064</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="144" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="B5" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="144" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="144" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B6" s="144" t="s">
         <v>138</v>
@@ -16487,7 +16629,7 @@
     </row>
     <row r="7">
       <c r="A7" s="144" t="s">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="B7" s="144" t="s">
         <v>5</v>
@@ -16496,12 +16638,12 @@
         <v>15</v>
       </c>
       <c r="D7" s="144" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="144" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="B8" s="144" t="s">
         <v>59</v>
@@ -16510,35 +16652,35 @@
         <v>60</v>
       </c>
       <c r="D8" s="144" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="144" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="B9" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="144" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D9" s="144" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="144" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="B10" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="144" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D10" s="144" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
     </row>
   </sheetData>
@@ -16571,7 +16713,7 @@
     </row>
     <row r="2">
       <c r="A2" s="146" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="B2" s="146" t="s">
         <v>5</v>
@@ -16580,12 +16722,12 @@
         <v>66</v>
       </c>
       <c r="D2" s="146" t="s">
-        <v>1068</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="146" t="s">
-        <v>1069</v>
+        <v>1079</v>
       </c>
       <c r="B3" s="146" t="s">
         <v>5</v>
@@ -16594,12 +16736,12 @@
         <v>69</v>
       </c>
       <c r="D3" s="146" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="146" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="B4" s="146" t="s">
         <v>5</v>
@@ -16608,12 +16750,12 @@
         <v>72</v>
       </c>
       <c r="D4" s="146" t="s">
-        <v>1072</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="146" t="s">
-        <v>1073</v>
+        <v>1083</v>
       </c>
       <c r="B5" s="146" t="s">
         <v>5</v>
@@ -16622,40 +16764,40 @@
         <v>72</v>
       </c>
       <c r="D5" s="146" t="s">
-        <v>1074</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="146" t="s">
-        <v>1075</v>
+        <v>1085</v>
       </c>
       <c r="B6" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="146" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D6" s="146" t="s">
-        <v>1076</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="146" t="s">
-        <v>1077</v>
+        <v>1087</v>
       </c>
       <c r="B7" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="146" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D7" s="146" t="s">
-        <v>1078</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="146" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B8" s="146" t="s">
         <v>5</v>
@@ -16664,12 +16806,12 @@
         <v>333</v>
       </c>
       <c r="D8" s="146" t="s">
-        <v>1079</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="146" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B9" s="146" t="s">
         <v>5</v>
@@ -16678,21 +16820,21 @@
         <v>336</v>
       </c>
       <c r="D9" s="146" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="146" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="B10" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="146" t="s">
-        <v>1082</v>
+        <v>1092</v>
       </c>
       <c r="D10" s="146" t="s">
-        <v>1083</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="11">
@@ -16749,35 +16891,35 @@
     </row>
     <row r="3">
       <c r="A3" s="148" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="148" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D3" s="148" t="s">
-        <v>1085</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="148" t="s">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="B4" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="148" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D4" s="148" t="s">
-        <v>1087</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="148" t="s">
-        <v>1088</v>
+        <v>1098</v>
       </c>
       <c r="B5" s="148" t="s">
         <v>5</v>
@@ -16786,12 +16928,12 @@
         <v>40</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>1089</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="148" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B6" s="148" t="s">
         <v>5</v>
@@ -16800,35 +16942,35 @@
         <v>15</v>
       </c>
       <c r="D6" s="148" t="s">
-        <v>1090</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="148" t="s">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="B7" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="148" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D7" s="148" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="148" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="B8" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="148" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="9">
@@ -16861,7 +17003,7 @@
     </row>
     <row r="11">
       <c r="A11" s="148" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="B11" s="148" t="s">
         <v>5</v>
@@ -16870,12 +17012,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>1090</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="148" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="B12" s="148" t="s">
         <v>5</v>
@@ -16884,7 +17026,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>1097</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="13">
@@ -16903,7 +17045,7 @@
     </row>
     <row r="14">
       <c r="A14" s="148" t="s">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="B14" s="148" t="s">
         <v>5</v>
@@ -16912,7 +17054,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="148" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="15">
@@ -16926,21 +17068,21 @@
         <v>435</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>1100</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="148" t="s">
-        <v>1101</v>
+        <v>1111</v>
       </c>
       <c r="B16" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="148" t="s">
-        <v>1102</v>
+        <v>1112</v>
       </c>
       <c r="D16" s="148" t="s">
-        <v>1103</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="17">
@@ -17001,7 +17143,7 @@
     </row>
     <row r="21">
       <c r="A21" s="148" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="B21" s="148" t="s">
         <v>5</v>
@@ -17010,7 +17152,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="148" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="22">
@@ -17029,7 +17171,7 @@
     </row>
     <row r="23">
       <c r="A23" s="148" t="s">
-        <v>1106</v>
+        <v>1116</v>
       </c>
       <c r="B23" s="148" t="s">
         <v>59</v>
@@ -17038,15 +17180,15 @@
         <v>60</v>
       </c>
       <c r="D23" s="148" t="s">
-        <v>1107</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="148" t="s">
-        <v>1108</v>
+        <v>1118</v>
       </c>
       <c r="B24" s="148" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
       <c r="C24" s="148" t="s">
         <v>64</v>
@@ -17057,10 +17199,10 @@
     </row>
     <row r="25">
       <c r="A25" s="148" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="B25" s="148" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
       <c r="C25" s="148" t="s">
         <v>64</v>
@@ -17071,7 +17213,7 @@
     </row>
     <row r="26">
       <c r="A26" s="148" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="B26" s="148" t="s">
         <v>59</v>
@@ -17080,12 +17222,12 @@
         <v>60</v>
       </c>
       <c r="D26" s="148" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="148" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="B27" s="148" t="s">
         <v>59</v>
@@ -17094,7 +17236,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="148" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="28">
@@ -17113,7 +17255,7 @@
     </row>
     <row r="29">
       <c r="A29" s="148" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="B29" s="148" t="s">
         <v>59</v>
@@ -17122,12 +17264,12 @@
         <v>60</v>
       </c>
       <c r="D29" s="148" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="148" t="s">
-        <v>1117</v>
+        <v>1127</v>
       </c>
       <c r="B30" s="148" t="s">
         <v>59</v>
@@ -17136,7 +17278,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="148" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="31">
@@ -17155,7 +17297,7 @@
     </row>
     <row r="32">
       <c r="A32" s="148" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
       <c r="B32" s="148" t="s">
         <v>59</v>
@@ -17164,7 +17306,7 @@
         <v>60</v>
       </c>
       <c r="D32" s="148" t="s">
-        <v>1120</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="33">
@@ -17183,7 +17325,7 @@
     </row>
     <row r="34">
       <c r="A34" s="148" t="s">
-        <v>1121</v>
+        <v>1131</v>
       </c>
       <c r="B34" s="148" t="s">
         <v>5</v>
@@ -17192,12 +17334,12 @@
         <v>15</v>
       </c>
       <c r="D34" s="148" t="s">
-        <v>1122</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="148" t="s">
-        <v>1123</v>
+        <v>1133</v>
       </c>
       <c r="B35" s="148" t="s">
         <v>5</v>
@@ -17206,12 +17348,12 @@
         <v>27</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>1124</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="148" t="s">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="B36" s="148" t="s">
         <v>59</v>
@@ -17220,7 +17362,7 @@
         <v>99</v>
       </c>
       <c r="D36" s="148" t="s">
-        <v>1126</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="37">
@@ -17270,7 +17412,7 @@
         <v>402</v>
       </c>
       <c r="B40" s="148" t="s">
-        <v>1127</v>
+        <v>1137</v>
       </c>
       <c r="C40" s="148" t="s">
         <v>64</v>
@@ -17309,7 +17451,7 @@
     </row>
     <row r="43">
       <c r="A43" s="148" t="s">
-        <v>1128</v>
+        <v>1138</v>
       </c>
       <c r="B43" s="148" t="s">
         <v>59</v>
@@ -17318,7 +17460,7 @@
         <v>99</v>
       </c>
       <c r="D43" s="148" t="s">
-        <v>1129</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="44">
@@ -17332,12 +17474,12 @@
         <v>405</v>
       </c>
       <c r="D44" s="148" t="s">
-        <v>1130</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="148" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="B45" s="148" t="s">
         <v>59</v>
@@ -17346,7 +17488,7 @@
         <v>99</v>
       </c>
       <c r="D45" s="148" t="s">
-        <v>1132</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="46">
@@ -17365,128 +17507,128 @@
     </row>
     <row r="47">
       <c r="A47" s="148" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="B47" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C47" s="148" t="s">
-        <v>1134</v>
+        <v>1144</v>
       </c>
       <c r="D47" s="148" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="148" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="B48" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C48" s="148" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D48" s="148" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="148" t="s">
-        <v>1137</v>
+        <v>1147</v>
       </c>
       <c r="B49" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="148" t="s">
-        <v>1138</v>
+        <v>1148</v>
       </c>
       <c r="D49" s="148" t="s">
-        <v>1139</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="148" t="s">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="B50" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C50" s="148" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D50" s="148" t="s">
-        <v>1141</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="148" t="s">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="B51" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="148" t="s">
-        <v>1143</v>
+        <v>1153</v>
       </c>
       <c r="D51" s="148" t="s">
-        <v>1144</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="148" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
       <c r="B52" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C52" s="148" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D52" s="148" t="s">
-        <v>1146</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="148" t="s">
-        <v>1147</v>
+        <v>1157</v>
       </c>
       <c r="B53" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="148" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="D53" s="148" t="s">
-        <v>1148</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="148" t="s">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="B54" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C54" s="148" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="D54" s="148" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="148" t="s">
-        <v>1151</v>
+        <v>1161</v>
       </c>
       <c r="B55" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C55" s="148" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
       <c r="D55" s="148" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="56">
@@ -17505,7 +17647,7 @@
     </row>
     <row r="57">
       <c r="A57" s="148" t="s">
-        <v>1154</v>
+        <v>1164</v>
       </c>
       <c r="B57" s="148" t="s">
         <v>5</v>
@@ -17514,12 +17656,12 @@
         <v>64</v>
       </c>
       <c r="D57" s="148" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="148" t="s">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="B58" s="148" t="s">
         <v>59</v>
@@ -17528,12 +17670,12 @@
         <v>99</v>
       </c>
       <c r="D58" s="148" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="148" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="B59" s="148" t="s">
         <v>5</v>
@@ -17542,7 +17684,7 @@
         <v>15</v>
       </c>
       <c r="D59" s="148" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="60">
@@ -17556,7 +17698,7 @@
         <v>64</v>
       </c>
       <c r="D60" s="148" t="s">
-        <v>1160</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="61">
@@ -17570,7 +17712,7 @@
         <v>64</v>
       </c>
       <c r="D61" s="148" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="62">
@@ -17578,7 +17720,7 @@
         <v>114</v>
       </c>
       <c r="B62" s="148" t="s">
-        <v>1162</v>
+        <v>1172</v>
       </c>
       <c r="C62" s="148" t="s">
         <v>64</v>
@@ -17609,15 +17751,15 @@
         <v>5</v>
       </c>
       <c r="C64" s="148" t="s">
-        <v>1163</v>
+        <v>1173</v>
       </c>
       <c r="D64" s="148" t="s">
-        <v>1164</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="148" t="s">
-        <v>1165</v>
+        <v>1175</v>
       </c>
       <c r="B65" s="148" t="s">
         <v>59</v>
@@ -17626,7 +17768,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="148" t="s">
-        <v>1166</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="66">
@@ -17648,7 +17790,7 @@
         <v>419</v>
       </c>
       <c r="B67" s="148" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="C67" s="148" t="s">
         <v>64</v>
@@ -17662,7 +17804,7 @@
         <v>421</v>
       </c>
       <c r="B68" s="148" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="C68" s="148" t="s">
         <v>64</v>
@@ -17673,7 +17815,7 @@
     </row>
     <row r="69">
       <c r="A69" s="148" t="s">
-        <v>1168</v>
+        <v>1178</v>
       </c>
       <c r="B69" s="148" t="s">
         <v>5</v>
@@ -17682,12 +17824,12 @@
         <v>27</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>1169</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="148" t="s">
-        <v>1170</v>
+        <v>1180</v>
       </c>
       <c r="B70" s="148" t="s">
         <v>5</v>
@@ -17696,7 +17838,7 @@
         <v>27</v>
       </c>
       <c r="D70" s="148" t="s">
-        <v>1169</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="71">
@@ -17879,35 +18021,35 @@
     </row>
     <row r="3">
       <c r="A3" s="150" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="B3" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="150" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D3" s="150" t="s">
-        <v>1171</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="150" t="s">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="B4" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="150" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>1087</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="150" t="s">
-        <v>1088</v>
+        <v>1098</v>
       </c>
       <c r="B5" s="150" t="s">
         <v>5</v>
@@ -17916,21 +18058,21 @@
         <v>40</v>
       </c>
       <c r="D5" s="150" t="s">
-        <v>1089</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="150" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B6" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="150" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="D6" s="150" t="s">
-        <v>1090</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
@@ -17949,38 +18091,38 @@
     </row>
     <row r="8">
       <c r="A8" s="150" t="s">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="B8" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="150" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D8" s="150" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="150" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="B9" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="150" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D9" s="150" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="150" t="s">
-        <v>1172</v>
+        <v>1182</v>
       </c>
       <c r="B10" s="150" t="s">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="C10" s="150" t="s">
         <v>64</v>
@@ -17991,10 +18133,10 @@
     </row>
     <row r="11">
       <c r="A11" s="150" t="s">
-        <v>1174</v>
+        <v>1184</v>
       </c>
       <c r="B11" s="150" t="s">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="C11" s="150" t="s">
         <v>64</v>
@@ -18005,7 +18147,7 @@
     </row>
     <row r="12">
       <c r="A12" s="150" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="B12" s="150" t="s">
         <v>5</v>
@@ -18014,7 +18156,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="150" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="13">
@@ -18033,7 +18175,7 @@
     </row>
     <row r="14">
       <c r="A14" s="150" t="s">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="B14" s="150" t="s">
         <v>5</v>
@@ -18042,7 +18184,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="150" t="s">
-        <v>1178</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="15">
@@ -18061,16 +18203,16 @@
     </row>
     <row r="16">
       <c r="A16" s="150" t="s">
-        <v>1101</v>
+        <v>1111</v>
       </c>
       <c r="B16" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="150" t="s">
-        <v>1102</v>
+        <v>1112</v>
       </c>
       <c r="D16" s="150" t="s">
-        <v>1103</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="17">
@@ -18131,7 +18273,7 @@
     </row>
     <row r="21">
       <c r="A21" s="150" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="B21" s="150" t="s">
         <v>5</v>
@@ -18140,7 +18282,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="150" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="22">
@@ -18187,7 +18329,7 @@
     </row>
     <row r="25">
       <c r="A25" s="150" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="B25" s="150" t="s">
         <v>59</v>
@@ -18196,7 +18338,7 @@
         <v>60</v>
       </c>
       <c r="D25" s="150" t="s">
-        <v>1179</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="26">
@@ -18215,7 +18357,7 @@
     </row>
     <row r="27">
       <c r="A27" s="150" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
       <c r="B27" s="150" t="s">
         <v>59</v>
@@ -18224,7 +18366,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="150" t="s">
-        <v>1180</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="28">
@@ -18274,7 +18416,7 @@
         <v>402</v>
       </c>
       <c r="B31" s="150" t="s">
-        <v>1127</v>
+        <v>1137</v>
       </c>
       <c r="C31" s="150" t="s">
         <v>64</v>
@@ -18285,7 +18427,7 @@
     </row>
     <row r="32">
       <c r="A32" s="150" t="s">
-        <v>1181</v>
+        <v>1191</v>
       </c>
       <c r="B32" s="150" t="s">
         <v>59</v>
@@ -18294,7 +18436,7 @@
         <v>99</v>
       </c>
       <c r="D32" s="150" t="s">
-        <v>1182</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="33">
@@ -18313,7 +18455,7 @@
     </row>
     <row r="34">
       <c r="A34" s="150" t="s">
-        <v>1183</v>
+        <v>1193</v>
       </c>
       <c r="B34" s="150" t="s">
         <v>59</v>
@@ -18322,7 +18464,7 @@
         <v>99</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>1184</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="35">
@@ -18341,128 +18483,128 @@
     </row>
     <row r="36">
       <c r="A36" s="150" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="B36" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="150" t="s">
-        <v>1134</v>
+        <v>1144</v>
       </c>
       <c r="D36" s="150" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="150" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="B37" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="150" t="s">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="D37" s="150" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="150" t="s">
-        <v>1137</v>
+        <v>1147</v>
       </c>
       <c r="B38" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="150" t="s">
-        <v>1186</v>
+        <v>1196</v>
       </c>
       <c r="D38" s="150" t="s">
-        <v>1139</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="150" t="s">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="B39" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="150" t="s">
-        <v>1186</v>
+        <v>1196</v>
       </c>
       <c r="D39" s="150" t="s">
-        <v>1187</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="150" t="s">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="B40" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="150" t="s">
-        <v>1143</v>
+        <v>1153</v>
       </c>
       <c r="D40" s="150" t="s">
-        <v>1144</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="150" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
       <c r="B41" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="150" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D41" s="150" t="s">
-        <v>1146</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="150" t="s">
-        <v>1147</v>
+        <v>1157</v>
       </c>
       <c r="B42" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="150" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="D42" s="150" t="s">
-        <v>1148</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="150" t="s">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="B43" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="150" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="D43" s="150" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="150" t="s">
-        <v>1151</v>
+        <v>1161</v>
       </c>
       <c r="B44" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="150" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
       <c r="D44" s="150" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="45">
@@ -18490,7 +18632,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="150" t="s">
-        <v>1188</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="47">
@@ -18498,7 +18640,7 @@
         <v>419</v>
       </c>
       <c r="B47" s="150" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="C47" s="150" t="s">
         <v>64</v>
@@ -18512,7 +18654,7 @@
         <v>421</v>
       </c>
       <c r="B48" s="150" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="C48" s="150" t="s">
         <v>64</v>
@@ -18523,7 +18665,7 @@
     </row>
     <row r="49">
       <c r="A49" s="150" t="s">
-        <v>1189</v>
+        <v>1199</v>
       </c>
       <c r="B49" s="150" t="s">
         <v>5</v>
@@ -18532,7 +18674,7 @@
         <v>27</v>
       </c>
       <c r="D49" s="150" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="50">
@@ -18540,7 +18682,7 @@
         <v>456</v>
       </c>
       <c r="B50" s="150" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="C50" s="150" t="s">
         <v>64</v>
@@ -18575,35 +18717,35 @@
     </row>
     <row r="2">
       <c r="A2" s="152" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
       <c r="B2" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="152" t="s">
-        <v>1186</v>
+        <v>1196</v>
       </c>
       <c r="D2" s="152" t="s">
-        <v>1192</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="152" t="s">
-        <v>1193</v>
+        <v>1203</v>
       </c>
       <c r="B3" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="152" t="s">
-        <v>1194</v>
+        <v>1204</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>1195</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="152" t="s">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="B4" s="152" t="s">
         <v>5</v>
@@ -18612,35 +18754,35 @@
         <v>15</v>
       </c>
       <c r="D4" s="152" t="s">
-        <v>1197</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="152" t="s">
-        <v>1198</v>
+        <v>1208</v>
       </c>
       <c r="B5" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="152" t="s">
-        <v>1199</v>
+        <v>1209</v>
       </c>
       <c r="D5" s="152" t="s">
-        <v>1200</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="152" t="s">
-        <v>1201</v>
+        <v>1211</v>
       </c>
       <c r="B6" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="152" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="D6" s="152" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
     </row>
   </sheetData>
@@ -18669,7 +18811,7 @@
     </row>
     <row r="2">
       <c r="A2" s="154" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="B2" s="154" t="s">
         <v>5</v>
@@ -18678,12 +18820,12 @@
         <v>72</v>
       </c>
       <c r="D2" s="154" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="154" t="s">
-        <v>1205</v>
+        <v>1215</v>
       </c>
       <c r="B3" s="154" t="s">
         <v>5</v>
@@ -18692,12 +18834,12 @@
         <v>75</v>
       </c>
       <c r="D3" s="154" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="154" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="B4" s="154" t="s">
         <v>5</v>
@@ -18706,12 +18848,12 @@
         <v>66</v>
       </c>
       <c r="D4" s="154" t="s">
-        <v>1206</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="154" t="s">
-        <v>1207</v>
+        <v>1217</v>
       </c>
       <c r="B5" s="154" t="s">
         <v>5</v>
@@ -18720,91 +18862,91 @@
         <v>69</v>
       </c>
       <c r="D5" s="154" t="s">
-        <v>1206</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="154" t="s">
-        <v>1208</v>
+        <v>1218</v>
       </c>
       <c r="B6" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="154" t="s">
-        <v>1209</v>
+        <v>1219</v>
       </c>
       <c r="D6" s="154" t="s">
-        <v>1210</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="154" t="s">
-        <v>1211</v>
+        <v>1221</v>
       </c>
       <c r="B7" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="154" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
       <c r="D7" s="154" t="s">
-        <v>1213</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="154" t="s">
-        <v>1214</v>
+        <v>1224</v>
       </c>
       <c r="B8" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="154" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D8" s="154" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="154" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="B9" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="154" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D9" s="154" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="154" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="B10" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="154" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D10" s="154" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="154" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B11" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="154" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D11" s="154" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -18814,7 +18956,7 @@
 
 <file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -18833,7 +18975,7 @@
     </row>
     <row r="2">
       <c r="A2" s="156" t="s">
-        <v>1216</v>
+        <v>1226</v>
       </c>
       <c r="B2" s="156" t="s">
         <v>5</v>
@@ -18842,12 +18984,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="156" t="s">
-        <v>1217</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="156" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
       <c r="B3" s="156" t="s">
         <v>59</v>
@@ -18856,91 +18998,175 @@
         <v>60</v>
       </c>
       <c r="D3" s="156" t="s">
-        <v>1219</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="156" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="B4" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D4" s="156" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="156" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="B5" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="156" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D5" s="156" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="156" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B6" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="156" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D6" s="156" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="156" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
       <c r="B7" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="156" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="D7" s="156" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="156" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B8" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="156" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D8" s="156" t="s">
-        <v>555</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="156" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B9" s="156" t="s">
-        <v>1227</v>
+        <v>1238</v>
       </c>
       <c r="C9" s="156" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="156" t="s">
-        <v>1228</v>
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="156" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B10" s="156" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="156" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="156" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="156" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B11" s="156" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="156" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="156" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="156" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B12" s="156" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="156" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D12" s="156" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="156" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B13" s="156" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="156" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="156" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="156" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B14" s="156" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="156" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D14" s="156" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="156" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B15" s="156" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="156" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="156" t="s">
+        <v>1252</v>
       </c>
     </row>
   </sheetData>
@@ -18969,7 +19195,7 @@
     </row>
     <row r="2">
       <c r="A2" s="158" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B2" s="158" t="s">
         <v>63</v>
@@ -18983,7 +19209,7 @@
     </row>
     <row r="3">
       <c r="A3" s="158" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B3" s="158" t="s">
         <v>166</v>
@@ -18997,7 +19223,7 @@
     </row>
     <row r="4">
       <c r="A4" s="158" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B4" s="158" t="s">
         <v>171</v>
@@ -19011,7 +19237,7 @@
     </row>
     <row r="5">
       <c r="A5" s="158" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B5" s="158" t="s">
         <v>166</v>
@@ -19025,7 +19251,7 @@
     </row>
     <row r="6">
       <c r="A6" s="158" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B6" s="158" t="s">
         <v>166</v>
@@ -19039,7 +19265,7 @@
     </row>
     <row r="7">
       <c r="A7" s="158" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B7" s="158" t="s">
         <v>166</v>
@@ -19053,44 +19279,44 @@
     </row>
     <row r="8">
       <c r="A8" s="158" t="s">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="B8" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="158" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
       <c r="D8" s="158" t="s">
-        <v>1230</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="158" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B9" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="158" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D9" s="158" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="158" t="s">
-        <v>1231</v>
+        <v>1255</v>
       </c>
       <c r="B10" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="158" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
       <c r="D10" s="158" t="s">
-        <v>1232</v>
+        <v>1256</v>
       </c>
     </row>
   </sheetData>
@@ -19171,7 +19397,7 @@
     </row>
     <row r="2">
       <c r="A2" s="160" t="s">
-        <v>1233</v>
+        <v>1257</v>
       </c>
       <c r="B2" s="160" t="s">
         <v>5</v>
@@ -19180,12 +19406,12 @@
         <v>27</v>
       </c>
       <c r="D2" s="160" t="s">
-        <v>1169</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="160" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B3" s="160" t="s">
         <v>128</v>
@@ -19194,12 +19420,12 @@
         <v>64</v>
       </c>
       <c r="D3" s="160" t="s">
-        <v>1234</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="160" t="s">
-        <v>1235</v>
+        <v>1259</v>
       </c>
       <c r="B4" s="160" t="s">
         <v>171</v>
@@ -19237,7 +19463,7 @@
     </row>
     <row r="2">
       <c r="A2" s="162" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="B2" s="162" t="s">
         <v>5</v>
@@ -19246,12 +19472,12 @@
         <v>64</v>
       </c>
       <c r="D2" s="162" t="s">
-        <v>1237</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="162" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="B3" s="162" t="s">
         <v>59</v>
@@ -19260,12 +19486,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="162" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="162" t="s">
-        <v>1240</v>
+        <v>1264</v>
       </c>
       <c r="B4" s="162" t="s">
         <v>59</v>
@@ -19274,12 +19500,12 @@
         <v>60</v>
       </c>
       <c r="D4" s="162" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="162" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B5" s="162" t="s">
         <v>138</v>
@@ -19293,21 +19519,21 @@
     </row>
     <row r="6">
       <c r="A6" s="162" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B6" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="162" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D6" s="162" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="162" t="s">
-        <v>1242</v>
+        <v>1266</v>
       </c>
       <c r="B7" s="162" t="s">
         <v>59</v>
@@ -19316,12 +19542,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="162" t="s">
-        <v>1243</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="162" t="s">
-        <v>1244</v>
+        <v>1268</v>
       </c>
       <c r="B8" s="162" t="s">
         <v>59</v>
@@ -19330,12 +19556,12 @@
         <v>60</v>
       </c>
       <c r="D8" s="162" t="s">
-        <v>1245</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="162" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B9" s="162" t="s">
         <v>138</v>
@@ -19349,21 +19575,21 @@
     </row>
     <row r="10">
       <c r="A10" s="162" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B10" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="162" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D10" s="162" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="162" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B11" s="162" t="s">
         <v>166</v>
@@ -19377,7 +19603,7 @@
     </row>
     <row r="12">
       <c r="A12" s="162" t="s">
-        <v>1246</v>
+        <v>1270</v>
       </c>
       <c r="B12" s="162" t="s">
         <v>59</v>
@@ -19386,12 +19612,12 @@
         <v>99</v>
       </c>
       <c r="D12" s="162" t="s">
-        <v>1247</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="162" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B13" s="162" t="s">
         <v>5</v>
@@ -19400,26 +19626,26 @@
         <v>64</v>
       </c>
       <c r="D13" s="162" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="162" t="s">
-        <v>1248</v>
+        <v>1272</v>
       </c>
       <c r="B14" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="162" t="s">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="D14" s="162" t="s">
-        <v>1250</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="162" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B15" s="162" t="s">
         <v>166</v>
@@ -19433,7 +19659,7 @@
     </row>
     <row r="16">
       <c r="A16" s="162" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B16" s="162" t="s">
         <v>166</v>
@@ -19447,7 +19673,7 @@
     </row>
     <row r="17">
       <c r="A17" s="162" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B17" s="162" t="s">
         <v>171</v>
@@ -19461,35 +19687,35 @@
     </row>
     <row r="18">
       <c r="A18" s="162" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B18" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="162" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D18" s="162" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="162" t="s">
-        <v>1231</v>
+        <v>1255</v>
       </c>
       <c r="B19" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="162" t="s">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="D19" s="162" t="s">
-        <v>1251</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="162" t="s">
-        <v>1252</v>
+        <v>1276</v>
       </c>
       <c r="B20" s="162" t="s">
         <v>5</v>
@@ -19498,12 +19724,12 @@
         <v>15</v>
       </c>
       <c r="D20" s="162" t="s">
-        <v>1253</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="162" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B21" s="162" t="s">
         <v>63</v>
@@ -19517,21 +19743,21 @@
     </row>
     <row r="22">
       <c r="A22" s="162" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B22" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="162" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D22" s="162" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="162" t="s">
-        <v>1254</v>
+        <v>1278</v>
       </c>
       <c r="B23" s="162" t="s">
         <v>59</v>
@@ -19540,26 +19766,26 @@
         <v>99</v>
       </c>
       <c r="D23" s="162" t="s">
-        <v>1255</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="162" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B24" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="162" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D24" s="162" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="162" t="s">
-        <v>1256</v>
+        <v>1280</v>
       </c>
       <c r="B25" s="162" t="s">
         <v>5</v>
@@ -19568,12 +19794,12 @@
         <v>64</v>
       </c>
       <c r="D25" s="162" t="s">
-        <v>1257</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="162" t="s">
-        <v>1258</v>
+        <v>1282</v>
       </c>
       <c r="B26" s="162" t="s">
         <v>59</v>
@@ -19582,7 +19808,7 @@
         <v>60</v>
       </c>
       <c r="D26" s="162" t="s">
-        <v>1259</v>
+        <v>1283</v>
       </c>
     </row>
   </sheetData>
@@ -19611,7 +19837,7 @@
     </row>
     <row r="2">
       <c r="A2" s="164" t="s">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="B2" s="164" t="s">
         <v>5</v>
@@ -19620,12 +19846,12 @@
         <v>64</v>
       </c>
       <c r="D2" s="164" t="s">
-        <v>1260</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="164" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="B3" s="164" t="s">
         <v>59</v>
@@ -19634,12 +19860,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="164" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="164" t="s">
-        <v>1240</v>
+        <v>1264</v>
       </c>
       <c r="B4" s="164" t="s">
         <v>59</v>
@@ -19648,12 +19874,12 @@
         <v>60</v>
       </c>
       <c r="D4" s="164" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="164" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B5" s="164" t="s">
         <v>138</v>
@@ -19667,21 +19893,21 @@
     </row>
     <row r="6">
       <c r="A6" s="164" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B6" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="164" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D6" s="164" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="164" t="s">
-        <v>1242</v>
+        <v>1266</v>
       </c>
       <c r="B7" s="164" t="s">
         <v>59</v>
@@ -19690,12 +19916,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="164" t="s">
-        <v>1243</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="164" t="s">
-        <v>1244</v>
+        <v>1268</v>
       </c>
       <c r="B8" s="164" t="s">
         <v>59</v>
@@ -19704,12 +19930,12 @@
         <v>60</v>
       </c>
       <c r="D8" s="164" t="s">
-        <v>1245</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="164" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B9" s="164" t="s">
         <v>138</v>
@@ -19723,21 +19949,21 @@
     </row>
     <row r="10">
       <c r="A10" s="164" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B10" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="164" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D10" s="164" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="164" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B11" s="164" t="s">
         <v>166</v>
@@ -19751,7 +19977,7 @@
     </row>
     <row r="12">
       <c r="A12" s="164" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B12" s="164" t="s">
         <v>166</v>
@@ -19765,7 +19991,7 @@
     </row>
     <row r="13">
       <c r="A13" s="164" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B13" s="164" t="s">
         <v>171</v>
@@ -19779,63 +20005,63 @@
     </row>
     <row r="14">
       <c r="A14" s="164" t="s">
-        <v>1261</v>
+        <v>1285</v>
       </c>
       <c r="B14" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="164" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="D14" s="164" t="s">
-        <v>1263</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="164" t="s">
-        <v>1264</v>
+        <v>1288</v>
       </c>
       <c r="B15" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="164" t="s">
-        <v>1265</v>
+        <v>1289</v>
       </c>
       <c r="D15" s="164" t="s">
-        <v>1266</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="164" t="s">
-        <v>1267</v>
+        <v>1291</v>
       </c>
       <c r="B16" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="164" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="D16" s="164" t="s">
-        <v>1268</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="164" t="s">
-        <v>1269</v>
+        <v>1293</v>
       </c>
       <c r="B17" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="164" t="s">
-        <v>1265</v>
+        <v>1289</v>
       </c>
       <c r="D17" s="164" t="s">
-        <v>1270</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="164" t="s">
-        <v>1271</v>
+        <v>1295</v>
       </c>
       <c r="B18" s="164" t="s">
         <v>5</v>
@@ -19844,12 +20070,12 @@
         <v>64</v>
       </c>
       <c r="D18" s="164" t="s">
-        <v>1272</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="164" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B19" s="164" t="s">
         <v>171</v>
@@ -19863,63 +20089,63 @@
     </row>
     <row r="20">
       <c r="A20" s="164" t="s">
-        <v>1273</v>
+        <v>1297</v>
       </c>
       <c r="B20" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="164" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="D20" s="164" t="s">
-        <v>1274</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="164" t="s">
-        <v>1275</v>
+        <v>1299</v>
       </c>
       <c r="B21" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="164" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>1276</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="164" t="s">
-        <v>1277</v>
+        <v>1301</v>
       </c>
       <c r="B22" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="164" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="D22" s="164" t="s">
-        <v>1278</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="164" t="s">
-        <v>1279</v>
+        <v>1303</v>
       </c>
       <c r="B23" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="164" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="D23" s="164" t="s">
-        <v>1280</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="164" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B24" s="164" t="s">
         <v>5</v>
@@ -19928,12 +20154,12 @@
         <v>368</v>
       </c>
       <c r="D24" s="164" t="s">
-        <v>1281</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="164" t="s">
-        <v>1282</v>
+        <v>1306</v>
       </c>
       <c r="B25" s="164" t="s">
         <v>5</v>
@@ -19942,21 +20168,21 @@
         <v>15</v>
       </c>
       <c r="D25" s="164" t="s">
-        <v>1283</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="164" t="s">
-        <v>1284</v>
+        <v>1308</v>
       </c>
       <c r="B26" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="D26" s="164" t="s">
-        <v>1285</v>
+        <v>1309</v>
       </c>
     </row>
   </sheetData>
@@ -19985,7 +20211,7 @@
     </row>
     <row r="2">
       <c r="A2" s="166" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B2" s="166" t="s">
         <v>166</v>
@@ -19999,7 +20225,7 @@
     </row>
     <row r="3">
       <c r="A3" s="166" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="B3" s="166" t="s">
         <v>5</v>
@@ -20008,7 +20234,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="166" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="4">
@@ -20027,7 +20253,7 @@
     </row>
     <row r="5">
       <c r="A5" s="166" t="s">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="B5" s="166" t="s">
         <v>5</v>
@@ -20036,7 +20262,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="166" t="s">
-        <v>1178</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -20055,35 +20281,35 @@
     </row>
     <row r="7">
       <c r="A7" s="166" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="B7" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="166" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="D7" s="166" t="s">
-        <v>1286</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="166" t="s">
-        <v>1287</v>
+        <v>1311</v>
       </c>
       <c r="B8" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="166" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="D8" s="166" t="s">
-        <v>1288</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="166" t="s">
-        <v>1289</v>
+        <v>1313</v>
       </c>
       <c r="B9" s="166" t="s">
         <v>59</v>
@@ -20092,26 +20318,26 @@
         <v>60</v>
       </c>
       <c r="D9" s="166" t="s">
-        <v>1290</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="166" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B10" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="166" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D10" s="166" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="166" t="s">
-        <v>1291</v>
+        <v>1315</v>
       </c>
       <c r="B11" s="166" t="s">
         <v>5</v>
@@ -20120,12 +20346,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="166" t="s">
-        <v>1292</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="166" t="s">
-        <v>1246</v>
+        <v>1270</v>
       </c>
       <c r="B12" s="166" t="s">
         <v>59</v>
@@ -20134,12 +20360,12 @@
         <v>99</v>
       </c>
       <c r="D12" s="166" t="s">
-        <v>1293</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="166" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B13" s="166" t="s">
         <v>5</v>
@@ -20148,12 +20374,12 @@
         <v>64</v>
       </c>
       <c r="D13" s="166" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="166" t="s">
-        <v>1240</v>
+        <v>1264</v>
       </c>
       <c r="B14" s="166" t="s">
         <v>59</v>
@@ -20162,12 +20388,12 @@
         <v>60</v>
       </c>
       <c r="D14" s="166" t="s">
-        <v>1241</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="166" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B15" s="166" t="s">
         <v>138</v>
@@ -20181,21 +20407,21 @@
     </row>
     <row r="16">
       <c r="A16" s="166" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B16" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="166" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D16" s="166" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="166" t="s">
-        <v>1238</v>
+        <v>1262</v>
       </c>
       <c r="B17" s="166" t="s">
         <v>59</v>
@@ -20204,12 +20430,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="166" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="166" t="s">
-        <v>1242</v>
+        <v>1266</v>
       </c>
       <c r="B18" s="166" t="s">
         <v>59</v>
@@ -20218,12 +20444,12 @@
         <v>60</v>
       </c>
       <c r="D18" s="166" t="s">
-        <v>1243</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="166" t="s">
-        <v>1244</v>
+        <v>1268</v>
       </c>
       <c r="B19" s="166" t="s">
         <v>59</v>
@@ -20232,12 +20458,12 @@
         <v>60</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>1245</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="166" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B20" s="166" t="s">
         <v>138</v>
@@ -20251,35 +20477,35 @@
     </row>
     <row r="21">
       <c r="A21" s="166" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B21" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="166" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D21" s="166" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="166" t="s">
-        <v>1248</v>
+        <v>1272</v>
       </c>
       <c r="B22" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="166" t="s">
-        <v>1294</v>
+        <v>1318</v>
       </c>
       <c r="D22" s="166" t="s">
-        <v>1295</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="166" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B23" s="166" t="s">
         <v>166</v>
@@ -20293,7 +20519,7 @@
     </row>
     <row r="24">
       <c r="A24" s="166" t="s">
-        <v>1254</v>
+        <v>1278</v>
       </c>
       <c r="B24" s="166" t="s">
         <v>59</v>
@@ -20302,40 +20528,40 @@
         <v>99</v>
       </c>
       <c r="D24" s="166" t="s">
-        <v>1255</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="166" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B25" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C25" s="166" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D25" s="166" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="166" t="s">
-        <v>1296</v>
+        <v>1320</v>
       </c>
       <c r="B26" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="166" t="s">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="D26" s="166" t="s">
-        <v>1297</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="166" t="s">
-        <v>1298</v>
+        <v>1322</v>
       </c>
       <c r="B27" s="166" t="s">
         <v>63</v>
@@ -20349,35 +20575,35 @@
     </row>
     <row r="28">
       <c r="A28" s="166" t="s">
-        <v>1299</v>
+        <v>1323</v>
       </c>
       <c r="B28" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="166" t="s">
-        <v>1300</v>
+        <v>1324</v>
       </c>
       <c r="D28" s="166" t="s">
-        <v>1301</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="166" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B29" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="166" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D29" s="166" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="166" t="s">
-        <v>1302</v>
+        <v>1326</v>
       </c>
       <c r="B30" s="166" t="s">
         <v>5</v>
@@ -20386,12 +20612,12 @@
         <v>15</v>
       </c>
       <c r="D30" s="166" t="s">
-        <v>1303</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="166" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B31" s="166" t="s">
         <v>171</v>
@@ -20405,7 +20631,7 @@
     </row>
     <row r="32">
       <c r="A32" s="166" t="s">
-        <v>1258</v>
+        <v>1282</v>
       </c>
       <c r="B32" s="166" t="s">
         <v>59</v>
@@ -20414,12 +20640,12 @@
         <v>60</v>
       </c>
       <c r="D32" s="166" t="s">
-        <v>1259</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="166" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B33" s="166" t="s">
         <v>166</v>
@@ -20457,7 +20683,7 @@
     </row>
     <row r="2">
       <c r="A2" s="168" t="s">
-        <v>1304</v>
+        <v>1328</v>
       </c>
       <c r="B2" s="168" t="s">
         <v>5</v>
@@ -20466,7 +20692,7 @@
         <v>64</v>
       </c>
       <c r="D2" s="168" t="s">
-        <v>1305</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3">
@@ -20499,7 +20725,7 @@
     </row>
     <row r="5">
       <c r="A5" s="168" t="s">
-        <v>1306</v>
+        <v>1330</v>
       </c>
       <c r="B5" s="168" t="s">
         <v>5</v>
@@ -20508,7 +20734,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="168" t="s">
-        <v>1307</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="6">
@@ -20519,29 +20745,29 @@
         <v>5</v>
       </c>
       <c r="C6" s="168" t="s">
-        <v>1308</v>
+        <v>1332</v>
       </c>
       <c r="D6" s="168" t="s">
-        <v>1309</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="168" t="s">
-        <v>1310</v>
+        <v>1334</v>
       </c>
       <c r="B7" s="168" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="168" t="s">
-        <v>1311</v>
+        <v>1335</v>
       </c>
       <c r="D7" s="168" t="s">
-        <v>1312</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="168" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B8" s="168" t="s">
         <v>166</v>
@@ -20579,7 +20805,7 @@
     </row>
     <row r="2">
       <c r="A2" s="170" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B2" s="170" t="s">
         <v>171</v>
@@ -20593,16 +20819,16 @@
     </row>
     <row r="3">
       <c r="A3" s="170" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B3" s="170" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>1313</v>
+        <v>1337</v>
       </c>
       <c r="D3" s="170" t="s">
-        <v>1314</v>
+        <v>1338</v>
       </c>
     </row>
   </sheetData>
@@ -20645,21 +20871,21 @@
     </row>
     <row r="3">
       <c r="A3" s="172" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B3" s="172" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="172" t="s">
-        <v>1315</v>
+        <v>1339</v>
       </c>
       <c r="D3" s="172" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="172" t="s">
-        <v>1316</v>
+        <v>1340</v>
       </c>
       <c r="B4" s="172" t="s">
         <v>5</v>
@@ -20668,7 +20894,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="172" t="s">
-        <v>1317</v>
+        <v>1341</v>
       </c>
     </row>
   </sheetData>
@@ -20686,7 +20912,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="174" t="s">
-        <v>1318</v>
+        <v>1342</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -20711,16 +20937,16 @@
     </row>
     <row r="3">
       <c r="A3" s="174" t="s">
-        <v>1319</v>
+        <v>1343</v>
       </c>
       <c r="B3" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="174" t="s">
-        <v>1320</v>
+        <v>1344</v>
       </c>
       <c r="D3" s="174" t="s">
-        <v>1321</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="4">
@@ -20731,10 +20957,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="174" t="s">
-        <v>1322</v>
+        <v>1346</v>
       </c>
       <c r="D4" s="174" t="s">
-        <v>1323</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="5">
@@ -20745,10 +20971,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="174" t="s">
-        <v>1324</v>
+        <v>1348</v>
       </c>
       <c r="D5" s="174" t="s">
-        <v>1324</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="6">
@@ -20776,7 +21002,7 @@
         <v>64</v>
       </c>
       <c r="D7" s="174" t="s">
-        <v>1325</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="8">
@@ -20790,12 +21016,12 @@
         <v>64</v>
       </c>
       <c r="D8" s="174" t="s">
-        <v>1326</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="174" t="s">
-        <v>1327</v>
+        <v>1351</v>
       </c>
       <c r="B9" s="174" t="s">
         <v>226</v>
@@ -20818,7 +21044,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="174" t="s">
-        <v>1328</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="11">
@@ -20952,7 +21178,7 @@
         <v>145</v>
       </c>
       <c r="B20" s="174" t="s">
-        <v>1329</v>
+        <v>1353</v>
       </c>
       <c r="C20" s="174" t="s">
         <v>64</v>
@@ -20966,7 +21192,7 @@
         <v>147</v>
       </c>
       <c r="B21" s="174" t="s">
-        <v>1330</v>
+        <v>1354</v>
       </c>
       <c r="C21" s="174" t="s">
         <v>64</v>
@@ -20980,7 +21206,7 @@
         <v>149</v>
       </c>
       <c r="B22" s="174" t="s">
-        <v>1331</v>
+        <v>1355</v>
       </c>
       <c r="C22" s="174" t="s">
         <v>64</v>
@@ -20994,7 +21220,7 @@
         <v>151</v>
       </c>
       <c r="B23" s="174" t="s">
-        <v>1332</v>
+        <v>1356</v>
       </c>
       <c r="C23" s="174" t="s">
         <v>64</v>
@@ -21008,7 +21234,7 @@
         <v>153</v>
       </c>
       <c r="B24" s="174" t="s">
-        <v>1333</v>
+        <v>1357</v>
       </c>
       <c r="C24" s="174" t="s">
         <v>64</v>
@@ -21022,7 +21248,7 @@
         <v>155</v>
       </c>
       <c r="B25" s="174" t="s">
-        <v>1334</v>
+        <v>1358</v>
       </c>
       <c r="C25" s="174" t="s">
         <v>64</v>
@@ -21036,7 +21262,7 @@
         <v>201</v>
       </c>
       <c r="B26" s="174" t="s">
-        <v>1335</v>
+        <v>1359</v>
       </c>
       <c r="C26" s="174" t="s">
         <v>64</v>
@@ -21050,7 +21276,7 @@
         <v>157</v>
       </c>
       <c r="B27" s="174" t="s">
-        <v>1336</v>
+        <v>1360</v>
       </c>
       <c r="C27" s="174" t="s">
         <v>64</v>
@@ -21064,7 +21290,7 @@
         <v>159</v>
       </c>
       <c r="B28" s="174" t="s">
-        <v>1337</v>
+        <v>1361</v>
       </c>
       <c r="C28" s="174" t="s">
         <v>64</v>
@@ -21078,7 +21304,7 @@
         <v>161</v>
       </c>
       <c r="B29" s="174" t="s">
-        <v>1338</v>
+        <v>1362</v>
       </c>
       <c r="C29" s="174" t="s">
         <v>64</v>
@@ -21092,7 +21318,7 @@
         <v>163</v>
       </c>
       <c r="B30" s="174" t="s">
-        <v>1338</v>
+        <v>1362</v>
       </c>
       <c r="C30" s="174" t="s">
         <v>64</v>
@@ -21106,7 +21332,7 @@
         <v>164</v>
       </c>
       <c r="B31" s="174" t="s">
-        <v>1338</v>
+        <v>1362</v>
       </c>
       <c r="C31" s="174" t="s">
         <v>64</v>
@@ -21162,7 +21388,7 @@
         <v>173</v>
       </c>
       <c r="B35" s="174" t="s">
-        <v>1339</v>
+        <v>1363</v>
       </c>
       <c r="C35" s="174" t="s">
         <v>64</v>
@@ -21176,7 +21402,7 @@
         <v>175</v>
       </c>
       <c r="B36" s="174" t="s">
-        <v>1340</v>
+        <v>1364</v>
       </c>
       <c r="C36" s="174" t="s">
         <v>64</v>
@@ -21190,7 +21416,7 @@
         <v>177</v>
       </c>
       <c r="B37" s="174" t="s">
-        <v>1341</v>
+        <v>1365</v>
       </c>
       <c r="C37" s="174" t="s">
         <v>64</v>
@@ -21204,7 +21430,7 @@
         <v>179</v>
       </c>
       <c r="B38" s="174" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="C38" s="174" t="s">
         <v>64</v>
@@ -21218,7 +21444,7 @@
         <v>181</v>
       </c>
       <c r="B39" s="174" t="s">
-        <v>1343</v>
+        <v>1367</v>
       </c>
       <c r="C39" s="174" t="s">
         <v>64</v>
@@ -21232,7 +21458,7 @@
         <v>183</v>
       </c>
       <c r="B40" s="174" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="C40" s="174" t="s">
         <v>64</v>
@@ -21246,7 +21472,7 @@
         <v>185</v>
       </c>
       <c r="B41" s="174" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="C41" s="174" t="s">
         <v>64</v>
@@ -21260,7 +21486,7 @@
         <v>187</v>
       </c>
       <c r="B42" s="174" t="s">
-        <v>1346</v>
+        <v>1370</v>
       </c>
       <c r="C42" s="174" t="s">
         <v>64</v>
@@ -21274,7 +21500,7 @@
         <v>189</v>
       </c>
       <c r="B43" s="174" t="s">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="C43" s="174" t="s">
         <v>64</v>
@@ -21288,7 +21514,7 @@
         <v>191</v>
       </c>
       <c r="B44" s="174" t="s">
-        <v>1348</v>
+        <v>1372</v>
       </c>
       <c r="C44" s="174" t="s">
         <v>64</v>
@@ -21330,7 +21556,7 @@
         <v>217</v>
       </c>
       <c r="B47" s="174" t="s">
-        <v>1349</v>
+        <v>1373</v>
       </c>
       <c r="C47" s="174" t="s">
         <v>64</v>
@@ -21344,7 +21570,7 @@
         <v>205</v>
       </c>
       <c r="B48" s="174" t="s">
-        <v>1350</v>
+        <v>1374</v>
       </c>
       <c r="C48" s="174" t="s">
         <v>64</v>
@@ -21400,7 +21626,7 @@
         <v>235</v>
       </c>
       <c r="B52" s="174" t="s">
-        <v>1351</v>
+        <v>1375</v>
       </c>
       <c r="C52" s="174" t="s">
         <v>64</v>
@@ -21414,7 +21640,7 @@
         <v>198</v>
       </c>
       <c r="B53" s="174" t="s">
-        <v>1352</v>
+        <v>1376</v>
       </c>
       <c r="C53" s="174" t="s">
         <v>64</v>
@@ -21428,7 +21654,7 @@
         <v>233</v>
       </c>
       <c r="B54" s="174" t="s">
-        <v>1353</v>
+        <v>1377</v>
       </c>
       <c r="C54" s="174" t="s">
         <v>64</v>
@@ -21455,7 +21681,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>1354</v>
+        <v>1378</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -21480,7 +21706,7 @@
     </row>
     <row r="3">
       <c r="A3" s="176" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B3" s="176" t="s">
         <v>166</v>
@@ -21494,7 +21720,7 @@
     </row>
     <row r="4">
       <c r="A4" s="176" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B4" s="176" t="s">
         <v>166</v>
@@ -21508,7 +21734,7 @@
     </row>
     <row r="5">
       <c r="A5" s="176" t="s">
-        <v>1355</v>
+        <v>1379</v>
       </c>
       <c r="B5" s="176" t="s">
         <v>247</v>
@@ -21517,12 +21743,12 @@
         <v>15</v>
       </c>
       <c r="D5" s="176" t="s">
-        <v>1356</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="176" t="s">
-        <v>1357</v>
+        <v>1381</v>
       </c>
       <c r="B6" s="176" t="s">
         <v>247</v>
@@ -21531,124 +21757,124 @@
         <v>15</v>
       </c>
       <c r="D6" s="176" t="s">
-        <v>1358</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="176" t="s">
-        <v>1359</v>
+        <v>1383</v>
       </c>
       <c r="B7" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="176" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D7" s="176" t="s">
-        <v>1360</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="176" t="s">
-        <v>1361</v>
+        <v>1385</v>
       </c>
       <c r="B8" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="176" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D8" s="176" t="s">
-        <v>1362</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="176" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="B9" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="176" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D9" s="176" t="s">
-        <v>1363</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="176" t="s">
-        <v>1364</v>
+        <v>1388</v>
       </c>
       <c r="B10" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="176" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D10" s="176" t="s">
-        <v>1365</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="176" t="s">
-        <v>1366</v>
+        <v>1390</v>
       </c>
       <c r="B11" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="176" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D11" s="176" t="s">
-        <v>1367</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="176" t="s">
-        <v>1368</v>
+        <v>1392</v>
       </c>
       <c r="B12" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="176" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D12" s="176" t="s">
-        <v>1369</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="176" t="s">
-        <v>1370</v>
+        <v>1394</v>
       </c>
       <c r="B13" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="176" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D13" s="176" t="s">
-        <v>1371</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="176" t="s">
-        <v>1372</v>
+        <v>1396</v>
       </c>
       <c r="B14" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="176" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D14" s="176" t="s">
-        <v>1373</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="176" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B15" s="176" t="s">
         <v>138</v>
@@ -21662,21 +21888,21 @@
     </row>
     <row r="16">
       <c r="A16" s="176" t="s">
-        <v>1374</v>
+        <v>1398</v>
       </c>
       <c r="B16" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="176" t="s">
-        <v>1375</v>
+        <v>1399</v>
       </c>
       <c r="D16" s="176" t="s">
-        <v>1376</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="176" t="s">
-        <v>1377</v>
+        <v>1401</v>
       </c>
       <c r="B17" s="176" t="s">
         <v>59</v>
@@ -21685,12 +21911,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="176" t="s">
-        <v>1378</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="176" t="s">
-        <v>1379</v>
+        <v>1403</v>
       </c>
       <c r="B18" s="176" t="s">
         <v>5</v>
@@ -21699,12 +21925,12 @@
         <v>32</v>
       </c>
       <c r="D18" s="176" t="s">
-        <v>1380</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="176" t="s">
-        <v>1381</v>
+        <v>1405</v>
       </c>
       <c r="B19" s="176" t="s">
         <v>128</v>
@@ -21713,12 +21939,12 @@
         <v>64</v>
       </c>
       <c r="D19" s="176" t="s">
-        <v>1382</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="176" t="s">
-        <v>1383</v>
+        <v>1407</v>
       </c>
       <c r="B20" s="176" t="s">
         <v>247</v>
@@ -21727,7 +21953,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="176" t="s">
-        <v>1384</v>
+        <v>1408</v>
       </c>
     </row>
   </sheetData>
@@ -21748,7 +21974,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="178" t="s">
-        <v>1354</v>
+        <v>1378</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -21787,7 +22013,7 @@
     </row>
     <row r="4">
       <c r="A4" s="178" t="s">
-        <v>1385</v>
+        <v>1409</v>
       </c>
       <c r="B4" s="178" t="s">
         <v>166</v>
@@ -21810,12 +22036,12 @@
         <v>15</v>
       </c>
       <c r="D5" s="178" t="s">
-        <v>1386</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="178" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B6" s="178" t="s">
         <v>171</v>
@@ -21829,35 +22055,35 @@
     </row>
     <row r="7">
       <c r="A7" s="178" t="s">
-        <v>1370</v>
+        <v>1394</v>
       </c>
       <c r="B7" s="178" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="178" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D7" s="178" t="s">
-        <v>1387</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="178" t="s">
-        <v>1372</v>
+        <v>1396</v>
       </c>
       <c r="B8" s="178" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="178" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D8" s="178" t="s">
-        <v>1388</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="178" t="s">
-        <v>1389</v>
+        <v>1413</v>
       </c>
       <c r="B9" s="178" t="s">
         <v>5</v>
@@ -21866,7 +22092,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="178" t="s">
-        <v>1390</v>
+        <v>1414</v>
       </c>
     </row>
   </sheetData>
@@ -21981,7 +22207,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="180" t="s">
-        <v>1354</v>
+        <v>1378</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -22020,7 +22246,7 @@
     </row>
     <row r="4">
       <c r="A4" s="180" t="s">
-        <v>1385</v>
+        <v>1409</v>
       </c>
       <c r="B4" s="180" t="s">
         <v>166</v>
@@ -22043,12 +22269,12 @@
         <v>15</v>
       </c>
       <c r="D5" s="180" t="s">
-        <v>1386</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="180" t="s">
-        <v>1391</v>
+        <v>1415</v>
       </c>
       <c r="B6" s="180" t="s">
         <v>5</v>
@@ -22057,7 +22283,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="180" t="s">
-        <v>1392</v>
+        <v>1416</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
+++ b/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4580" uniqueCount="1434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4584" uniqueCount="1434">
   <si>
     <t>Campo</t>
   </si>
@@ -1721,6 +1721,15 @@
     <t>accordoScioglimento</t>
   </si>
   <si>
+    <t>officianteEventoUnioneCivile</t>
+  </si>
+  <si>
+    <t>Gianni Rossi Sindaco</t>
+  </si>
+  <si>
+    <t>Officiante che ha celebrato l'unione civile.</t>
+  </si>
+  <si>
     <t>Testo libero per modifica accordo (formula 121-septies.1)</t>
   </si>
   <si>
@@ -4122,15 +4131,6 @@
   </si>
   <si>
     <t>luogoEventoUnioneCivile</t>
-  </si>
-  <si>
-    <t>officianteEventoUnioneCivile</t>
-  </si>
-  <si>
-    <t>Gianni Rossi Sindaco</t>
-  </si>
-  <si>
-    <t>Officiante che ha celebrato l'unione civile.</t>
   </si>
   <si>
     <t>tipoProvvedimentoScioglimento</t>
@@ -10027,7 +10027,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10200,43 +10200,57 @@
     </row>
     <row r="13">
       <c r="A13" s="62" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="B13" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="62" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="62" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="B14" s="62" t="s">
-        <v>406</v>
+        <v>5</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>64</v>
+        <v>524</v>
       </c>
       <c r="D14" s="62" t="s">
-        <v>64</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="62" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B15" s="62" t="s">
+        <v>406</v>
+      </c>
+      <c r="C15" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="62" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="62" t="s">
+        <v>544</v>
+      </c>
+      <c r="B16" s="62" t="s">
         <v>366</v>
       </c>
-      <c r="C15" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="62" t="s">
+      <c r="C16" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="62" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10266,7 +10280,7 @@
     </row>
     <row r="2">
       <c r="A2" s="64" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B2" s="64" t="s">
         <v>366</v>
@@ -10280,7 +10294,7 @@
     </row>
     <row r="3">
       <c r="A3" s="64" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B3" s="64" t="s">
         <v>366</v>
@@ -10294,7 +10308,7 @@
     </row>
     <row r="4">
       <c r="A4" s="64" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B4" s="64" t="s">
         <v>380</v>
@@ -10346,7 +10360,7 @@
     </row>
     <row r="3">
       <c r="A3" s="66" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B3" s="66" t="s">
         <v>5</v>
@@ -10355,7 +10369,7 @@
         <v>64</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
@@ -10384,7 +10398,7 @@
     </row>
     <row r="2">
       <c r="A2" s="68" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B2" s="68" t="s">
         <v>5</v>
@@ -10393,12 +10407,12 @@
         <v>199</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="68" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B3" s="68" t="s">
         <v>5</v>
@@ -10407,26 +10421,26 @@
         <v>199</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="68" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B4" s="68" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="68" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B5" s="68" t="s">
         <v>5</v>
@@ -10435,7 +10449,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -10464,7 +10478,7 @@
     </row>
     <row r="2">
       <c r="A2" s="70" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B2" s="70" t="s">
         <v>5</v>
@@ -10478,7 +10492,7 @@
     </row>
     <row r="3">
       <c r="A3" s="70" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B3" s="70" t="s">
         <v>5</v>
@@ -10501,7 +10515,7 @@
         <v>352</v>
       </c>
       <c r="D4" s="70" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -10530,16 +10544,16 @@
     </row>
     <row r="2">
       <c r="A2" s="72" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B2" s="72" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D2" s="72" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -10568,24 +10582,24 @@
     </row>
     <row r="2">
       <c r="A2" s="74" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B2" s="74" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D2" s="74" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="74" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C3" s="74" t="s">
         <v>64</v>
@@ -10596,16 +10610,16 @@
     </row>
     <row r="4">
       <c r="A4" s="74" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B4" s="74" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D4" s="74" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
@@ -10648,7 +10662,7 @@
     </row>
     <row r="3">
       <c r="A3" s="76" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B3" s="76" t="s">
         <v>5</v>
@@ -10686,16 +10700,16 @@
     </row>
     <row r="2">
       <c r="A2" s="78" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B2" s="78" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D2" s="78" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>
@@ -10828,7 +10842,7 @@
     </row>
     <row r="2">
       <c r="A2" s="82" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B2" s="82" t="s">
         <v>364</v>
@@ -10842,7 +10856,7 @@
     </row>
     <row r="3">
       <c r="A3" s="82" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B3" s="82" t="s">
         <v>406</v>
@@ -10917,7 +10931,7 @@
         <v>64</v>
       </c>
       <c r="D4" s="84" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -11060,113 +11074,113 @@
         <v>5</v>
       </c>
       <c r="C2" s="90" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D2" s="90" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="90" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B3" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="90" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D3" s="90" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="90" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B4" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="90" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B5" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="90" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D5" s="90" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="90" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B6" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="90" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D6" s="90" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="90" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B7" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="90" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D7" s="90" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="90" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B8" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="90" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D8" s="90" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="90" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B9" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="90" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D9" s="90" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="90" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B10" s="90" t="s">
         <v>5</v>
@@ -11175,68 +11189,68 @@
         <v>15</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="90" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B11" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="90" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D11" s="90" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="90" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B12" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="90" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D12" s="90" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="90" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B13" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="90" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D13" s="90" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="90" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B14" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="90" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D14" s="90" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="90" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B15" s="90" t="s">
         <v>5</v>
@@ -11245,82 +11259,82 @@
         <v>72</v>
       </c>
       <c r="D15" s="90" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="90" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B16" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="90" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D16" s="90" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="90" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B17" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="90" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D17" s="90" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="90" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B18" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="90" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D18" s="90" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="90" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B19" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="90" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D19" s="90" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="90" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B20" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="90" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D20" s="90" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="90" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B21" s="90" t="s">
         <v>5</v>
@@ -11329,49 +11343,49 @@
         <v>72</v>
       </c>
       <c r="D21" s="90" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="90" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B22" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="90" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D22" s="90" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="90" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B23" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D23" s="90" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="90" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B24" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="90" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D24" s="90" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="25">
@@ -11385,12 +11399,12 @@
         <v>333</v>
       </c>
       <c r="D25" s="90" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="90" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B26" s="90" t="s">
         <v>5</v>
@@ -11399,26 +11413,26 @@
         <v>15</v>
       </c>
       <c r="D26" s="90" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="90" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B27" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="90" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D27" s="90" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="90" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B28" s="90" t="s">
         <v>5</v>
@@ -11427,12 +11441,12 @@
         <v>64</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="90" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B29" s="90" t="s">
         <v>5</v>
@@ -11441,21 +11455,21 @@
         <v>15</v>
       </c>
       <c r="D29" s="90" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="90" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B30" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="90" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D30" s="90" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="31">
@@ -11474,7 +11488,7 @@
     </row>
     <row r="32">
       <c r="A32" s="90" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B32" s="90" t="s">
         <v>59</v>
@@ -11483,12 +11497,12 @@
         <v>99</v>
       </c>
       <c r="D32" s="90" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="90" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B33" s="90" t="s">
         <v>59</v>
@@ -11497,12 +11511,12 @@
         <v>99</v>
       </c>
       <c r="D33" s="90" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="90" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B34" s="90" t="s">
         <v>59</v>
@@ -11511,40 +11525,40 @@
         <v>99</v>
       </c>
       <c r="D34" s="90" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="90" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B35" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="90" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D35" s="90" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="90" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B36" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="90" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D36" s="90" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="90" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B37" s="90" t="s">
         <v>5</v>
@@ -11553,29 +11567,29 @@
         <v>72</v>
       </c>
       <c r="D37" s="90" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="90" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B38" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="90" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D38" s="90" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="90" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B39" s="90" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C39" s="90" t="s">
         <v>64</v>
@@ -11586,10 +11600,10 @@
     </row>
     <row r="40">
       <c r="A40" s="90" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B40" s="90" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C40" s="90" t="s">
         <v>64</v>
@@ -11609,12 +11623,12 @@
         <v>318</v>
       </c>
       <c r="D41" s="90" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="90" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B42" s="90" t="s">
         <v>59</v>
@@ -11623,12 +11637,12 @@
         <v>99</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="90" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B43" s="90" t="s">
         <v>59</v>
@@ -11637,7 +11651,7 @@
         <v>99</v>
       </c>
       <c r="D43" s="90" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="44">
@@ -11656,7 +11670,7 @@
     </row>
     <row r="45">
       <c r="A45" s="90" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B45" s="90" t="s">
         <v>5</v>
@@ -11665,21 +11679,21 @@
         <v>83</v>
       </c>
       <c r="D45" s="90" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="90" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B46" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="90" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D46" s="90" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -11708,7 +11722,7 @@
     </row>
     <row r="2">
       <c r="A2" s="92" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B2" s="92" t="s">
         <v>5</v>
@@ -11717,12 +11731,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="92" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="92" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B3" s="92" t="s">
         <v>5</v>
@@ -11731,12 +11745,12 @@
         <v>199</v>
       </c>
       <c r="D3" s="92" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="92" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B4" s="92" t="s">
         <v>5</v>
@@ -11745,40 +11759,40 @@
         <v>199</v>
       </c>
       <c r="D4" s="92" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="92" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B5" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="92" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D5" s="92" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="92" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B6" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D6" s="92" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="92" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B7" s="92" t="s">
         <v>5</v>
@@ -11787,12 +11801,12 @@
         <v>72</v>
       </c>
       <c r="D7" s="92" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="92" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B8" s="92" t="s">
         <v>5</v>
@@ -11801,96 +11815,96 @@
         <v>72</v>
       </c>
       <c r="D8" s="92" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="92" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B9" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="92" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D9" s="92" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="92" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B10" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D10" s="92" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="92" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B11" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="92" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D11" s="92" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="92" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B12" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="92" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D12" s="92" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="92" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B13" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="92" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D13" s="92" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="92" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B14" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="92" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D14" s="92" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="92" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B15" s="92" t="s">
         <v>5</v>
@@ -11899,21 +11913,21 @@
         <v>3</v>
       </c>
       <c r="D15" s="92" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="92" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B16" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="92" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>
@@ -11976,10 +11990,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
@@ -12018,15 +12032,15 @@
         <v>5</v>
       </c>
       <c r="C2" s="96" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="96" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B3" s="96" t="s">
         <v>5</v>
@@ -12035,40 +12049,40 @@
         <v>15</v>
       </c>
       <c r="D3" s="96" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="96" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B4" s="96" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="96" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="96" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B5" s="96" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="96" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D5" s="96" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="96" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B6" s="96" t="s">
         <v>5</v>
@@ -12077,12 +12091,12 @@
         <v>388</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="96" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B7" s="96" t="s">
         <v>5</v>
@@ -12091,12 +12105,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="96" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="96" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B8" s="96" t="s">
         <v>5</v>
@@ -12105,7 +12119,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -12123,7 +12137,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="98" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -12171,12 +12185,12 @@
         <v>333</v>
       </c>
       <c r="D4" s="98" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="98" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B5" s="98" t="s">
         <v>5</v>
@@ -12185,26 +12199,26 @@
         <v>64</v>
       </c>
       <c r="D5" s="98" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="98" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B6" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="98" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D6" s="98" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="98" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B7" s="98" t="s">
         <v>5</v>
@@ -12213,7 +12227,7 @@
         <v>40</v>
       </c>
       <c r="D7" s="98" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -12232,7 +12246,7 @@
     </row>
     <row r="9">
       <c r="A9" s="98" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B9" s="98" t="s">
         <v>5</v>
@@ -12241,12 +12255,12 @@
         <v>102</v>
       </c>
       <c r="D9" s="98" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="98" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B10" s="98" t="s">
         <v>5</v>
@@ -12255,26 +12269,26 @@
         <v>64</v>
       </c>
       <c r="D10" s="98" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="98" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B11" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D11" s="98" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="98" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B12" s="98" t="s">
         <v>5</v>
@@ -12283,12 +12297,12 @@
         <v>102</v>
       </c>
       <c r="D12" s="98" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="98" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B13" s="98" t="s">
         <v>5</v>
@@ -12297,7 +12311,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="98" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="14">
@@ -12330,7 +12344,7 @@
     </row>
     <row r="16">
       <c r="A16" s="98" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B16" s="98" t="s">
         <v>5</v>
@@ -12339,12 +12353,12 @@
         <v>15</v>
       </c>
       <c r="D16" s="98" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="98" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B17" s="98" t="s">
         <v>5</v>
@@ -12353,40 +12367,40 @@
         <v>15</v>
       </c>
       <c r="D17" s="98" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="98" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B18" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="98" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D18" s="98" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="98" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B19" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="98" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D19" s="98" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="98" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B20" s="98" t="s">
         <v>5</v>
@@ -12395,7 +12409,7 @@
         <v>40</v>
       </c>
       <c r="D20" s="98" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -12846,7 +12860,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="100" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -12871,21 +12885,21 @@
     </row>
     <row r="3">
       <c r="A3" s="100" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B3" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="100" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D3" s="100" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="100" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B4" s="100" t="s">
         <v>5</v>
@@ -12894,26 +12908,26 @@
         <v>15</v>
       </c>
       <c r="D4" s="100" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="100" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B5" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="100" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D5" s="100" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="100" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B6" s="100" t="s">
         <v>5</v>
@@ -12922,21 +12936,21 @@
         <v>15</v>
       </c>
       <c r="D6" s="100" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="100" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B7" s="100" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="100" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D7" s="100" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -12968,58 +12982,58 @@
     </row>
     <row r="2">
       <c r="A2" s="102" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B2" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="102" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D2" s="102" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="102" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B3" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="102" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D3" s="102" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="102" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B4" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="102" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B5" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="102" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D5" s="102" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6">
@@ -13033,7 +13047,7 @@
         <v>343</v>
       </c>
       <c r="D6" s="102" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
@@ -13044,10 +13058,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="102" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D7" s="102" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="8">
@@ -13058,24 +13072,24 @@
         <v>5</v>
       </c>
       <c r="C8" s="102" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="D8" s="102" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="102" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B9" s="102" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="102" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D9" s="102" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="10">
@@ -13089,7 +13103,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="102" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -13118,30 +13132,30 @@
     </row>
     <row r="2">
       <c r="A2" s="104" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B2" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="104" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D2" s="104" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="104" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B3" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="104" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D3" s="104" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="4">
@@ -13160,21 +13174,21 @@
     </row>
     <row r="5">
       <c r="A5" s="104" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B5" s="104" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="104" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D5" s="104" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="104" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B6" s="104" t="s">
         <v>5</v>
@@ -13183,12 +13197,12 @@
         <v>64</v>
       </c>
       <c r="D6" s="104" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="104" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B7" s="104" t="s">
         <v>5</v>
@@ -13197,7 +13211,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="104" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
     </row>
     <row r="8">
@@ -13254,7 +13268,7 @@
     </row>
     <row r="3">
       <c r="A3" s="106" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B3" s="106" t="s">
         <v>5</v>
@@ -13263,12 +13277,12 @@
         <v>66</v>
       </c>
       <c r="D3" s="106" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="106" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B4" s="106" t="s">
         <v>5</v>
@@ -13277,12 +13291,12 @@
         <v>69</v>
       </c>
       <c r="D4" s="106" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="106" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B5" s="106" t="s">
         <v>5</v>
@@ -13291,12 +13305,12 @@
         <v>72</v>
       </c>
       <c r="D5" s="106" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="106" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B6" s="106" t="s">
         <v>5</v>
@@ -13305,35 +13319,35 @@
         <v>72</v>
       </c>
       <c r="D6" s="106" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="106" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="B7" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="106" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D7" s="106" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="106" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B8" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="106" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D8" s="106" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="9">
@@ -13366,72 +13380,72 @@
     </row>
     <row r="11">
       <c r="A11" s="106" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B11" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="106" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D11" s="106" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="106" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B12" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="106" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D12" s="106" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="106" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B13" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="106" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D13" s="106" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="106" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B14" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="106" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D14" s="106" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="106" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B15" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="106" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D15" s="106" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="16">
@@ -13442,15 +13456,15 @@
         <v>5</v>
       </c>
       <c r="C16" s="106" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D16" s="106" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="106" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B17" s="106" t="s">
         <v>5</v>
@@ -13459,40 +13473,40 @@
         <v>35</v>
       </c>
       <c r="D17" s="106" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="106" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="B18" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="106" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D18" s="106" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="106" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B19" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D19" s="106" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="106" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B20" s="106" t="s">
         <v>5</v>
@@ -13501,21 +13515,21 @@
         <v>45</v>
       </c>
       <c r="D20" s="106" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="106" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B21" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="106" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D21" s="106" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="22">
@@ -13534,16 +13548,16 @@
     </row>
     <row r="23">
       <c r="A23" s="106" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B23" s="106" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="106" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D23" s="106" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -13572,49 +13586,49 @@
     </row>
     <row r="2">
       <c r="A2" s="108" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B2" s="108" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="108" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D2" s="108" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="108" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B3" s="108" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="108" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D3" s="108" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="108" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B4" s="108" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="108" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="108" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B5" s="108" t="s">
         <v>5</v>
@@ -13623,7 +13637,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="108" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -13652,7 +13666,7 @@
     </row>
     <row r="2">
       <c r="A2" s="110" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B2" s="110" t="s">
         <v>5</v>
@@ -13661,12 +13675,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="110" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="110" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B3" s="110" t="s">
         <v>5</v>
@@ -13675,7 +13689,7 @@
         <v>143</v>
       </c>
       <c r="D3" s="110" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -13713,21 +13727,21 @@
         <v>15</v>
       </c>
       <c r="D2" s="112" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="112" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B3" s="112" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="112" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D3" s="112" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="4">
@@ -13826,7 +13840,7 @@
     </row>
     <row r="3">
       <c r="A3" s="114" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B3" s="114" t="s">
         <v>5</v>
@@ -13835,12 +13849,12 @@
         <v>15</v>
       </c>
       <c r="D3" s="114" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="114" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B4" s="114" t="s">
         <v>5</v>
@@ -13849,21 +13863,21 @@
         <v>15</v>
       </c>
       <c r="D4" s="114" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="114" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B5" s="114" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D5" s="114" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="6">
@@ -13896,21 +13910,21 @@
     </row>
     <row r="8">
       <c r="A8" s="114" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B8" s="114" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="114" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D8" s="114" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="114" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B9" s="114" t="s">
         <v>5</v>
@@ -13919,12 +13933,12 @@
         <v>78</v>
       </c>
       <c r="D9" s="114" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="114" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B10" s="114" t="s">
         <v>59</v>
@@ -13933,12 +13947,12 @@
         <v>99</v>
       </c>
       <c r="D10" s="114" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="114" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B11" s="114" t="s">
         <v>59</v>
@@ -13947,12 +13961,12 @@
         <v>99</v>
       </c>
       <c r="D11" s="114" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="114" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B12" s="114" t="s">
         <v>59</v>
@@ -13961,12 +13975,12 @@
         <v>99</v>
       </c>
       <c r="D12" s="114" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="114" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B13" s="114" t="s">
         <v>59</v>
@@ -13975,12 +13989,12 @@
         <v>99</v>
       </c>
       <c r="D13" s="114" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="114" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B14" s="114" t="s">
         <v>59</v>
@@ -13989,12 +14003,12 @@
         <v>60</v>
       </c>
       <c r="D14" s="114" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="114" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B15" s="114" t="s">
         <v>5</v>
@@ -14003,7 +14017,7 @@
         <v>388</v>
       </c>
       <c r="D15" s="114" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="16">
@@ -14060,30 +14074,30 @@
     </row>
     <row r="2">
       <c r="A2" s="116" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B2" s="116" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="116" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D2" s="116" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="116" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B3" s="116" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="116" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D3" s="116" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>
@@ -14112,7 +14126,7 @@
     </row>
     <row r="2">
       <c r="A2" s="118" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B2" s="118" t="s">
         <v>59</v>
@@ -14121,7 +14135,7 @@
         <v>99</v>
       </c>
       <c r="D2" s="118" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="3">
@@ -14143,7 +14157,7 @@
         <v>472</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C4" s="118" t="s">
         <v>64</v>
@@ -14233,7 +14247,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="120" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14258,30 +14272,30 @@
     </row>
     <row r="3">
       <c r="A3" s="120" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B3" s="120" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="120" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D3" s="120" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="120" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B4" s="120" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="120" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D4" s="120" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
   </sheetData>
@@ -14302,7 +14316,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14327,21 +14341,21 @@
     </row>
     <row r="3">
       <c r="A3" s="122" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B3" s="122" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="122" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D3" s="122" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="122" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B4" s="122" t="s">
         <v>5</v>
@@ -14350,7 +14364,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="122" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="5">
@@ -14375,10 +14389,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="122" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D6" s="122" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
   </sheetData>
@@ -14399,7 +14413,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="124" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14424,7 +14438,7 @@
     </row>
     <row r="3">
       <c r="A3" s="124" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B3" s="124" t="s">
         <v>5</v>
@@ -14433,21 +14447,21 @@
         <v>15</v>
       </c>
       <c r="D3" s="124" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="124" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B4" s="124" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="124" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D4" s="124" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
     <row r="5">
@@ -14483,7 +14497,7 @@
         <v>474</v>
       </c>
       <c r="B7" s="124" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C7" s="124" t="s">
         <v>64</v>
@@ -14497,7 +14511,7 @@
         <v>451</v>
       </c>
       <c r="B8" s="124" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C8" s="124" t="s">
         <v>64</v>
@@ -14508,7 +14522,7 @@
     </row>
     <row r="9">
       <c r="A9" s="124" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B9" s="124" t="s">
         <v>172</v>
@@ -14536,7 +14550,7 @@
     </row>
     <row r="11">
       <c r="A11" s="124" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B11" s="124" t="s">
         <v>172</v>
@@ -14604,7 +14618,7 @@
         <v>392</v>
       </c>
       <c r="B1" s="128" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -14643,7 +14657,7 @@
     </row>
     <row r="4">
       <c r="A4" s="128" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B4" s="128" t="s">
         <v>5</v>
@@ -14652,12 +14666,12 @@
         <v>15</v>
       </c>
       <c r="D4" s="128" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="128" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B5" s="128" t="s">
         <v>5</v>
@@ -14666,7 +14680,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="128" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="6">
@@ -14677,7 +14691,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="128" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="D6" s="128" t="s">
         <v>485</v>
@@ -14685,7 +14699,7 @@
     </row>
     <row r="7">
       <c r="A7" s="128" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B7" s="128" t="s">
         <v>5</v>
@@ -14694,12 +14708,12 @@
         <v>145</v>
       </c>
       <c r="D7" s="128" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="128" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B8" s="128" t="s">
         <v>5</v>
@@ -14708,12 +14722,12 @@
         <v>64</v>
       </c>
       <c r="D8" s="128" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="128" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B9" s="128" t="s">
         <v>59</v>
@@ -14722,26 +14736,26 @@
         <v>99</v>
       </c>
       <c r="D9" s="128" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="128" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B10" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="128" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D10" s="128" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="128" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B11" s="128" t="s">
         <v>5</v>
@@ -14750,7 +14764,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="128" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="12">
@@ -14769,35 +14783,35 @@
     </row>
     <row r="13">
       <c r="A13" s="128" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B13" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="128" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D13" s="128" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="128" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B14" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="128" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D14" s="128" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="128" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B15" s="128" t="s">
         <v>5</v>
@@ -14806,26 +14820,26 @@
         <v>15</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="128" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B16" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="128" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D16" s="128" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="128" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B17" s="128" t="s">
         <v>5</v>
@@ -14834,63 +14848,63 @@
         <v>15</v>
       </c>
       <c r="D17" s="128" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="128" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B18" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="128" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D18" s="128" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="128" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B19" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="128" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D19" s="128" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="128" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B20" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="128" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="128" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B21" s="128" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="128" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="D21" s="128" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="22">
@@ -14937,7 +14951,7 @@
     </row>
     <row r="25">
       <c r="A25" s="128" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B25" s="128" t="s">
         <v>59</v>
@@ -14946,12 +14960,12 @@
         <v>60</v>
       </c>
       <c r="D25" s="128" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="128" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B26" s="128" t="s">
         <v>5</v>
@@ -14960,7 +14974,7 @@
         <v>27</v>
       </c>
       <c r="D26" s="128" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="27">
@@ -14996,13 +15010,13 @@
         <v>422</v>
       </c>
       <c r="B29" s="128" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C29" s="128" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="128" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -15063,16 +15077,16 @@
     </row>
     <row r="4">
       <c r="A4" s="130" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B4" s="130" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="130" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D4" s="130" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="5">
@@ -15083,10 +15097,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="130" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D5" s="130" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="6">
@@ -15097,10 +15111,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="130" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D6" s="130" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -15114,7 +15128,7 @@
         <v>66</v>
       </c>
       <c r="D7" s="130" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="8">
@@ -15125,7 +15139,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="130" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="D8" s="130" t="s">
         <v>272</v>
@@ -15142,7 +15156,7 @@
         <v>72</v>
       </c>
       <c r="D9" s="130" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -15178,7 +15192,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="132" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -15231,7 +15245,7 @@
     </row>
     <row r="5">
       <c r="A5" s="132" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B5" s="132" t="s">
         <v>5</v>
@@ -15240,21 +15254,21 @@
         <v>15</v>
       </c>
       <c r="D5" s="132" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="132" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B6" s="132" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="132" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D6" s="132" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
   </sheetData>
@@ -15288,7 +15302,7 @@
     </row>
     <row r="2">
       <c r="A2" s="134" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B2" s="134" t="s">
         <v>59</v>
@@ -15297,7 +15311,7 @@
         <v>60</v>
       </c>
       <c r="D2" s="134" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="3">
@@ -15305,7 +15319,7 @@
         <v>372</v>
       </c>
       <c r="B3" s="134" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C3" s="134" t="s">
         <v>64</v>
@@ -15325,7 +15339,7 @@
         <v>375</v>
       </c>
       <c r="D4" s="134" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="5">
@@ -15344,49 +15358,49 @@
     </row>
     <row r="6">
       <c r="A6" s="134" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B6" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D6" s="134" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="134" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B7" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D7" s="134" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="134" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B8" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="134" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B9" s="134" t="s">
         <v>59</v>
@@ -15395,12 +15409,12 @@
         <v>60</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="134" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B10" s="134" t="s">
         <v>5</v>
@@ -15409,7 +15423,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="11">
@@ -15428,7 +15442,7 @@
     </row>
     <row r="12">
       <c r="A12" s="134" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B12" s="134" t="s">
         <v>5</v>
@@ -15437,7 +15451,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="134" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="13">
@@ -15456,7 +15470,7 @@
     </row>
     <row r="14">
       <c r="A14" s="134" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="B14" s="134" t="s">
         <v>5</v>
@@ -15465,12 +15479,12 @@
         <v>15</v>
       </c>
       <c r="D14" s="134" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="134" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B15" s="134" t="s">
         <v>5</v>
@@ -15479,12 +15493,12 @@
         <v>15</v>
       </c>
       <c r="D15" s="134" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="134" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B16" s="134" t="s">
         <v>5</v>
@@ -15493,12 +15507,12 @@
         <v>72</v>
       </c>
       <c r="D16" s="134" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="134" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B17" s="134" t="s">
         <v>5</v>
@@ -15507,54 +15521,54 @@
         <v>75</v>
       </c>
       <c r="D17" s="134" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="134" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B18" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="134" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D18" s="134" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="134" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="B19" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="134" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="134" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B20" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="134" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D20" s="134" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="134" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="B21" s="134" t="s">
         <v>5</v>
@@ -15563,7 +15577,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="134" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="22">
@@ -15588,15 +15602,15 @@
         <v>5</v>
       </c>
       <c r="C23" s="134" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D23" s="134" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="134" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B24" s="134" t="s">
         <v>59</v>
@@ -15605,7 +15619,7 @@
         <v>60</v>
       </c>
       <c r="D24" s="134" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="25">
@@ -15624,105 +15638,105 @@
     </row>
     <row r="26">
       <c r="A26" s="134" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B26" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="134" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="D26" s="134" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="134" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="B27" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="134" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D27" s="134" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="134" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B28" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="134" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D28" s="134" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="134" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B29" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="134" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D29" s="134" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="134" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B30" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="134" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D30" s="134" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="134" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="B31" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="134" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="D31" s="134" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="134" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B32" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="134" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D32" s="134" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="134" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B33" s="134" t="s">
         <v>59</v>
@@ -15731,7 +15745,7 @@
         <v>60</v>
       </c>
       <c r="D33" s="134" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="34">
@@ -15742,7 +15756,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="134" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D34" s="134" t="s">
         <v>386</v>
@@ -15750,7 +15764,7 @@
     </row>
     <row r="35">
       <c r="A35" s="134" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="B35" s="134" t="s">
         <v>5</v>
@@ -15759,12 +15773,12 @@
         <v>15</v>
       </c>
       <c r="D35" s="134" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="134" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B36" s="134" t="s">
         <v>5</v>
@@ -15773,21 +15787,21 @@
         <v>15</v>
       </c>
       <c r="D36" s="134" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="134" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B37" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="134" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D37" s="134" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="38">
@@ -15801,7 +15815,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="134" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="39">
@@ -15815,12 +15829,12 @@
         <v>15</v>
       </c>
       <c r="D39" s="134" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="134" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B40" s="134" t="s">
         <v>5</v>
@@ -15829,40 +15843,40 @@
         <v>15</v>
       </c>
       <c r="D40" s="134" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="134" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B41" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="134" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D41" s="134" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="134" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B42" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="134" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D42" s="134" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="134" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B43" s="134" t="s">
         <v>5</v>
@@ -15871,21 +15885,21 @@
         <v>15</v>
       </c>
       <c r="D43" s="134" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="134" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B44" s="134" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="134" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D44" s="134" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>
@@ -15903,7 +15917,7 @@
         <v>392</v>
       </c>
       <c r="B1" s="136" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -15942,16 +15956,16 @@
     </row>
     <row r="4">
       <c r="A4" s="136" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B4" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="136" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D4" s="136" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5">
@@ -15962,7 +15976,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="136" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D5" s="136" t="s">
         <v>494</v>
@@ -15970,7 +15984,7 @@
     </row>
     <row r="6">
       <c r="A6" s="136" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B6" s="136" t="s">
         <v>5</v>
@@ -15979,26 +15993,26 @@
         <v>64</v>
       </c>
       <c r="D6" s="136" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="136" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="B7" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="136" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D7" s="136" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="136" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="B8" s="136" t="s">
         <v>5</v>
@@ -16007,77 +16021,77 @@
         <v>78</v>
       </c>
       <c r="D8" s="136" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="136" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B9" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="136" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D9" s="136" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="136" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B10" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="136" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D10" s="136" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="136" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B11" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="136" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D11" s="136" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="136" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B12" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="136" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D12" s="136" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="136" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B13" s="136" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="136" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D13" s="136" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="14">
@@ -16105,12 +16119,12 @@
         <v>15</v>
       </c>
       <c r="D15" s="136" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="136" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="B16" s="136" t="s">
         <v>59</v>
@@ -16119,12 +16133,12 @@
         <v>60</v>
       </c>
       <c r="D16" s="136" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="136" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B17" s="136" t="s">
         <v>59</v>
@@ -16133,12 +16147,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="136" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="136" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B18" s="136" t="s">
         <v>5</v>
@@ -16147,7 +16161,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="136" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="19">
@@ -16183,7 +16197,7 @@
         <v>392</v>
       </c>
       <c r="B1" s="138" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16222,21 +16236,21 @@
     </row>
     <row r="4">
       <c r="A4" s="138" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B4" s="138" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="138" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B5" s="138" t="s">
         <v>5</v>
@@ -16245,7 +16259,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="138" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="6">
@@ -16417,7 +16431,7 @@
         <v>392</v>
       </c>
       <c r="B1" s="140" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16456,16 +16470,16 @@
     </row>
     <row r="4">
       <c r="A4" s="140" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B4" s="140" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="140" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D4" s="140" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="5">
@@ -16501,7 +16515,7 @@
         <v>392</v>
       </c>
       <c r="B1" s="142" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16540,7 +16554,7 @@
     </row>
     <row r="4">
       <c r="A4" s="142" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="B4" s="142" t="s">
         <v>59</v>
@@ -16549,7 +16563,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="142" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="5">
@@ -16582,7 +16596,7 @@
     </row>
     <row r="7">
       <c r="A7" s="142" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B7" s="142" t="s">
         <v>5</v>
@@ -16591,40 +16605,40 @@
         <v>15</v>
       </c>
       <c r="D7" s="142" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="142" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B8" s="142" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="142" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D8" s="142" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="142" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B9" s="142" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="142" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D9" s="142" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="142" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="B10" s="142" t="s">
         <v>5</v>
@@ -16633,7 +16647,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="142" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
     </row>
   </sheetData>
@@ -16655,7 +16669,7 @@
         <v>392</v>
       </c>
       <c r="B1" s="144" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -16694,7 +16708,7 @@
     </row>
     <row r="4">
       <c r="A4" s="144" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="B4" s="144" t="s">
         <v>5</v>
@@ -16703,21 +16717,21 @@
         <v>64</v>
       </c>
       <c r="D4" s="144" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="144" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B5" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="144" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="6">
@@ -16736,7 +16750,7 @@
     </row>
     <row r="7">
       <c r="A7" s="144" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="B7" s="144" t="s">
         <v>5</v>
@@ -16745,12 +16759,12 @@
         <v>15</v>
       </c>
       <c r="D7" s="144" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="144" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="B8" s="144" t="s">
         <v>59</v>
@@ -16759,35 +16773,35 @@
         <v>60</v>
       </c>
       <c r="D8" s="144" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="144" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B9" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="144" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D9" s="144" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="144" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B10" s="144" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="144" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D10" s="144" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
@@ -16820,7 +16834,7 @@
     </row>
     <row r="2">
       <c r="A2" s="146" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="B2" s="146" t="s">
         <v>5</v>
@@ -16829,12 +16843,12 @@
         <v>66</v>
       </c>
       <c r="D2" s="146" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="146" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B3" s="146" t="s">
         <v>5</v>
@@ -16843,12 +16857,12 @@
         <v>69</v>
       </c>
       <c r="D3" s="146" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="146" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="B4" s="146" t="s">
         <v>5</v>
@@ -16857,12 +16871,12 @@
         <v>72</v>
       </c>
       <c r="D4" s="146" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="146" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="B5" s="146" t="s">
         <v>5</v>
@@ -16871,40 +16885,40 @@
         <v>72</v>
       </c>
       <c r="D5" s="146" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="146" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="B6" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="146" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D6" s="146" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="146" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="B7" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="146" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D7" s="146" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="146" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B8" s="146" t="s">
         <v>5</v>
@@ -16913,12 +16927,12 @@
         <v>343</v>
       </c>
       <c r="D8" s="146" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="146" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B9" s="146" t="s">
         <v>5</v>
@@ -16927,21 +16941,21 @@
         <v>346</v>
       </c>
       <c r="D9" s="146" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="146" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="B10" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="146" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D10" s="146" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="11">
@@ -16998,35 +17012,35 @@
     </row>
     <row r="3">
       <c r="A3" s="148" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="148" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D3" s="148" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="148" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B4" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="148" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D4" s="148" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="148" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B5" s="148" t="s">
         <v>5</v>
@@ -17035,7 +17049,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="6">
@@ -17049,35 +17063,35 @@
         <v>15</v>
       </c>
       <c r="D6" s="148" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="148" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B7" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="148" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D7" s="148" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="148" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="B8" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="148" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9">
@@ -17110,7 +17124,7 @@
     </row>
     <row r="11">
       <c r="A11" s="148" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="B11" s="148" t="s">
         <v>5</v>
@@ -17119,12 +17133,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="148" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B12" s="148" t="s">
         <v>5</v>
@@ -17133,7 +17147,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13">
@@ -17152,7 +17166,7 @@
     </row>
     <row r="14">
       <c r="A14" s="148" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="B14" s="148" t="s">
         <v>5</v>
@@ -17161,7 +17175,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="148" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="15">
@@ -17175,21 +17189,21 @@
         <v>445</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="148" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B16" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="148" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D16" s="148" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="17">
@@ -17250,7 +17264,7 @@
     </row>
     <row r="21">
       <c r="A21" s="148" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B21" s="148" t="s">
         <v>5</v>
@@ -17259,7 +17273,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="148" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="22">
@@ -17278,7 +17292,7 @@
     </row>
     <row r="23">
       <c r="A23" s="148" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="B23" s="148" t="s">
         <v>59</v>
@@ -17287,15 +17301,15 @@
         <v>60</v>
       </c>
       <c r="D23" s="148" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="148" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="B24" s="148" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="C24" s="148" t="s">
         <v>64</v>
@@ -17306,10 +17320,10 @@
     </row>
     <row r="25">
       <c r="A25" s="148" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="B25" s="148" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="C25" s="148" t="s">
         <v>64</v>
@@ -17320,7 +17334,7 @@
     </row>
     <row r="26">
       <c r="A26" s="148" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="B26" s="148" t="s">
         <v>59</v>
@@ -17329,12 +17343,12 @@
         <v>60</v>
       </c>
       <c r="D26" s="148" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="148" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="B27" s="148" t="s">
         <v>59</v>
@@ -17343,7 +17357,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="148" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="28">
@@ -17362,7 +17376,7 @@
     </row>
     <row r="29">
       <c r="A29" s="148" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="B29" s="148" t="s">
         <v>59</v>
@@ -17371,12 +17385,12 @@
         <v>60</v>
       </c>
       <c r="D29" s="148" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="148" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="B30" s="148" t="s">
         <v>59</v>
@@ -17385,7 +17399,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="148" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="31">
@@ -17404,7 +17418,7 @@
     </row>
     <row r="32">
       <c r="A32" s="148" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="B32" s="148" t="s">
         <v>59</v>
@@ -17413,7 +17427,7 @@
         <v>60</v>
       </c>
       <c r="D32" s="148" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="33">
@@ -17432,7 +17446,7 @@
     </row>
     <row r="34">
       <c r="A34" s="148" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="B34" s="148" t="s">
         <v>5</v>
@@ -17441,12 +17455,12 @@
         <v>15</v>
       </c>
       <c r="D34" s="148" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="148" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B35" s="148" t="s">
         <v>5</v>
@@ -17455,12 +17469,12 @@
         <v>27</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="148" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="B36" s="148" t="s">
         <v>59</v>
@@ -17469,7 +17483,7 @@
         <v>99</v>
       </c>
       <c r="D36" s="148" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="37">
@@ -17519,7 +17533,7 @@
         <v>412</v>
       </c>
       <c r="B40" s="148" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="C40" s="148" t="s">
         <v>64</v>
@@ -17558,7 +17572,7 @@
     </row>
     <row r="43">
       <c r="A43" s="148" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B43" s="148" t="s">
         <v>59</v>
@@ -17567,7 +17581,7 @@
         <v>99</v>
       </c>
       <c r="D43" s="148" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="44">
@@ -17581,12 +17595,12 @@
         <v>415</v>
       </c>
       <c r="D44" s="148" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="148" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="B45" s="148" t="s">
         <v>59</v>
@@ -17595,7 +17609,7 @@
         <v>99</v>
       </c>
       <c r="D45" s="148" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="46">
@@ -17614,128 +17628,128 @@
     </row>
     <row r="47">
       <c r="A47" s="148" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="B47" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C47" s="148" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="D47" s="148" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="148" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="B48" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C48" s="148" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D48" s="148" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="148" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="B49" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="148" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="D49" s="148" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="148" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="B50" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C50" s="148" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D50" s="148" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="148" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="B51" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="148" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D51" s="148" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="148" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="B52" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C52" s="148" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D52" s="148" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="148" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="B53" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="148" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D53" s="148" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="148" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B54" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C54" s="148" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="D54" s="148" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="148" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="B55" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C55" s="148" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="D55" s="148" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="56">
@@ -17754,7 +17768,7 @@
     </row>
     <row r="57">
       <c r="A57" s="148" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="B57" s="148" t="s">
         <v>5</v>
@@ -17763,12 +17777,12 @@
         <v>64</v>
       </c>
       <c r="D57" s="148" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="148" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="B58" s="148" t="s">
         <v>59</v>
@@ -17777,12 +17791,12 @@
         <v>99</v>
       </c>
       <c r="D58" s="148" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="148" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="B59" s="148" t="s">
         <v>5</v>
@@ -17791,7 +17805,7 @@
         <v>15</v>
       </c>
       <c r="D59" s="148" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="60">
@@ -17805,7 +17819,7 @@
         <v>64</v>
       </c>
       <c r="D60" s="148" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="61">
@@ -17819,7 +17833,7 @@
         <v>64</v>
       </c>
       <c r="D61" s="148" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="62">
@@ -17827,7 +17841,7 @@
         <v>114</v>
       </c>
       <c r="B62" s="148" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="C62" s="148" t="s">
         <v>64</v>
@@ -17858,15 +17872,15 @@
         <v>5</v>
       </c>
       <c r="C64" s="148" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="D64" s="148" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="148" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="B65" s="148" t="s">
         <v>59</v>
@@ -17875,7 +17889,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="148" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="66">
@@ -17897,7 +17911,7 @@
         <v>429</v>
       </c>
       <c r="B67" s="148" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="C67" s="148" t="s">
         <v>64</v>
@@ -17911,7 +17925,7 @@
         <v>431</v>
       </c>
       <c r="B68" s="148" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="C68" s="148" t="s">
         <v>64</v>
@@ -17922,7 +17936,7 @@
     </row>
     <row r="69">
       <c r="A69" s="148" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="B69" s="148" t="s">
         <v>5</v>
@@ -17931,12 +17945,12 @@
         <v>27</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="148" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="B70" s="148" t="s">
         <v>5</v>
@@ -17945,7 +17959,7 @@
         <v>27</v>
       </c>
       <c r="D70" s="148" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="71">
@@ -18128,35 +18142,35 @@
     </row>
     <row r="3">
       <c r="A3" s="150" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="B3" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="150" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D3" s="150" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="150" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B4" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="150" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="150" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B5" s="150" t="s">
         <v>5</v>
@@ -18165,7 +18179,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="150" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="6">
@@ -18176,15 +18190,15 @@
         <v>5</v>
       </c>
       <c r="C6" s="150" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D6" s="150" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="150" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="B7" s="150" t="s">
         <v>5</v>
@@ -18193,21 +18207,21 @@
         <v>15</v>
       </c>
       <c r="D7" s="150" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="150" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="B8" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="150" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="D8" s="150" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="9">
@@ -18226,38 +18240,38 @@
     </row>
     <row r="10">
       <c r="A10" s="150" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B10" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="150" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D10" s="150" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="150" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="B11" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="150" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D11" s="150" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="150" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="B12" s="150" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="C12" s="150" t="s">
         <v>64</v>
@@ -18268,10 +18282,10 @@
     </row>
     <row r="13">
       <c r="A13" s="150" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="B13" s="150" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="C13" s="150" t="s">
         <v>64</v>
@@ -18282,7 +18296,7 @@
     </row>
     <row r="14">
       <c r="A14" s="150" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B14" s="150" t="s">
         <v>5</v>
@@ -18291,7 +18305,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="150" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="15">
@@ -18310,7 +18324,7 @@
     </row>
     <row r="16">
       <c r="A16" s="150" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="B16" s="150" t="s">
         <v>5</v>
@@ -18319,7 +18333,7 @@
         <v>27</v>
       </c>
       <c r="D16" s="150" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="17">
@@ -18338,16 +18352,16 @@
     </row>
     <row r="18">
       <c r="A18" s="150" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B18" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="150" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D18" s="150" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="19">
@@ -18408,7 +18422,7 @@
     </row>
     <row r="23">
       <c r="A23" s="150" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B23" s="150" t="s">
         <v>5</v>
@@ -18417,7 +18431,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="150" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="24">
@@ -18464,7 +18478,7 @@
     </row>
     <row r="27">
       <c r="A27" s="150" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="B27" s="150" t="s">
         <v>59</v>
@@ -18473,7 +18487,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="150" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="28">
@@ -18492,7 +18506,7 @@
     </row>
     <row r="29">
       <c r="A29" s="150" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="B29" s="150" t="s">
         <v>59</v>
@@ -18501,7 +18515,7 @@
         <v>60</v>
       </c>
       <c r="D29" s="150" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="30">
@@ -18551,7 +18565,7 @@
         <v>412</v>
       </c>
       <c r="B33" s="150" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="C33" s="150" t="s">
         <v>64</v>
@@ -18562,7 +18576,7 @@
     </row>
     <row r="34">
       <c r="A34" s="150" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="B34" s="150" t="s">
         <v>59</v>
@@ -18571,7 +18585,7 @@
         <v>99</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="35">
@@ -18590,7 +18604,7 @@
     </row>
     <row r="36">
       <c r="A36" s="150" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="B36" s="150" t="s">
         <v>59</v>
@@ -18599,7 +18613,7 @@
         <v>99</v>
       </c>
       <c r="D36" s="150" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="37">
@@ -18618,128 +18632,128 @@
     </row>
     <row r="38">
       <c r="A38" s="150" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="B38" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="150" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="D38" s="150" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="150" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="B39" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="150" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="D39" s="150" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="150" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="B40" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="150" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D40" s="150" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="150" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="B41" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="150" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D41" s="150" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="150" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="B42" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="150" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D42" s="150" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="150" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="B43" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="150" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D43" s="150" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="150" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="B44" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="150" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D44" s="150" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="150" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B45" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C45" s="150" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="D45" s="150" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="150" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="B46" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="150" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="D46" s="150" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="47">
@@ -18767,7 +18781,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="150" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="49">
@@ -18775,7 +18789,7 @@
         <v>429</v>
       </c>
       <c r="B49" s="150" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="C49" s="150" t="s">
         <v>64</v>
@@ -18789,7 +18803,7 @@
         <v>431</v>
       </c>
       <c r="B50" s="150" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="C50" s="150" t="s">
         <v>64</v>
@@ -18800,7 +18814,7 @@
     </row>
     <row r="51">
       <c r="A51" s="150" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="B51" s="150" t="s">
         <v>5</v>
@@ -18809,7 +18823,7 @@
         <v>27</v>
       </c>
       <c r="D51" s="150" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="52">
@@ -18817,7 +18831,7 @@
         <v>466</v>
       </c>
       <c r="B52" s="150" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="C52" s="150" t="s">
         <v>64</v>
@@ -18852,35 +18866,35 @@
     </row>
     <row r="2">
       <c r="A2" s="152" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B2" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="152" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D2" s="152" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="152" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B3" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="152" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="152" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B4" s="152" t="s">
         <v>5</v>
@@ -18889,35 +18903,35 @@
         <v>15</v>
       </c>
       <c r="D4" s="152" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="152" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B5" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="152" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="D5" s="152" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="152" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="B6" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="152" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="D6" s="152" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
     </row>
   </sheetData>
@@ -18946,7 +18960,7 @@
     </row>
     <row r="2">
       <c r="A2" s="154" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="B2" s="154" t="s">
         <v>5</v>
@@ -18955,12 +18969,12 @@
         <v>72</v>
       </c>
       <c r="D2" s="154" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="154" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="B3" s="154" t="s">
         <v>5</v>
@@ -18969,12 +18983,12 @@
         <v>75</v>
       </c>
       <c r="D3" s="154" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="154" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="B4" s="154" t="s">
         <v>5</v>
@@ -18983,12 +18997,12 @@
         <v>66</v>
       </c>
       <c r="D4" s="154" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="154" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="B5" s="154" t="s">
         <v>5</v>
@@ -18997,91 +19011,91 @@
         <v>69</v>
       </c>
       <c r="D5" s="154" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="154" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="B6" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="154" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="D6" s="154" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="154" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="B7" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="154" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="D7" s="154" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="154" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="B8" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="154" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D8" s="154" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="154" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="B9" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="154" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D9" s="154" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="154" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B10" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="154" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D10" s="154" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="154" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B11" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="154" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D11" s="154" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -19110,7 +19124,7 @@
     </row>
     <row r="2">
       <c r="A2" s="156" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="B2" s="156" t="s">
         <v>5</v>
@@ -19119,12 +19133,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="156" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="156" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="B3" s="156" t="s">
         <v>59</v>
@@ -19133,96 +19147,96 @@
         <v>60</v>
       </c>
       <c r="D3" s="156" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="156" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B4" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="156" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D4" s="156" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="156" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="B5" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="156" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D5" s="156" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="156" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B6" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="156" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D6" s="156" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="156" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B7" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="156" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="D7" s="156" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="156" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B8" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="156" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D8" s="156" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="156" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B9" s="156" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="C9" s="156" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="156" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="156" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="B10" s="156" t="s">
         <v>5</v>
@@ -19231,12 +19245,12 @@
         <v>15</v>
       </c>
       <c r="D10" s="156" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="156" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="B11" s="156" t="s">
         <v>5</v>
@@ -19245,26 +19259,26 @@
         <v>15</v>
       </c>
       <c r="D11" s="156" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="156" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="B12" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="156" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="D12" s="156" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="156" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="B13" s="156" t="s">
         <v>5</v>
@@ -19273,26 +19287,26 @@
         <v>15</v>
       </c>
       <c r="D13" s="156" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="156" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B14" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="156" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="D14" s="156" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="156" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B15" s="156" t="s">
         <v>59</v>
@@ -19301,7 +19315,7 @@
         <v>60</v>
       </c>
       <c r="D15" s="156" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -19414,16 +19428,16 @@
     </row>
     <row r="8">
       <c r="A8" s="158" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="B8" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="158" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="D8" s="158" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="9">
@@ -19442,21 +19456,21 @@
     </row>
     <row r="10">
       <c r="A10" s="158" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B10" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="158" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="D10" s="158" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="158" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B11" s="158" t="s">
         <v>5</v>
@@ -19465,21 +19479,21 @@
         <v>15</v>
       </c>
       <c r="D11" s="158" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="158" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B12" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="158" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="D12" s="158" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
     </row>
   </sheetData>
@@ -19560,7 +19574,7 @@
     </row>
     <row r="2">
       <c r="A2" s="160" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B2" s="160" t="s">
         <v>5</v>
@@ -19569,12 +19583,12 @@
         <v>27</v>
       </c>
       <c r="D2" s="160" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="160" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B3" s="160" t="s">
         <v>128</v>
@@ -19583,12 +19597,12 @@
         <v>64</v>
       </c>
       <c r="D3" s="160" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="160" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="B4" s="160" t="s">
         <v>177</v>
@@ -19626,7 +19640,7 @@
     </row>
     <row r="2">
       <c r="A2" s="162" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B2" s="162" t="s">
         <v>5</v>
@@ -19635,12 +19649,12 @@
         <v>64</v>
       </c>
       <c r="D2" s="162" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="162" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B3" s="162" t="s">
         <v>59</v>
@@ -19649,12 +19663,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="162" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="162" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B4" s="162" t="s">
         <v>59</v>
@@ -19663,7 +19677,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="162" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="5">
@@ -19696,7 +19710,7 @@
     </row>
     <row r="7">
       <c r="A7" s="162" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B7" s="162" t="s">
         <v>59</v>
@@ -19705,12 +19719,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="162" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="162" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B8" s="162" t="s">
         <v>59</v>
@@ -19719,7 +19733,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="162" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="9">
@@ -19766,7 +19780,7 @@
     </row>
     <row r="12">
       <c r="A12" s="162" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B12" s="162" t="s">
         <v>59</v>
@@ -19775,7 +19789,7 @@
         <v>99</v>
       </c>
       <c r="D12" s="162" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="13">
@@ -19794,16 +19808,16 @@
     </row>
     <row r="14">
       <c r="A14" s="162" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B14" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="162" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D14" s="162" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="15">
@@ -19864,21 +19878,21 @@
     </row>
     <row r="19">
       <c r="A19" s="162" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B19" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="162" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D19" s="162" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="162" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B20" s="162" t="s">
         <v>5</v>
@@ -19887,26 +19901,26 @@
         <v>15</v>
       </c>
       <c r="D20" s="162" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="162" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B21" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="162" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="D21" s="162" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="162" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="B22" s="162" t="s">
         <v>5</v>
@@ -19915,7 +19929,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="162" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="23">
@@ -19948,7 +19962,7 @@
     </row>
     <row r="25">
       <c r="A25" s="162" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="B25" s="162" t="s">
         <v>59</v>
@@ -19957,7 +19971,7 @@
         <v>99</v>
       </c>
       <c r="D25" s="162" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="26">
@@ -19976,7 +19990,7 @@
     </row>
     <row r="27">
       <c r="A27" s="162" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="B27" s="162" t="s">
         <v>5</v>
@@ -19985,12 +19999,12 @@
         <v>64</v>
       </c>
       <c r="D27" s="162" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="162" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="B28" s="162" t="s">
         <v>59</v>
@@ -19999,7 +20013,7 @@
         <v>60</v>
       </c>
       <c r="D28" s="162" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
     </row>
   </sheetData>
@@ -20028,7 +20042,7 @@
     </row>
     <row r="2">
       <c r="A2" s="164" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B2" s="164" t="s">
         <v>5</v>
@@ -20037,12 +20051,12 @@
         <v>64</v>
       </c>
       <c r="D2" s="164" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="164" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B3" s="164" t="s">
         <v>59</v>
@@ -20051,12 +20065,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="164" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="164" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B4" s="164" t="s">
         <v>59</v>
@@ -20065,7 +20079,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="164" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="5">
@@ -20098,7 +20112,7 @@
     </row>
     <row r="7">
       <c r="A7" s="164" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B7" s="164" t="s">
         <v>59</v>
@@ -20107,12 +20121,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="164" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="164" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B8" s="164" t="s">
         <v>59</v>
@@ -20121,7 +20135,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="164" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="9">
@@ -20196,63 +20210,63 @@
     </row>
     <row r="14">
       <c r="A14" s="164" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="B14" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="164" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="D14" s="164" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="164" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="B15" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="164" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="D15" s="164" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="164" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="B16" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="164" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="D16" s="164" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="164" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="B17" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="164" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="D17" s="164" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="164" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="B18" s="164" t="s">
         <v>5</v>
@@ -20261,7 +20275,7 @@
         <v>64</v>
       </c>
       <c r="D18" s="164" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="19">
@@ -20280,58 +20294,58 @@
     </row>
     <row r="20">
       <c r="A20" s="164" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="B20" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="164" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="D20" s="164" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="164" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="B21" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="164" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="164" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="B22" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="164" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="D22" s="164" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="164" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B23" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="164" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="D23" s="164" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="24">
@@ -20345,12 +20359,12 @@
         <v>378</v>
       </c>
       <c r="D24" s="164" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="164" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="B25" s="164" t="s">
         <v>5</v>
@@ -20359,21 +20373,21 @@
         <v>15</v>
       </c>
       <c r="D25" s="164" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="164" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B26" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="D26" s="164" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
     </row>
   </sheetData>
@@ -20416,7 +20430,7 @@
     </row>
     <row r="3">
       <c r="A3" s="166" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B3" s="166" t="s">
         <v>5</v>
@@ -20425,7 +20439,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="166" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="4">
@@ -20444,7 +20458,7 @@
     </row>
     <row r="5">
       <c r="A5" s="166" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="B5" s="166" t="s">
         <v>5</v>
@@ -20453,7 +20467,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="166" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="6">
@@ -20472,35 +20486,35 @@
     </row>
     <row r="7">
       <c r="A7" s="166" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B7" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="166" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="D7" s="166" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="166" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="B8" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="166" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="D8" s="166" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="166" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="B9" s="166" t="s">
         <v>59</v>
@@ -20509,7 +20523,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="166" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="10">
@@ -20528,7 +20542,7 @@
     </row>
     <row r="11">
       <c r="A11" s="166" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="B11" s="166" t="s">
         <v>5</v>
@@ -20537,12 +20551,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="166" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="166" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B12" s="166" t="s">
         <v>59</v>
@@ -20551,7 +20565,7 @@
         <v>99</v>
       </c>
       <c r="D12" s="166" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="13">
@@ -20570,7 +20584,7 @@
     </row>
     <row r="14">
       <c r="A14" s="166" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B14" s="166" t="s">
         <v>59</v>
@@ -20579,7 +20593,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="166" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="15">
@@ -20612,7 +20626,7 @@
     </row>
     <row r="17">
       <c r="A17" s="166" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B17" s="166" t="s">
         <v>59</v>
@@ -20621,12 +20635,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="166" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="166" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B18" s="166" t="s">
         <v>59</v>
@@ -20635,12 +20649,12 @@
         <v>60</v>
       </c>
       <c r="D18" s="166" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="166" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B19" s="166" t="s">
         <v>59</v>
@@ -20649,7 +20663,7 @@
         <v>60</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="20">
@@ -20682,16 +20696,16 @@
     </row>
     <row r="22">
       <c r="A22" s="166" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B22" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="166" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="D22" s="166" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="23">
@@ -20710,7 +20724,7 @@
     </row>
     <row r="24">
       <c r="A24" s="166" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="B24" s="166" t="s">
         <v>59</v>
@@ -20719,7 +20733,7 @@
         <v>99</v>
       </c>
       <c r="D24" s="166" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="25">
@@ -20738,21 +20752,21 @@
     </row>
     <row r="26">
       <c r="A26" s="166" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="B26" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="166" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D26" s="166" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="166" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="B27" s="166" t="s">
         <v>63</v>
@@ -20766,16 +20780,16 @@
     </row>
     <row r="28">
       <c r="A28" s="166" t="s">
-        <v>1340</v>
+        <v>539</v>
       </c>
       <c r="B28" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="166" t="s">
-        <v>1341</v>
+        <v>540</v>
       </c>
       <c r="D28" s="166" t="s">
-        <v>1342</v>
+        <v>541</v>
       </c>
     </row>
     <row r="29">
@@ -20789,7 +20803,7 @@
         <v>524</v>
       </c>
       <c r="D29" s="166" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="30">
@@ -20808,7 +20822,7 @@
     </row>
     <row r="31">
       <c r="A31" s="166" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B31" s="166" t="s">
         <v>177</v>
@@ -20822,7 +20836,7 @@
     </row>
     <row r="32">
       <c r="A32" s="166" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="B32" s="166" t="s">
         <v>59</v>
@@ -20831,12 +20845,12 @@
         <v>60</v>
       </c>
       <c r="D32" s="166" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="166" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B33" s="166" t="s">
         <v>172</v>
@@ -21010,7 +21024,7 @@
     </row>
     <row r="3">
       <c r="A3" s="170" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B3" s="170" t="s">
         <v>5</v>
@@ -21062,7 +21076,7 @@
     </row>
     <row r="3">
       <c r="A3" s="172" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B3" s="172" t="s">
         <v>5</v>
@@ -21071,7 +21085,7 @@
         <v>1356</v>
       </c>
       <c r="D3" s="172" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4">
@@ -21897,7 +21911,7 @@
     </row>
     <row r="3">
       <c r="A3" s="176" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B3" s="176" t="s">
         <v>172</v>
@@ -21911,7 +21925,7 @@
     </row>
     <row r="4">
       <c r="A4" s="176" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B4" s="176" t="s">
         <v>172</v>
@@ -21959,7 +21973,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="176" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D7" s="176" t="s">
         <v>1401</v>
@@ -21973,7 +21987,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="176" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D8" s="176" t="s">
         <v>1403</v>
@@ -21981,13 +21995,13 @@
     </row>
     <row r="9">
       <c r="A9" s="176" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B9" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="176" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D9" s="176" t="s">
         <v>1404</v>
@@ -22001,7 +22015,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="176" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D10" s="176" t="s">
         <v>1406</v>
@@ -22015,7 +22029,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="176" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D11" s="176" t="s">
         <v>1408</v>
@@ -22029,7 +22043,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="176" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D12" s="176" t="s">
         <v>1410</v>
@@ -22043,7 +22057,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="176" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D13" s="176" t="s">
         <v>1412</v>
@@ -22057,7 +22071,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="176" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D14" s="176" t="s">
         <v>1414</v>
@@ -22065,7 +22079,7 @@
     </row>
     <row r="15">
       <c r="A15" s="176" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B15" s="176" t="s">
         <v>144</v>
@@ -22252,7 +22266,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="178" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D7" s="178" t="s">
         <v>1428</v>
@@ -22266,7 +22280,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="178" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D8" s="178" t="s">
         <v>1429</v>
